--- a/pdb/nsp3/SARS-CoV-2/domains_and_infos_of_nsp3.xlsx
+++ b/pdb/nsp3/SARS-CoV-2/domains_and_infos_of_nsp3.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1666" uniqueCount="711">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1771" uniqueCount="755">
   <si>
     <t>nsp3_Macro1_</t>
   </si>
@@ -340,6 +340,15 @@
     <t>PANDDA ANALYSIS GROUP DEPOSITION -- CRYSTAL STRUCTURE OF SARS-COV-2 NSP3 MACRODOMAIN IN COMPLEX WITH ZINC000019685960</t>
   </si>
   <si>
+    <t>7twt</t>
+  </si>
+  <si>
+    <t>CRYSTAL STRUCTURE OF SARS-COV-2 NSP3 MACRODOMAIN IN COMPLEX WITH ADP- RIBOSE AT PH 4 (P43 CRYSTAL FORM)</t>
+  </si>
+  <si>
+    <t>2022-02-07</t>
+  </si>
+  <si>
     <t>5ruw</t>
   </si>
   <si>
@@ -394,6 +403,12 @@
     <t>PANDDA ANALYSIS GROUP DEPOSITION -- CRYSTAL STRUCTURE OF SARS-COV-2 NSP3 MACRODOMAIN IN COMPLEX WITH ZINC000000251609</t>
   </si>
   <si>
+    <t>7twr</t>
+  </si>
+  <si>
+    <t>CRYSTAL STRUCTURE OF SARS-COV-2 NSP3 MACRODOMAIN AT PH 8 (P43 CRYSTAL FORM)</t>
+  </si>
+  <si>
     <t>5s3p</t>
   </si>
   <si>
@@ -406,6 +421,15 @@
     <t>PANDDA ANALYSIS GROUP DEPOSITION -- CRYSTAL STRUCTURE OF SARS-COV-2 NSP3 MACRODOMAIN IN COMPLEX WITH NCL-00023825</t>
   </si>
   <si>
+    <t>7tx4</t>
+  </si>
+  <si>
+    <t>NEUTRON CRYSTAL STRUCTURE OF SARS-COV-2 NSP3 MACRODOMAIN AT 293 K (P21 CRYSTAL FORM)</t>
+  </si>
+  <si>
+    <t>X-RAY DIFFRACTION; NEUTRON DIFFRACTION</t>
+  </si>
+  <si>
     <t>5s3l</t>
   </si>
   <si>
@@ -469,6 +493,12 @@
     <t>PANDDA ANALYSIS GROUP DEPOSITION -- CRYSTAL STRUCTURE OF SARS-COV-2 NSP3 MACRODOMAIN IN COMPLEX WITH Z1186029914</t>
   </si>
   <si>
+    <t>7twx</t>
+  </si>
+  <si>
+    <t>CRYSTAL STRUCTURE OF SARS-COV-2 NSP3 MACRODOMAIN IN COMPLEX WITH ADP- RIBOSE AT PH 7 (P43 CRYSTAL FORM)</t>
+  </si>
+  <si>
     <t>5rvo</t>
   </si>
   <si>
@@ -559,6 +589,12 @@
     <t>PANDDA ANALYSIS GROUP DEPOSITION -- CRYSTAL STRUCTURE OF SARS-COV-2 NSP3 MACRODOMAIN IN COMPLEX WITH Z57446103</t>
   </si>
   <si>
+    <t>7twi</t>
+  </si>
+  <si>
+    <t>CRYSTAL STRUCTURE OF SARS-COV-2 NSP3 MACRODOMAIN AT 293 K (P43 CRYSTAL FORM, 539 KGY)</t>
+  </si>
+  <si>
     <t>6ywm</t>
   </si>
   <si>
@@ -574,6 +610,12 @@
     <t>2020-12-03</t>
   </si>
   <si>
+    <t>7twy</t>
+  </si>
+  <si>
+    <t>CRYSTAL STRUCTURE OF SARS-COV-2 NSP3 MACRODOMAIN IN COMPLEX WITH ADP- RIBOSE AT PH 8 (P43 CRYSTAL FORM)</t>
+  </si>
+  <si>
     <t>5s3c</t>
   </si>
   <si>
@@ -676,6 +718,12 @@
     <t>PANDDA ANALYSIS GROUP DEPOSITION -- CRYSTAL STRUCTURE OF SARS-COV-2 NSP3 MACRODOMAIN IN COMPLEX WITH NCL-00023824</t>
   </si>
   <si>
+    <t>7twj</t>
+  </si>
+  <si>
+    <t>CRYSTAL STRUCTURE OF SARS-COV-2 NSP3 MACRODOMAIN AT PH 4 (P43 CRYSTAL FORM)</t>
+  </si>
+  <si>
     <t>5s2l</t>
   </si>
   <si>
@@ -688,6 +736,12 @@
     <t>PANDDA ANALYSIS GROUP DEPOSITION -- CRYSTAL STRUCTURE OF SARS-COV-2 NSP3 MACRODOMAIN IN COMPLEX WITH Z409974522</t>
   </si>
   <si>
+    <t>7tx3</t>
+  </si>
+  <si>
+    <t>NEUTRON CRYSTAL STRUCTURE OF SARS-COV-2 NSP3 MACRODOMAIN AT 293 K (P43 CRYSTAL FORM)</t>
+  </si>
+  <si>
     <t>5ru0</t>
   </si>
   <si>
@@ -751,6 +805,12 @@
     <t>PANDDA ANALYSIS GROUP DEPOSITION -- CRYSTAL STRUCTURE OF SARS-COV-2 NSP3 MACRODOMAIN IN COMPLEX WITH ZINC000000332540</t>
   </si>
   <si>
+    <t>7twf</t>
+  </si>
+  <si>
+    <t>CRYSTAL STRUCTURE OF SARS-COV-2 NSP3 MACRODOMAIN AT 293 K (P43 CRYSTAL FORM, 73 KGY)</t>
+  </si>
+  <si>
     <t>7jme</t>
   </si>
   <si>
@@ -817,6 +877,12 @@
     <t>PANDDA ANALYSIS GROUP DEPOSITION -- CRYSTAL STRUCTURE OF SARS-COV-2 NSP3 MACRODOMAIN IN COMPLEX WITH Z19727416</t>
   </si>
   <si>
+    <t>7twh</t>
+  </si>
+  <si>
+    <t>CRYSTAL STRUCTURE OF SARS-COV-2 NSP3 MACRODOMAIN AT 293 K (P43 CRYSTAL FORM, 290 KGY)</t>
+  </si>
+  <si>
     <t>6w02</t>
   </si>
   <si>
@@ -904,6 +970,12 @@
     <t>PANDDA ANALYSIS GROUP DEPOSITION -- CRYSTAL STRUCTURE OF SARS-COV-2 NSP3 MACRODOMAIN IN COMPLEX WITH ZINC000000159004</t>
   </si>
   <si>
+    <t>7twn</t>
+  </si>
+  <si>
+    <t>CRYSTAL STRUCTURE OF SARS-COV-2 NSP3 MACRODOMAIN AT PH 5 (P43 CRYSTAL FORM)</t>
+  </si>
+  <si>
     <t>5s2w</t>
   </si>
   <si>
@@ -988,6 +1060,12 @@
     <t>PANDDA ANALYSIS GROUP DEPOSITION -- CRYSTAL STRUCTURE OF SARS-COV-2 NSP3 MACRODOMAIN IN COMPLEX WITH Z927746322</t>
   </si>
   <si>
+    <t>7tww</t>
+  </si>
+  <si>
+    <t>CRYSTAL STRUCTURE OF SARS-COV-2 NSP3 MACRODOMAIN IN COMPLEX WITH ADP- RIBOSE AT PH 6 (P43 CRYSTAL FORM)</t>
+  </si>
+  <si>
     <t>5s4j</t>
   </si>
   <si>
@@ -1330,6 +1408,12 @@
     <t>CRYSTAL STRUCTURE OF SARS-COV-2 MACRODOMAIN IN COMPLEX WITH ADP- RIBOSE-PHOSPHATE (ADP-RIBOSE-2'-PHOSPHATE, ADPRP)</t>
   </si>
   <si>
+    <t>7tx5</t>
+  </si>
+  <si>
+    <t>NEUTRON CRYSTAL STRUCTURE OF SARS-COV-2 NSP3 MACRODOMAIN IN COMPLEX WITH ADP-RIBOSE AT 293 K (C2 CRYSTAL FORM)</t>
+  </si>
+  <si>
     <t>5rt0</t>
   </si>
   <si>
@@ -1345,6 +1429,12 @@
     <t>PANDDA ANALYSIS GROUP DEPOSITION -- CRYSTAL STRUCTURE OF SARS-COV-2 NSP3 MACRODOMAIN IN COMPLEX WITH ZINC000000149580</t>
   </si>
   <si>
+    <t>7two</t>
+  </si>
+  <si>
+    <t>CRYSTAL STRUCTURE OF SARS-COV-2 NSP3 MACRODOMAIN AT PH 6 (P43 CRYSTAL FORM)</t>
+  </si>
+  <si>
     <t>5rtf</t>
   </si>
   <si>
@@ -1369,12 +1459,24 @@
     <t>PANDDA ANALYSIS GROUP DEPOSITION -- CRYSTAL STRUCTURE OF SARS-COV-2 NSP3 MACRODOMAIN IN COMPLEX WITH ZINC000019015078</t>
   </si>
   <si>
+    <t>7twp</t>
+  </si>
+  <si>
+    <t>CRYSTAL STRUCTURE OF SARS-COV-2 NSP3 MACRODOMAIN AT PH 7 (P43 CRYSTAL FORM)</t>
+  </si>
+  <si>
     <t>5rsp</t>
   </si>
   <si>
     <t>PANDDA ANALYSIS GROUP DEPOSITION -- CRYSTAL STRUCTURE OF SARS-COV-2 NSP3 MACRODOMAIN IN COMPLEX WITH ZINC000002560357</t>
   </si>
   <si>
+    <t>7tws</t>
+  </si>
+  <si>
+    <t>CRYSTAL STRUCTURE OF SARS-COV-2 NSP3 MACRODOMAIN AT PH 10 (P43 CRYSTAL FORM)</t>
+  </si>
+  <si>
     <t>5rvr</t>
   </si>
   <si>
@@ -1441,6 +1543,12 @@
     <t>PANDDA ANALYSIS GROUP DEPOSITION -- CRYSTAL STRUCTURE OF SARS-COV-2 NSP3 MACRODOMAIN IN COMPLEX WITH Z445856640</t>
   </si>
   <si>
+    <t>7twv</t>
+  </si>
+  <si>
+    <t>CRYSTAL STRUCTURE OF SARS-COV-2 NSP3 MACRODOMAIN IN COMPLEX WITH ADP- RIBOSE AT PH 5 (P43 CRYSTAL FORM)</t>
+  </si>
+  <si>
     <t>5rv4</t>
   </si>
   <si>
@@ -1597,6 +1705,12 @@
     <t>CRYSTAL STRUCTURE OF SARS-COV-2 MACRODOMAIN IN COMPLEX WITH GMP</t>
   </si>
   <si>
+    <t>7tx1</t>
+  </si>
+  <si>
+    <t>CRYSTAL STRUCTURE OF SARS-COV-2 NSP3 MACRODOMAIN IN COMPLEX WITH ADP- RIBOSE AT PH 10 (P43 CRYSTAL FORM)</t>
+  </si>
+  <si>
     <t>5rt3</t>
   </si>
   <si>
@@ -1615,6 +1729,12 @@
     <t>PANDDA ANALYSIS GROUP DEPOSITION -- CRYSTAL STRUCTURE OF SARS-COV-2 NSP3 MACRODOMAIN IN COMPLEX WITH ZINC000000161958</t>
   </si>
   <si>
+    <t>7tx0</t>
+  </si>
+  <si>
+    <t>CRYSTAL STRUCTURE OF SARS-COV-2 NSP3 MACRODOMAIN IN COMPLEX WITH ADP- RIBOSE AT PH 9 (P43 CRYSTAL FORM)</t>
+  </si>
+  <si>
     <t>5s3b</t>
   </si>
   <si>
@@ -1657,6 +1777,12 @@
     <t>PANDDA ANALYSIS GROUP DEPOSITION -- CRYSTAL STRUCTURE OF SARS-COV-2 NSP3 MACRODOMAIN IN COMPLEX WITH Z2856434920</t>
   </si>
   <si>
+    <t>7twq</t>
+  </si>
+  <si>
+    <t>CRYSTAL STRUCTURE OF SARS-COV-2 NSP3 MACRODOMAIN AT PH 9 (P43 CRYSTAL FORM)</t>
+  </si>
+  <si>
     <t>5s1q</t>
   </si>
   <si>
@@ -1673,6 +1799,12 @@
   </si>
   <si>
     <t>PANDDA ANALYSIS GROUP DEPOSITION -- CRYSTAL STRUCTURE OF SARS-COV-2 NSP3 MACRODOMAIN IN COMPLEX WITH ZINC000000001099</t>
+  </si>
+  <si>
+    <t>7twg</t>
+  </si>
+  <si>
+    <t>CRYSTAL STRUCTURE OF SARS-COV-2 NSP3 MACRODOMAIN AT 293 K (P43 CRYSTAL FORM, 153 KGY)</t>
   </si>
   <si>
     <t>6z72</t>
@@ -2490,7 +2622,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E267"/>
+  <dimension ref="A1:E288"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="110.7109375" customWidth="1"/>
@@ -3273,7 +3405,7 @@
         <v>104</v>
       </c>
       <c r="B47">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="C47" t="s">
         <v>105</v>
@@ -3282,18 +3414,18 @@
         <v>8</v>
       </c>
       <c r="E47" t="s">
-        <v>9</v>
+        <v>106</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B48">
         <v>1</v>
       </c>
       <c r="C48" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D48" t="s">
         <v>8</v>
@@ -3304,30 +3436,30 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B49">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="C49" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D49" t="s">
         <v>8</v>
       </c>
       <c r="E49" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B50">
         <v>1.13</v>
       </c>
       <c r="C50" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D50" t="s">
         <v>8</v>
@@ -3338,13 +3470,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B51">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="C51" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D51" t="s">
         <v>8</v>
@@ -3355,47 +3487,47 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B52">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="C52" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D52" t="s">
         <v>8</v>
       </c>
       <c r="E52" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B53">
-        <v>1.19</v>
+        <v>1</v>
       </c>
       <c r="C53" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D53" t="s">
         <v>8</v>
       </c>
       <c r="E53" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B54">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="C54" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D54" t="s">
         <v>8</v>
@@ -3406,64 +3538,64 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B55">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="C55" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D55" t="s">
         <v>8</v>
       </c>
       <c r="E55" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B56">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="C56" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D56" t="s">
         <v>8</v>
       </c>
       <c r="E56" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B57">
-        <v>1.19</v>
+        <v>0.9</v>
       </c>
       <c r="C57" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D57" t="s">
         <v>8</v>
       </c>
       <c r="E57" t="s">
-        <v>21</v>
+        <v>106</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B58">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="C58" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D58" t="s">
         <v>8</v>
@@ -3474,81 +3606,81 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B59">
-        <v>1</v>
+        <v>1.19</v>
       </c>
       <c r="C59" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D59" t="s">
         <v>8</v>
       </c>
       <c r="E59" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B60">
-        <v>1.11</v>
+        <v>1.9</v>
       </c>
       <c r="C60" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D60" t="s">
-        <v>8</v>
+        <v>133</v>
       </c>
       <c r="E60" t="s">
-        <v>21</v>
+        <v>106</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B61">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="C61" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D61" t="s">
         <v>8</v>
       </c>
       <c r="E61" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B62">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="C62" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D62" t="s">
         <v>8</v>
       </c>
       <c r="E62" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B63">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="C63" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D63" t="s">
         <v>8</v>
@@ -3559,47 +3691,47 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B64">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="C64" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D64" t="s">
         <v>8</v>
       </c>
       <c r="E64" t="s">
-        <v>140</v>
+        <v>9</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B65">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="C65" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D65" t="s">
         <v>8</v>
       </c>
       <c r="E65" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B66">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="C66" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D66" t="s">
         <v>8</v>
@@ -3610,217 +3742,217 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B67">
-        <v>1.08</v>
+        <v>2.2</v>
       </c>
       <c r="C67" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D67" t="s">
         <v>8</v>
       </c>
       <c r="E67" t="s">
-        <v>21</v>
+        <v>148</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B68">
-        <v>1.52</v>
+        <v>1</v>
       </c>
       <c r="C68" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D68" t="s">
         <v>8</v>
       </c>
       <c r="E68" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B69">
-        <v>1.03</v>
+        <v>1.26</v>
       </c>
       <c r="C69" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D69" t="s">
         <v>8</v>
       </c>
       <c r="E69" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B70">
-        <v>1.26</v>
+        <v>1.08</v>
       </c>
       <c r="C70" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D70" t="s">
         <v>8</v>
       </c>
       <c r="E70" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B71">
-        <v>1.01</v>
+        <v>0.9</v>
       </c>
       <c r="C71" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D71" t="s">
         <v>8</v>
       </c>
       <c r="E71" t="s">
-        <v>9</v>
+        <v>106</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B72">
-        <v>1.14</v>
+        <v>1.52</v>
       </c>
       <c r="C72" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D72" t="s">
         <v>8</v>
       </c>
       <c r="E72" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B73">
-        <v>0.98</v>
+        <v>1.03</v>
       </c>
       <c r="C73" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D73" t="s">
         <v>8</v>
       </c>
       <c r="E73" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B74">
-        <v>1</v>
+        <v>1.26</v>
       </c>
       <c r="C74" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D74" t="s">
         <v>8</v>
       </c>
       <c r="E74" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B75">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="C75" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D75" t="s">
         <v>8</v>
       </c>
       <c r="E75" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B76">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="C76" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D76" t="s">
         <v>8</v>
       </c>
       <c r="E76" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B77">
-        <v>1.14</v>
+        <v>0.98</v>
       </c>
       <c r="C77" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D77" t="s">
         <v>8</v>
       </c>
       <c r="E77" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B78">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="C78" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D78" t="s">
         <v>8</v>
       </c>
       <c r="E78" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B79">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="C79" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D79" t="s">
         <v>8</v>
@@ -3831,47 +3963,47 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B80">
-        <v>1.18</v>
+        <v>1</v>
       </c>
       <c r="C80" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D80" t="s">
         <v>8</v>
       </c>
       <c r="E80" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B81">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="C81" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D81" t="s">
         <v>8</v>
       </c>
       <c r="E81" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B82">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="C82" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D82" t="s">
         <v>8</v>
@@ -3882,104 +4014,104 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B83">
-        <v>2.16</v>
+        <v>1.09</v>
       </c>
       <c r="C83" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D83" t="s">
         <v>8</v>
       </c>
       <c r="E83" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B84">
-        <v>1.55</v>
+        <v>1.18</v>
       </c>
       <c r="C84" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D84" t="s">
         <v>8</v>
       </c>
       <c r="E84" t="s">
-        <v>181</v>
+        <v>21</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B85">
-        <v>1.19</v>
+        <v>1</v>
       </c>
       <c r="C85" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D85" t="s">
         <v>8</v>
       </c>
       <c r="E85" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B86">
-        <v>1</v>
+        <v>1.16</v>
       </c>
       <c r="C86" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D86" t="s">
         <v>8</v>
       </c>
       <c r="E86" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B87">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="C87" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D87" t="s">
         <v>8</v>
       </c>
       <c r="E87" t="s">
-        <v>9</v>
+        <v>106</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B88">
-        <v>0.95</v>
+        <v>2.16</v>
       </c>
       <c r="C88" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D88" t="s">
         <v>8</v>
       </c>
       <c r="E88" t="s">
-        <v>190</v>
+        <v>30</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -3987,7 +4119,7 @@
         <v>191</v>
       </c>
       <c r="B89">
-        <v>1</v>
+        <v>1.55</v>
       </c>
       <c r="C89" t="s">
         <v>192</v>
@@ -3996,69 +4128,69 @@
         <v>8</v>
       </c>
       <c r="E89" t="s">
-        <v>9</v>
+        <v>193</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B90">
-        <v>1.01</v>
+        <v>0.9</v>
       </c>
       <c r="C90" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D90" t="s">
         <v>8</v>
       </c>
       <c r="E90" t="s">
-        <v>9</v>
+        <v>106</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B91">
-        <v>1</v>
+        <v>1.19</v>
       </c>
       <c r="C91" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D91" t="s">
         <v>8</v>
       </c>
       <c r="E91" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B92">
-        <v>1.19</v>
+        <v>1</v>
       </c>
       <c r="C92" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D92" t="s">
         <v>8</v>
       </c>
       <c r="E92" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B93">
         <v>1</v>
       </c>
       <c r="C93" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D93" t="s">
         <v>8</v>
@@ -4069,81 +4201,81 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B94">
-        <v>1.19</v>
+        <v>0.95</v>
       </c>
       <c r="C94" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D94" t="s">
         <v>8</v>
       </c>
       <c r="E94" t="s">
-        <v>21</v>
+        <v>204</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B95">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="C95" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D95" t="s">
         <v>8</v>
       </c>
       <c r="E95" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B96">
-        <v>3.83</v>
+        <v>1.01</v>
       </c>
       <c r="C96" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D96" t="s">
         <v>8</v>
       </c>
       <c r="E96" t="s">
-        <v>207</v>
+        <v>9</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B97">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="C97" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D97" t="s">
         <v>8</v>
       </c>
       <c r="E97" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B98">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="C98" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D98" t="s">
         <v>8</v>
@@ -4154,30 +4286,30 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B99">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="C99" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D99" t="s">
         <v>8</v>
       </c>
       <c r="E99" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B100">
         <v>1.19</v>
       </c>
       <c r="C100" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D100" t="s">
         <v>8</v>
@@ -4188,13 +4320,13 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B101">
         <v>1.09</v>
       </c>
       <c r="C101" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D101" t="s">
         <v>8</v>
@@ -4205,132 +4337,132 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B102">
-        <v>1.09</v>
+        <v>3.83</v>
       </c>
       <c r="C102" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D102" t="s">
         <v>8</v>
       </c>
       <c r="E102" t="s">
-        <v>21</v>
+        <v>221</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B103">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="C103" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D103" t="s">
         <v>8</v>
       </c>
       <c r="E103" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B104">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="C104" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D104" t="s">
         <v>8</v>
       </c>
       <c r="E104" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B105">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="C105" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D105" t="s">
         <v>8</v>
       </c>
       <c r="E105" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B106">
-        <v>1.45</v>
+        <v>1.19</v>
       </c>
       <c r="C106" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D106" t="s">
         <v>8</v>
       </c>
       <c r="E106" t="s">
-        <v>228</v>
+        <v>21</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B107">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="C107" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D107" t="s">
         <v>8</v>
       </c>
       <c r="E107" t="s">
-        <v>9</v>
+        <v>106</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B108">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="C108" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D108" t="s">
         <v>8</v>
       </c>
       <c r="E108" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B109">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="C109" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D109" t="s">
         <v>8</v>
@@ -4341,30 +4473,30 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B110">
-        <v>1.07</v>
+        <v>1.6</v>
       </c>
       <c r="C110" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D110" t="s">
-        <v>8</v>
+        <v>133</v>
       </c>
       <c r="E110" t="s">
-        <v>21</v>
+        <v>106</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B111">
         <v>1</v>
       </c>
       <c r="C111" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D111" t="s">
         <v>8</v>
@@ -4375,13 +4507,13 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B112">
         <v>1</v>
       </c>
       <c r="C112" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D112" t="s">
         <v>8</v>
@@ -4392,19 +4524,19 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B113">
-        <v>1.55</v>
+        <v>1.04</v>
       </c>
       <c r="C113" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D113" t="s">
         <v>8</v>
       </c>
       <c r="E113" t="s">
-        <v>243</v>
+        <v>9</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -4446,7 +4578,7 @@
         <v>249</v>
       </c>
       <c r="B116">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="C116" t="s">
         <v>250</v>
@@ -4455,7 +4587,7 @@
         <v>8</v>
       </c>
       <c r="E116" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -4463,7 +4595,7 @@
         <v>251</v>
       </c>
       <c r="B117">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="C117" t="s">
         <v>252</v>
@@ -4480,7 +4612,7 @@
         <v>253</v>
       </c>
       <c r="B118">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="C118" t="s">
         <v>254</v>
@@ -4497,7 +4629,7 @@
         <v>255</v>
       </c>
       <c r="B119">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="C119" t="s">
         <v>256</v>
@@ -4514,7 +4646,7 @@
         <v>257</v>
       </c>
       <c r="B120">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="C120" t="s">
         <v>258</v>
@@ -4523,7 +4655,7 @@
         <v>8</v>
       </c>
       <c r="E120" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -4531,7 +4663,7 @@
         <v>259</v>
       </c>
       <c r="B121">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="C121" t="s">
         <v>260</v>
@@ -4540,7 +4672,7 @@
         <v>8</v>
       </c>
       <c r="E121" t="s">
-        <v>21</v>
+        <v>106</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -4548,7 +4680,7 @@
         <v>261</v>
       </c>
       <c r="B122">
-        <v>1.05</v>
+        <v>1.55</v>
       </c>
       <c r="C122" t="s">
         <v>262</v>
@@ -4557,35 +4689,35 @@
         <v>8</v>
       </c>
       <c r="E122" t="s">
-        <v>21</v>
+        <v>263</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B123">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="C123" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D123" t="s">
         <v>8</v>
       </c>
       <c r="E123" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B124">
         <v>1</v>
       </c>
       <c r="C124" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D124" t="s">
         <v>8</v>
@@ -4596,47 +4728,47 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B125">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="C125" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D125" t="s">
         <v>8</v>
       </c>
       <c r="E125" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B126">
-        <v>1.26</v>
+        <v>1.08</v>
       </c>
       <c r="C126" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D126" t="s">
         <v>8</v>
       </c>
       <c r="E126" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B127">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="C127" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D127" t="s">
         <v>8</v>
@@ -4647,13 +4779,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B128">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="C128" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D128" t="s">
         <v>8</v>
@@ -4664,47 +4796,47 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B129">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="C129" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D129" t="s">
         <v>8</v>
       </c>
       <c r="E129" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B130">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="C130" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D130" t="s">
         <v>8</v>
       </c>
       <c r="E130" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B131">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="C131" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D131" t="s">
         <v>8</v>
@@ -4715,47 +4847,47 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B132">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="C132" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D132" t="s">
         <v>8</v>
       </c>
       <c r="E132" t="s">
-        <v>9</v>
+        <v>106</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B133">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="C133" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D133" t="s">
         <v>8</v>
       </c>
       <c r="E133" t="s">
-        <v>9</v>
+        <v>287</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B134">
         <v>1</v>
       </c>
       <c r="C134" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D134" t="s">
         <v>8</v>
@@ -4766,13 +4898,13 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B135">
         <v>1</v>
       </c>
       <c r="C135" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D135" t="s">
         <v>8</v>
@@ -4783,13 +4915,13 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B136">
-        <v>1.52</v>
+        <v>1.26</v>
       </c>
       <c r="C136" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D136" t="s">
         <v>8</v>
@@ -4800,13 +4932,13 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B137">
         <v>1.08</v>
       </c>
       <c r="C137" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D137" t="s">
         <v>8</v>
@@ -4817,30 +4949,30 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B138">
-        <v>1.16</v>
+        <v>1</v>
       </c>
       <c r="C138" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D138" t="s">
         <v>8</v>
       </c>
       <c r="E138" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B139">
         <v>1</v>
       </c>
       <c r="C139" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D139" t="s">
         <v>8</v>
@@ -4851,13 +4983,13 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B140">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="C140" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D140" t="s">
         <v>8</v>
@@ -4868,13 +5000,13 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B141">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="C141" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D141" t="s">
         <v>8</v>
@@ -4885,13 +5017,13 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B142">
         <v>1</v>
       </c>
       <c r="C142" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D142" t="s">
         <v>8</v>
@@ -4902,30 +5034,30 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B143">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="C143" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D143" t="s">
         <v>8</v>
       </c>
       <c r="E143" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B144">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="C144" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D144" t="s">
         <v>8</v>
@@ -4936,13 +5068,13 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B145">
         <v>1</v>
       </c>
       <c r="C145" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="D145" t="s">
         <v>8</v>
@@ -4953,115 +5085,115 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B146">
-        <v>1</v>
+        <v>1.52</v>
       </c>
       <c r="C146" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="D146" t="s">
         <v>8</v>
       </c>
       <c r="E146" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B147">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="C147" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="D147" t="s">
         <v>8</v>
       </c>
       <c r="E147" t="s">
-        <v>9</v>
+        <v>106</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B148">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="C148" t="s">
-        <v>150</v>
+        <v>317</v>
       </c>
       <c r="D148" t="s">
         <v>8</v>
       </c>
       <c r="E148" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B149">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
       <c r="C149" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D149" t="s">
         <v>8</v>
       </c>
       <c r="E149" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B150">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="C150" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="D150" t="s">
         <v>8</v>
       </c>
       <c r="E150" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="B151">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="C151" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D151" t="s">
         <v>8</v>
       </c>
       <c r="E151" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="152" spans="1:5">
       <c r="A152" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B152">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="C152" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="D152" t="s">
         <v>8</v>
@@ -5072,47 +5204,47 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B153">
-        <v>1.55</v>
+        <v>1</v>
       </c>
       <c r="C153" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="D153" t="s">
         <v>8</v>
       </c>
       <c r="E153" t="s">
-        <v>324</v>
+        <v>9</v>
       </c>
     </row>
     <row r="154" spans="1:5">
       <c r="A154" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B154">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="C154" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="D154" t="s">
         <v>8</v>
       </c>
       <c r="E154" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="155" spans="1:5">
       <c r="A155" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B155">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="C155" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D155" t="s">
         <v>8</v>
@@ -5123,64 +5255,64 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B156">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="C156" t="s">
-        <v>330</v>
+        <v>313</v>
       </c>
       <c r="D156" t="s">
         <v>8</v>
       </c>
       <c r="E156" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="157" spans="1:5">
       <c r="A157" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B157">
-        <v>1.18</v>
+        <v>1</v>
       </c>
       <c r="C157" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D157" t="s">
         <v>8</v>
       </c>
       <c r="E157" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="158" spans="1:5">
       <c r="A158" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B158">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="C158" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D158" t="s">
         <v>8</v>
       </c>
       <c r="E158" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="159" spans="1:5">
       <c r="A159" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B159">
         <v>1</v>
       </c>
       <c r="C159" t="s">
-        <v>336</v>
+        <v>160</v>
       </c>
       <c r="D159" t="s">
         <v>8</v>
@@ -5191,234 +5323,234 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B160">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="C160" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D160" t="s">
         <v>8</v>
       </c>
       <c r="E160" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="161" spans="1:5">
       <c r="A161" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B161">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="C161" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D161" t="s">
         <v>8</v>
       </c>
       <c r="E161" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="162" spans="1:5">
       <c r="A162" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B162">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="C162" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D162" t="s">
         <v>8</v>
       </c>
       <c r="E162" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="163" spans="1:5">
       <c r="A163" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B163">
-        <v>1.14</v>
+        <v>0.9</v>
       </c>
       <c r="C163" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D163" t="s">
         <v>8</v>
       </c>
       <c r="E163" t="s">
-        <v>21</v>
+        <v>106</v>
       </c>
     </row>
     <row r="164" spans="1:5">
       <c r="A164" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B164">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="C164" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D164" t="s">
         <v>8</v>
       </c>
       <c r="E164" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B165">
-        <v>1</v>
+        <v>1.55</v>
       </c>
       <c r="C165" t="s">
-        <v>57</v>
+        <v>349</v>
       </c>
       <c r="D165" t="s">
         <v>8</v>
       </c>
       <c r="E165" t="s">
-        <v>9</v>
+        <v>350</v>
       </c>
     </row>
     <row r="166" spans="1:5">
       <c r="A166" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B166">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="C166" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="D166" t="s">
         <v>8</v>
       </c>
       <c r="E166" t="s">
-        <v>350</v>
+        <v>9</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B167">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="C167" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D167" t="s">
         <v>8</v>
       </c>
       <c r="E167" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="168" spans="1:5">
       <c r="A168" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B168">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="C168" t="s">
-        <v>148</v>
+        <v>356</v>
       </c>
       <c r="D168" t="s">
         <v>8</v>
       </c>
       <c r="E168" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="169" spans="1:5">
       <c r="A169" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B169">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="C169" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="D169" t="s">
         <v>8</v>
       </c>
       <c r="E169" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="170" spans="1:5">
       <c r="A170" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B170">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="C170" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D170" t="s">
         <v>8</v>
       </c>
       <c r="E170" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="171" spans="1:5">
       <c r="A171" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B171">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="C171" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="D171" t="s">
         <v>8</v>
       </c>
       <c r="E171" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="172" spans="1:5">
       <c r="A172" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B172">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="C172" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="D172" t="s">
         <v>8</v>
       </c>
       <c r="E172" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="173" spans="1:5">
       <c r="A173" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B173">
         <v>1</v>
       </c>
       <c r="C173" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="D173" t="s">
         <v>8</v>
@@ -5429,47 +5561,47 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B174">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="C174" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="D174" t="s">
         <v>8</v>
       </c>
       <c r="E174" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="175" spans="1:5">
       <c r="A175" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B175">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="C175" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="D175" t="s">
         <v>8</v>
       </c>
       <c r="E175" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="176" spans="1:5">
       <c r="A176" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B176">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="C176" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="D176" t="s">
         <v>8</v>
@@ -5480,47 +5612,47 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="B177">
-        <v>1.19</v>
+        <v>1</v>
       </c>
       <c r="C177" t="s">
-        <v>371</v>
+        <v>57</v>
       </c>
       <c r="D177" t="s">
         <v>8</v>
       </c>
       <c r="E177" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="178" spans="1:5">
       <c r="A178" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B178">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="C178" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D178" t="s">
         <v>8</v>
       </c>
       <c r="E178" t="s">
-        <v>9</v>
+        <v>376</v>
       </c>
     </row>
     <row r="179" spans="1:5">
       <c r="A179" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B179">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="C179" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="D179" t="s">
         <v>8</v>
@@ -5531,47 +5663,47 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B180">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="C180" t="s">
-        <v>377</v>
+        <v>158</v>
       </c>
       <c r="D180" t="s">
         <v>8</v>
       </c>
       <c r="E180" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="181" spans="1:5">
       <c r="A181" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B181">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="C181" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D181" t="s">
         <v>8</v>
       </c>
       <c r="E181" t="s">
-        <v>380</v>
+        <v>9</v>
       </c>
     </row>
     <row r="182" spans="1:5">
       <c r="A182" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B182">
         <v>1</v>
       </c>
       <c r="C182" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D182" t="s">
         <v>8</v>
@@ -5582,47 +5714,47 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B183">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="C183" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D183" t="s">
         <v>8</v>
       </c>
       <c r="E183" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="184" spans="1:5">
       <c r="A184" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B184">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="C184" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D184" t="s">
         <v>8</v>
       </c>
       <c r="E184" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="185" spans="1:5">
       <c r="A185" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B185">
         <v>1</v>
       </c>
       <c r="C185" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D185" t="s">
         <v>8</v>
@@ -5633,36 +5765,36 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B186">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="C186" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D186" t="s">
         <v>8</v>
       </c>
       <c r="E186" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="187" spans="1:5">
       <c r="A187" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B187">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="C187" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D187" t="s">
         <v>8</v>
       </c>
       <c r="E187" t="s">
-        <v>393</v>
+        <v>9</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -5670,27 +5802,27 @@
         <v>394</v>
       </c>
       <c r="B188">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="C188" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="D188" t="s">
         <v>8</v>
       </c>
       <c r="E188" t="s">
-        <v>393</v>
+        <v>9</v>
       </c>
     </row>
     <row r="189" spans="1:5">
       <c r="A189" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B189">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="C189" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D189" t="s">
         <v>8</v>
@@ -5701,13 +5833,13 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B190">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="C190" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D190" t="s">
         <v>8</v>
@@ -5718,13 +5850,13 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B191">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="C191" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D191" t="s">
         <v>8</v>
@@ -5735,64 +5867,64 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B192">
         <v>1.01</v>
       </c>
       <c r="C192" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D192" t="s">
         <v>8</v>
       </c>
       <c r="E192" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="193" spans="1:5">
       <c r="A193" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B193">
-        <v>1.09</v>
+        <v>2.3</v>
       </c>
       <c r="C193" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D193" t="s">
         <v>8</v>
       </c>
       <c r="E193" t="s">
-        <v>21</v>
+        <v>406</v>
       </c>
     </row>
     <row r="194" spans="1:5">
       <c r="A194" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B194">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="C194" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D194" t="s">
         <v>8</v>
       </c>
       <c r="E194" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="195" spans="1:5">
       <c r="A195" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B195">
         <v>1</v>
       </c>
       <c r="C195" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D195" t="s">
         <v>8</v>
@@ -5803,13 +5935,13 @@
     </row>
     <row r="196" spans="1:5">
       <c r="A196" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B196">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="C196" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D196" t="s">
         <v>8</v>
@@ -5820,13 +5952,13 @@
     </row>
     <row r="197" spans="1:5">
       <c r="A197" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B197">
         <v>1</v>
       </c>
       <c r="C197" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D197" t="s">
         <v>8</v>
@@ -5837,13 +5969,13 @@
     </row>
     <row r="198" spans="1:5">
       <c r="A198" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B198">
         <v>1</v>
       </c>
       <c r="C198" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D198" t="s">
         <v>8</v>
@@ -5854,64 +5986,64 @@
     </row>
     <row r="199" spans="1:5">
       <c r="A199" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B199">
-        <v>0.85</v>
+        <v>0.96</v>
       </c>
       <c r="C199" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D199" t="s">
         <v>8</v>
       </c>
       <c r="E199" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="200" spans="1:5">
       <c r="A200" t="s">
+        <v>420</v>
+      </c>
+      <c r="B200">
+        <v>1.06</v>
+      </c>
+      <c r="C200" t="s">
         <v>418</v>
       </c>
-      <c r="B200">
-        <v>1</v>
-      </c>
-      <c r="C200" t="s">
+      <c r="D200" t="s">
+        <v>8</v>
+      </c>
+      <c r="E200" t="s">
         <v>419</v>
-      </c>
-      <c r="D200" t="s">
-        <v>8</v>
-      </c>
-      <c r="E200" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="201" spans="1:5">
       <c r="A201" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B201">
-        <v>2.15</v>
+        <v>1.18</v>
       </c>
       <c r="C201" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D201" t="s">
         <v>8</v>
       </c>
       <c r="E201" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="202" spans="1:5">
       <c r="A202" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B202">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="C202" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D202" t="s">
         <v>8</v>
@@ -5922,30 +6054,30 @@
     </row>
     <row r="203" spans="1:5">
       <c r="A203" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B203">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="C203" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D203" t="s">
         <v>8</v>
       </c>
       <c r="E203" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="204" spans="1:5">
       <c r="A204" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B204">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="C204" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D204" t="s">
         <v>8</v>
@@ -5956,166 +6088,166 @@
     </row>
     <row r="205" spans="1:5">
       <c r="A205" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B205">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="C205" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D205" t="s">
         <v>8</v>
       </c>
       <c r="E205" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="206" spans="1:5">
       <c r="A206" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B206">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="C206" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D206" t="s">
         <v>8</v>
       </c>
       <c r="E206" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="207" spans="1:5">
       <c r="A207" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B207">
-        <v>2.05</v>
+        <v>1</v>
       </c>
       <c r="C207" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D207" t="s">
         <v>8</v>
       </c>
       <c r="E207" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="208" spans="1:5">
       <c r="A208" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B208">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="C208" t="s">
-        <v>152</v>
+        <v>436</v>
       </c>
       <c r="D208" t="s">
         <v>8</v>
       </c>
       <c r="E208" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="209" spans="1:5">
       <c r="A209" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B209">
-        <v>1.19</v>
+        <v>1</v>
       </c>
       <c r="C209" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D209" t="s">
         <v>8</v>
       </c>
       <c r="E209" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="210" spans="1:5">
       <c r="A210" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B210">
-        <v>1.36</v>
+        <v>1</v>
       </c>
       <c r="C210" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D210" t="s">
         <v>8</v>
       </c>
       <c r="E210" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="211" spans="1:5">
       <c r="A211" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B211">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="C211" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D211" t="s">
         <v>8</v>
       </c>
       <c r="E211" t="s">
-        <v>9</v>
+        <v>443</v>
       </c>
     </row>
     <row r="212" spans="1:5">
       <c r="A212" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="B212">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="C212" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D212" t="s">
         <v>8</v>
       </c>
       <c r="E212" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="213" spans="1:5">
       <c r="A213" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="B213">
-        <v>1.2</v>
+        <v>2.15</v>
       </c>
       <c r="C213" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="D213" t="s">
         <v>8</v>
       </c>
       <c r="E213" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="214" spans="1:5">
       <c r="A214" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="B214">
         <v>1</v>
       </c>
       <c r="C214" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="D214" t="s">
         <v>8</v>
@@ -6126,13 +6258,13 @@
     </row>
     <row r="215" spans="1:5">
       <c r="A215" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B215">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="C215" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="D215" t="s">
         <v>8</v>
@@ -6143,30 +6275,30 @@
     </row>
     <row r="216" spans="1:5">
       <c r="A216" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="B216">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="C216" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="D216" t="s">
         <v>8</v>
       </c>
       <c r="E216" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="217" spans="1:5">
       <c r="A217" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="B217">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="C217" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D217" t="s">
         <v>8</v>
@@ -6177,121 +6309,121 @@
     </row>
     <row r="218" spans="1:5">
       <c r="A218" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B218">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="C218" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="D218" t="s">
         <v>8</v>
       </c>
       <c r="E218" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="219" spans="1:5">
       <c r="A219" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="B219">
-        <v>1</v>
+        <v>2.05</v>
       </c>
       <c r="C219" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="D219" t="s">
         <v>8</v>
       </c>
       <c r="E219" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="220" spans="1:5">
       <c r="A220" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="B220">
-        <v>1.19</v>
+        <v>1.95</v>
       </c>
       <c r="C220" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="D220" t="s">
-        <v>8</v>
+        <v>133</v>
       </c>
       <c r="E220" t="s">
-        <v>21</v>
+        <v>106</v>
       </c>
     </row>
     <row r="221" spans="1:5">
       <c r="A221" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="B221">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="C221" t="s">
-        <v>460</v>
+        <v>162</v>
       </c>
       <c r="D221" t="s">
         <v>8</v>
       </c>
       <c r="E221" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="222" spans="1:5">
       <c r="A222" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B222">
-        <v>2.03</v>
+        <v>1.19</v>
       </c>
       <c r="C222" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="D222" t="s">
         <v>8</v>
       </c>
       <c r="E222" t="s">
-        <v>463</v>
+        <v>21</v>
       </c>
     </row>
     <row r="223" spans="1:5">
       <c r="A223" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B223">
-        <v>1.06</v>
+        <v>1.36</v>
       </c>
       <c r="C223" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D223" t="s">
         <v>8</v>
       </c>
       <c r="E223" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="224" spans="1:5">
       <c r="A224" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B224">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="C224" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D224" t="s">
         <v>8</v>
       </c>
       <c r="E224" t="s">
-        <v>468</v>
+        <v>106</v>
       </c>
     </row>
     <row r="225" spans="1:5">
@@ -6299,7 +6431,7 @@
         <v>469</v>
       </c>
       <c r="B225">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="C225" t="s">
         <v>470</v>
@@ -6308,7 +6440,7 @@
         <v>8</v>
       </c>
       <c r="E225" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="226" spans="1:5">
@@ -6316,7 +6448,7 @@
         <v>471</v>
       </c>
       <c r="B226">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="C226" t="s">
         <v>472</v>
@@ -6325,7 +6457,7 @@
         <v>8</v>
       </c>
       <c r="E226" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="227" spans="1:5">
@@ -6333,7 +6465,7 @@
         <v>473</v>
       </c>
       <c r="B227">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="C227" t="s">
         <v>474</v>
@@ -6342,7 +6474,7 @@
         <v>8</v>
       </c>
       <c r="E227" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="228" spans="1:5">
@@ -6350,7 +6482,7 @@
         <v>475</v>
       </c>
       <c r="B228">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="C228" t="s">
         <v>476</v>
@@ -6359,7 +6491,7 @@
         <v>8</v>
       </c>
       <c r="E228" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="229" spans="1:5">
@@ -6367,7 +6499,7 @@
         <v>477</v>
       </c>
       <c r="B229">
-        <v>1.13</v>
+        <v>0.9</v>
       </c>
       <c r="C229" t="s">
         <v>478</v>
@@ -6376,7 +6508,7 @@
         <v>8</v>
       </c>
       <c r="E229" t="s">
-        <v>21</v>
+        <v>106</v>
       </c>
     </row>
     <row r="230" spans="1:5">
@@ -6384,7 +6516,7 @@
         <v>479</v>
       </c>
       <c r="B230">
-        <v>1.19</v>
+        <v>1.02</v>
       </c>
       <c r="C230" t="s">
         <v>480</v>
@@ -6393,7 +6525,7 @@
         <v>8</v>
       </c>
       <c r="E230" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="231" spans="1:5">
@@ -6401,7 +6533,7 @@
         <v>481</v>
       </c>
       <c r="B231">
-        <v>1.17</v>
+        <v>0.9</v>
       </c>
       <c r="C231" t="s">
         <v>482</v>
@@ -6410,7 +6542,7 @@
         <v>8</v>
       </c>
       <c r="E231" t="s">
-        <v>21</v>
+        <v>106</v>
       </c>
     </row>
     <row r="232" spans="1:5">
@@ -6418,7 +6550,7 @@
         <v>483</v>
       </c>
       <c r="B232">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="C232" t="s">
         <v>484</v>
@@ -6427,7 +6559,7 @@
         <v>8</v>
       </c>
       <c r="E232" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="233" spans="1:5">
@@ -6435,7 +6567,7 @@
         <v>485</v>
       </c>
       <c r="B233">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="C233" t="s">
         <v>486</v>
@@ -6444,7 +6576,7 @@
         <v>8</v>
       </c>
       <c r="E233" t="s">
-        <v>417</v>
+        <v>9</v>
       </c>
     </row>
     <row r="234" spans="1:5">
@@ -6461,7 +6593,7 @@
         <v>8</v>
       </c>
       <c r="E234" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="235" spans="1:5">
@@ -6486,7 +6618,7 @@
         <v>491</v>
       </c>
       <c r="B236">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="C236" t="s">
         <v>492</v>
@@ -6503,7 +6635,7 @@
         <v>493</v>
       </c>
       <c r="B237">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="C237" t="s">
         <v>494</v>
@@ -6512,7 +6644,7 @@
         <v>8</v>
       </c>
       <c r="E237" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="238" spans="1:5">
@@ -6520,7 +6652,7 @@
         <v>495</v>
       </c>
       <c r="B238">
-        <v>0.99</v>
+        <v>2.03</v>
       </c>
       <c r="C238" t="s">
         <v>496</v>
@@ -6529,52 +6661,52 @@
         <v>8</v>
       </c>
       <c r="E238" t="s">
-        <v>21</v>
+        <v>497</v>
       </c>
     </row>
     <row r="239" spans="1:5">
       <c r="A239" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B239">
-        <v>0.77</v>
+        <v>1.06</v>
       </c>
       <c r="C239" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D239" t="s">
         <v>8</v>
       </c>
       <c r="E239" t="s">
-        <v>324</v>
+        <v>21</v>
       </c>
     </row>
     <row r="240" spans="1:5">
       <c r="A240" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B240">
-        <v>1.06</v>
+        <v>2</v>
       </c>
       <c r="C240" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D240" t="s">
         <v>8</v>
       </c>
       <c r="E240" t="s">
-        <v>9</v>
+        <v>502</v>
       </c>
     </row>
     <row r="241" spans="1:5">
       <c r="A241" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B241">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="C241" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="D241" t="s">
         <v>8</v>
@@ -6585,64 +6717,64 @@
     </row>
     <row r="242" spans="1:5">
       <c r="A242" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B242">
-        <v>1.07</v>
+        <v>0.9</v>
       </c>
       <c r="C242" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="D242" t="s">
         <v>8</v>
       </c>
       <c r="E242" t="s">
-        <v>21</v>
+        <v>106</v>
       </c>
     </row>
     <row r="243" spans="1:5">
       <c r="A243" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B243">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="C243" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="D243" t="s">
         <v>8</v>
       </c>
       <c r="E243" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="244" spans="1:5">
       <c r="A244" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B244">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="C244" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="D244" t="s">
         <v>8</v>
       </c>
       <c r="E244" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="245" spans="1:5">
       <c r="A245" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B245">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="C245" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="D245" t="s">
         <v>8</v>
@@ -6653,30 +6785,30 @@
     </row>
     <row r="246" spans="1:5">
       <c r="A246" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B246">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="C246" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="D246" t="s">
         <v>8</v>
       </c>
       <c r="E246" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="247" spans="1:5">
       <c r="A247" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B247">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="C247" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D247" t="s">
         <v>8</v>
@@ -6687,30 +6819,30 @@
     </row>
     <row r="248" spans="1:5">
       <c r="A248" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B248">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="C248" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="D248" t="s">
         <v>8</v>
       </c>
       <c r="E248" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="249" spans="1:5">
       <c r="A249" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B249">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="C249" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D249" t="s">
         <v>8</v>
@@ -6721,47 +6853,47 @@
     </row>
     <row r="250" spans="1:5">
       <c r="A250" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B250">
-        <v>1.04</v>
+        <v>0.88</v>
       </c>
       <c r="C250" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="D250" t="s">
         <v>8</v>
       </c>
       <c r="E250" t="s">
-        <v>9</v>
+        <v>443</v>
       </c>
     </row>
     <row r="251" spans="1:5">
       <c r="A251" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B251">
-        <v>1.55</v>
+        <v>1.03</v>
       </c>
       <c r="C251" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="D251" t="s">
         <v>8</v>
       </c>
       <c r="E251" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="252" spans="1:5">
       <c r="A252" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B252">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="C252" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="D252" t="s">
         <v>8</v>
@@ -6772,13 +6904,13 @@
     </row>
     <row r="253" spans="1:5">
       <c r="A253" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B253">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="C253" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="D253" t="s">
         <v>8</v>
@@ -6789,13 +6921,13 @@
     </row>
     <row r="254" spans="1:5">
       <c r="A254" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B254">
         <v>1</v>
       </c>
       <c r="C254" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D254" t="s">
         <v>8</v>
@@ -6806,13 +6938,13 @@
     </row>
     <row r="255" spans="1:5">
       <c r="A255" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B255">
-        <v>1.09</v>
+        <v>0.99</v>
       </c>
       <c r="C255" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D255" t="s">
         <v>8</v>
@@ -6823,47 +6955,47 @@
     </row>
     <row r="256" spans="1:5">
       <c r="A256" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B256">
-        <v>1.08</v>
+        <v>0.77</v>
       </c>
       <c r="C256" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D256" t="s">
         <v>8</v>
       </c>
       <c r="E256" t="s">
-        <v>21</v>
+        <v>350</v>
       </c>
     </row>
     <row r="257" spans="1:5">
       <c r="A257" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B257">
-        <v>1.31</v>
+        <v>1.06</v>
       </c>
       <c r="C257" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D257" t="s">
         <v>8</v>
       </c>
       <c r="E257" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="258" spans="1:5">
       <c r="A258" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B258">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="C258" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D258" t="s">
         <v>8</v>
@@ -6874,64 +7006,64 @@
     </row>
     <row r="259" spans="1:5">
       <c r="A259" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B259">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="C259" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D259" t="s">
         <v>8</v>
       </c>
       <c r="E259" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="260" spans="1:5">
       <c r="A260" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B260">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="C260" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="D260" t="s">
         <v>8</v>
       </c>
       <c r="E260" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="261" spans="1:5">
       <c r="A261" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B261">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="C261" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="D261" t="s">
         <v>8</v>
       </c>
       <c r="E261" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="262" spans="1:5">
       <c r="A262" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B262">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="C262" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="D262" t="s">
         <v>8</v>
@@ -6942,13 +7074,13 @@
     </row>
     <row r="263" spans="1:5">
       <c r="A263" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B263">
         <v>1</v>
       </c>
       <c r="C263" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="D263" t="s">
         <v>8</v>
@@ -6959,69 +7091,426 @@
     </row>
     <row r="264" spans="1:5">
       <c r="A264" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B264">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="C264" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="D264" t="s">
         <v>8</v>
       </c>
       <c r="E264" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="265" spans="1:5">
       <c r="A265" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B265">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="C265" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="D265" t="s">
         <v>8</v>
       </c>
       <c r="E265" t="s">
-        <v>551</v>
+        <v>9</v>
       </c>
     </row>
     <row r="266" spans="1:5">
       <c r="A266" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B266">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="C266" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D266" t="s">
         <v>8</v>
       </c>
       <c r="E266" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="267" spans="1:5">
       <c r="A267" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B267">
+        <v>1.04</v>
+      </c>
+      <c r="C267" t="s">
+        <v>556</v>
+      </c>
+      <c r="D267" t="s">
+        <v>8</v>
+      </c>
+      <c r="E267" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5">
+      <c r="A268" t="s">
+        <v>557</v>
+      </c>
+      <c r="B268">
+        <v>1.55</v>
+      </c>
+      <c r="C268" t="s">
+        <v>558</v>
+      </c>
+      <c r="D268" t="s">
+        <v>8</v>
+      </c>
+      <c r="E268" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5">
+      <c r="A269" t="s">
+        <v>559</v>
+      </c>
+      <c r="B269">
+        <v>0.9</v>
+      </c>
+      <c r="C269" t="s">
+        <v>560</v>
+      </c>
+      <c r="D269" t="s">
+        <v>8</v>
+      </c>
+      <c r="E269" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5">
+      <c r="A270" t="s">
+        <v>561</v>
+      </c>
+      <c r="B270">
+        <v>1.05</v>
+      </c>
+      <c r="C270" t="s">
+        <v>562</v>
+      </c>
+      <c r="D270" t="s">
+        <v>8</v>
+      </c>
+      <c r="E270" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5">
+      <c r="A271" t="s">
+        <v>563</v>
+      </c>
+      <c r="B271">
+        <v>1.08</v>
+      </c>
+      <c r="C271" t="s">
+        <v>564</v>
+      </c>
+      <c r="D271" t="s">
+        <v>8</v>
+      </c>
+      <c r="E271" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5">
+      <c r="A272" t="s">
+        <v>565</v>
+      </c>
+      <c r="B272">
         <v>1</v>
       </c>
-      <c r="C267" t="s">
-        <v>555</v>
-      </c>
-      <c r="D267" t="s">
-        <v>8</v>
-      </c>
-      <c r="E267" t="s">
+      <c r="C272" t="s">
+        <v>566</v>
+      </c>
+      <c r="D272" t="s">
+        <v>8</v>
+      </c>
+      <c r="E272" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5">
+      <c r="A273" t="s">
+        <v>567</v>
+      </c>
+      <c r="B273">
+        <v>0.84</v>
+      </c>
+      <c r="C273" t="s">
+        <v>568</v>
+      </c>
+      <c r="D273" t="s">
+        <v>8</v>
+      </c>
+      <c r="E273" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5">
+      <c r="A274" t="s">
+        <v>569</v>
+      </c>
+      <c r="B274">
+        <v>1.09</v>
+      </c>
+      <c r="C274" t="s">
+        <v>570</v>
+      </c>
+      <c r="D274" t="s">
+        <v>8</v>
+      </c>
+      <c r="E274" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5">
+      <c r="A275" t="s">
+        <v>571</v>
+      </c>
+      <c r="B275">
+        <v>1.08</v>
+      </c>
+      <c r="C275" t="s">
+        <v>572</v>
+      </c>
+      <c r="D275" t="s">
+        <v>8</v>
+      </c>
+      <c r="E275" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5">
+      <c r="A276" t="s">
+        <v>573</v>
+      </c>
+      <c r="B276">
+        <v>1.31</v>
+      </c>
+      <c r="C276" t="s">
+        <v>574</v>
+      </c>
+      <c r="D276" t="s">
+        <v>8</v>
+      </c>
+      <c r="E276" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5">
+      <c r="A277" t="s">
+        <v>575</v>
+      </c>
+      <c r="B277">
+        <v>1.07</v>
+      </c>
+      <c r="C277" t="s">
+        <v>576</v>
+      </c>
+      <c r="D277" t="s">
+        <v>8</v>
+      </c>
+      <c r="E277" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5">
+      <c r="A278" t="s">
+        <v>577</v>
+      </c>
+      <c r="B278">
+        <v>1</v>
+      </c>
+      <c r="C278" t="s">
+        <v>578</v>
+      </c>
+      <c r="D278" t="s">
+        <v>8</v>
+      </c>
+      <c r="E278" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5">
+      <c r="A279" t="s">
+        <v>579</v>
+      </c>
+      <c r="B279">
+        <v>1</v>
+      </c>
+      <c r="C279" t="s">
+        <v>580</v>
+      </c>
+      <c r="D279" t="s">
+        <v>8</v>
+      </c>
+      <c r="E279" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5">
+      <c r="A280" t="s">
+        <v>581</v>
+      </c>
+      <c r="B280">
+        <v>1.07</v>
+      </c>
+      <c r="C280" t="s">
+        <v>582</v>
+      </c>
+      <c r="D280" t="s">
+        <v>8</v>
+      </c>
+      <c r="E280" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5">
+      <c r="A281" t="s">
+        <v>583</v>
+      </c>
+      <c r="B281">
+        <v>0.9</v>
+      </c>
+      <c r="C281" t="s">
+        <v>584</v>
+      </c>
+      <c r="D281" t="s">
+        <v>8</v>
+      </c>
+      <c r="E281" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5">
+      <c r="A282" t="s">
+        <v>585</v>
+      </c>
+      <c r="B282">
+        <v>1.13</v>
+      </c>
+      <c r="C282" t="s">
+        <v>586</v>
+      </c>
+      <c r="D282" t="s">
+        <v>8</v>
+      </c>
+      <c r="E282" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5">
+      <c r="A283" t="s">
+        <v>587</v>
+      </c>
+      <c r="B283">
+        <v>1</v>
+      </c>
+      <c r="C283" t="s">
+        <v>588</v>
+      </c>
+      <c r="D283" t="s">
+        <v>8</v>
+      </c>
+      <c r="E283" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5">
+      <c r="A284" t="s">
+        <v>589</v>
+      </c>
+      <c r="B284">
+        <v>1.02</v>
+      </c>
+      <c r="C284" t="s">
+        <v>590</v>
+      </c>
+      <c r="D284" t="s">
+        <v>8</v>
+      </c>
+      <c r="E284" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5">
+      <c r="A285" t="s">
+        <v>591</v>
+      </c>
+      <c r="B285">
+        <v>1.1</v>
+      </c>
+      <c r="C285" t="s">
+        <v>592</v>
+      </c>
+      <c r="D285" t="s">
+        <v>8</v>
+      </c>
+      <c r="E285" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5">
+      <c r="A286" t="s">
+        <v>593</v>
+      </c>
+      <c r="B286">
+        <v>2.3</v>
+      </c>
+      <c r="C286" t="s">
+        <v>594</v>
+      </c>
+      <c r="D286" t="s">
+        <v>8</v>
+      </c>
+      <c r="E286" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5">
+      <c r="A287" t="s">
+        <v>596</v>
+      </c>
+      <c r="B287">
+        <v>1</v>
+      </c>
+      <c r="C287" t="s">
+        <v>597</v>
+      </c>
+      <c r="D287" t="s">
+        <v>8</v>
+      </c>
+      <c r="E287" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5">
+      <c r="A288" t="s">
+        <v>598</v>
+      </c>
+      <c r="B288">
+        <v>1</v>
+      </c>
+      <c r="C288" t="s">
+        <v>599</v>
+      </c>
+      <c r="D288" t="s">
+        <v>8</v>
+      </c>
+      <c r="E288" t="s">
         <v>9</v>
       </c>
     </row>
@@ -7042,7 +7531,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>691</v>
+        <v>735</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -7064,19 +7553,19 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>692</v>
+        <v>736</v>
       </c>
       <c r="B3">
         <v>2.72</v>
       </c>
       <c r="C3" t="s">
-        <v>693</v>
+        <v>737</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>694</v>
+        <v>738</v>
       </c>
     </row>
   </sheetData>
@@ -7096,7 +7585,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>695</v>
+        <v>739</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -7118,19 +7607,19 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>696</v>
+        <v>740</v>
       </c>
       <c r="B3">
         <v>2.68</v>
       </c>
       <c r="C3" t="s">
-        <v>697</v>
+        <v>741</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>698</v>
+        <v>742</v>
       </c>
     </row>
   </sheetData>
@@ -7150,7 +7639,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>699</v>
+        <v>743</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -7172,36 +7661,36 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>700</v>
+        <v>744</v>
       </c>
       <c r="B3">
         <v>3.21</v>
       </c>
       <c r="C3" t="s">
-        <v>701</v>
+        <v>745</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>604</v>
+        <v>648</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>702</v>
+        <v>746</v>
       </c>
       <c r="B4">
         <v>2.73</v>
       </c>
       <c r="C4" t="s">
-        <v>703</v>
+        <v>747</v>
       </c>
       <c r="D4" t="s">
         <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>704</v>
+        <v>748</v>
       </c>
     </row>
   </sheetData>
@@ -7211,7 +7700,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B328"/>
+  <dimension ref="A1:B349"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.7109375" customWidth="1"/>
@@ -7219,12 +7708,12 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>705</v>
+        <v>749</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>706</v>
+        <v>750</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
@@ -7232,7 +7721,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>707</v>
+        <v>751</v>
       </c>
       <c r="B3" t="s">
         <v>6</v>
@@ -7275,7 +7764,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="B11" t="s">
-        <v>557</v>
+        <v>601</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -7285,7 +7774,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="B13" t="s">
-        <v>560</v>
+        <v>604</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -7300,7 +7789,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="B16" t="s">
-        <v>563</v>
+        <v>607</v>
       </c>
     </row>
     <row r="17" spans="2:2">
@@ -7320,7 +7809,7 @@
     </row>
     <row r="20" spans="2:2">
       <c r="B20" t="s">
-        <v>646</v>
+        <v>690</v>
       </c>
     </row>
     <row r="21" spans="2:2">
@@ -7335,7 +7824,7 @@
     </row>
     <row r="23" spans="2:2">
       <c r="B23" t="s">
-        <v>566</v>
+        <v>610</v>
       </c>
     </row>
     <row r="24" spans="2:2">
@@ -7395,7 +7884,7 @@
     </row>
     <row r="35" spans="2:2">
       <c r="B35" t="s">
-        <v>658</v>
+        <v>702</v>
       </c>
     </row>
     <row r="36" spans="2:2">
@@ -7420,7 +7909,7 @@
     </row>
     <row r="40" spans="2:2">
       <c r="B40" t="s">
-        <v>662</v>
+        <v>706</v>
       </c>
     </row>
     <row r="41" spans="2:2">
@@ -7435,7 +7924,7 @@
     </row>
     <row r="43" spans="2:2">
       <c r="B43" t="s">
-        <v>649</v>
+        <v>693</v>
       </c>
     </row>
     <row r="44" spans="2:2">
@@ -7445,7 +7934,7 @@
     </row>
     <row r="45" spans="2:2">
       <c r="B45" t="s">
-        <v>666</v>
+        <v>710</v>
       </c>
     </row>
     <row r="46" spans="2:2">
@@ -7480,7 +7969,7 @@
     </row>
     <row r="52" spans="2:2">
       <c r="B52" t="s">
-        <v>652</v>
+        <v>696</v>
       </c>
     </row>
     <row r="53" spans="2:2">
@@ -7495,7 +7984,7 @@
     </row>
     <row r="55" spans="2:2">
       <c r="B55" t="s">
-        <v>670</v>
+        <v>714</v>
       </c>
     </row>
     <row r="56" spans="2:2">
@@ -7515,237 +8004,237 @@
     </row>
     <row r="59" spans="2:2">
       <c r="B59" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="60" spans="2:2">
       <c r="B60" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="61" spans="2:2">
       <c r="B61" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="62" spans="2:2">
       <c r="B62" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="63" spans="2:2">
       <c r="B63" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="64" spans="2:2">
       <c r="B64" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="65" spans="2:2">
       <c r="B65" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="66" spans="2:2">
       <c r="B66" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="67" spans="2:2">
       <c r="B67" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="68" spans="2:2">
       <c r="B68" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="69" spans="2:2">
       <c r="B69" t="s">
-        <v>569</v>
+        <v>127</v>
       </c>
     </row>
     <row r="70" spans="2:2">
       <c r="B70" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="71" spans="2:2">
       <c r="B71" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="72" spans="2:2">
       <c r="B72" t="s">
-        <v>130</v>
+        <v>613</v>
       </c>
     </row>
     <row r="73" spans="2:2">
       <c r="B73" t="s">
-        <v>572</v>
+        <v>134</v>
       </c>
     </row>
     <row r="74" spans="2:2">
       <c r="B74" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="75" spans="2:2">
       <c r="B75" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="76" spans="2:2">
       <c r="B76" t="s">
-        <v>136</v>
+        <v>616</v>
       </c>
     </row>
     <row r="77" spans="2:2">
       <c r="B77" t="s">
-        <v>575</v>
+        <v>140</v>
       </c>
     </row>
     <row r="78" spans="2:2">
       <c r="B78" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="79" spans="2:2">
       <c r="B79" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="80" spans="2:2">
       <c r="B80" t="s">
-        <v>143</v>
+        <v>619</v>
       </c>
     </row>
     <row r="81" spans="2:2">
       <c r="B81" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="82" spans="2:2">
       <c r="B82" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="83" spans="2:2">
       <c r="B83" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="84" spans="2:2">
       <c r="B84" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="85" spans="2:2">
       <c r="B85" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="86" spans="2:2">
       <c r="B86" t="s">
-        <v>578</v>
+        <v>157</v>
       </c>
     </row>
     <row r="87" spans="2:2">
       <c r="B87" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="88" spans="2:2">
       <c r="B88" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="89" spans="2:2">
       <c r="B89" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="90" spans="2:2">
       <c r="B90" t="s">
-        <v>161</v>
+        <v>622</v>
       </c>
     </row>
     <row r="91" spans="2:2">
       <c r="B91" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="92" spans="2:2">
       <c r="B92" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="93" spans="2:2">
       <c r="B93" t="s">
-        <v>581</v>
+        <v>169</v>
       </c>
     </row>
     <row r="94" spans="2:2">
       <c r="B94" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="95" spans="2:2">
       <c r="B95" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="96" spans="2:2">
       <c r="B96" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="97" spans="2:2">
       <c r="B97" t="s">
-        <v>673</v>
+        <v>625</v>
       </c>
     </row>
     <row r="98" spans="2:2">
       <c r="B98" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="99" spans="2:2">
       <c r="B99" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="100" spans="2:2">
       <c r="B100" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="101" spans="2:2">
       <c r="B101" t="s">
-        <v>179</v>
+        <v>717</v>
       </c>
     </row>
     <row r="102" spans="2:2">
       <c r="B102" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="103" spans="2:2">
       <c r="B103" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="104" spans="2:2">
       <c r="B104" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="105" spans="2:2">
       <c r="B105" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="106" spans="2:2">
@@ -7755,802 +8244,802 @@
     </row>
     <row r="107" spans="2:2">
       <c r="B107" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="108" spans="2:2">
       <c r="B108" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="109" spans="2:2">
       <c r="B109" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="110" spans="2:2">
       <c r="B110" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="111" spans="2:2">
       <c r="B111" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="112" spans="2:2">
       <c r="B112" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="113" spans="2:2">
       <c r="B113" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="114" spans="2:2">
       <c r="B114" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="115" spans="2:2">
       <c r="B115" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="116" spans="2:2">
       <c r="B116" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="117" spans="2:2">
       <c r="B117" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="118" spans="2:2">
       <c r="B118" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="119" spans="2:2">
       <c r="B119" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="120" spans="2:2">
       <c r="B120" t="s">
-        <v>685</v>
+        <v>222</v>
       </c>
     </row>
     <row r="121" spans="2:2">
       <c r="B121" t="s">
-        <v>675</v>
+        <v>224</v>
       </c>
     </row>
     <row r="122" spans="2:2">
       <c r="B122" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
     </row>
     <row r="123" spans="2:2">
       <c r="B123" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
     </row>
     <row r="124" spans="2:2">
       <c r="B124" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
     </row>
     <row r="125" spans="2:2">
       <c r="B125" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
     </row>
     <row r="126" spans="2:2">
       <c r="B126" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
     </row>
     <row r="127" spans="2:2">
       <c r="B127" t="s">
-        <v>231</v>
+        <v>729</v>
       </c>
     </row>
     <row r="128" spans="2:2">
       <c r="B128" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="129" spans="2:2">
       <c r="B129" t="s">
-        <v>235</v>
+        <v>719</v>
       </c>
     </row>
     <row r="130" spans="2:2">
       <c r="B130" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="131" spans="2:2">
       <c r="B131" t="s">
-        <v>584</v>
+        <v>240</v>
       </c>
     </row>
     <row r="132" spans="2:2">
       <c r="B132" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="133" spans="2:2">
       <c r="B133" t="s">
-        <v>586</v>
+        <v>244</v>
       </c>
     </row>
     <row r="134" spans="2:2">
       <c r="B134" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
     </row>
     <row r="135" spans="2:2">
       <c r="B135" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
     </row>
     <row r="136" spans="2:2">
       <c r="B136" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
     </row>
     <row r="137" spans="2:2">
       <c r="B137" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
     </row>
     <row r="138" spans="2:2">
       <c r="B138" t="s">
-        <v>589</v>
+        <v>255</v>
       </c>
     </row>
     <row r="139" spans="2:2">
       <c r="B139" t="s">
-        <v>251</v>
+        <v>628</v>
       </c>
     </row>
     <row r="140" spans="2:2">
       <c r="B140" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
     </row>
     <row r="141" spans="2:2">
       <c r="B141" t="s">
-        <v>677</v>
+        <v>259</v>
       </c>
     </row>
     <row r="142" spans="2:2">
       <c r="B142" t="s">
-        <v>255</v>
+        <v>630</v>
       </c>
     </row>
     <row r="143" spans="2:2">
       <c r="B143" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
     </row>
     <row r="144" spans="2:2">
       <c r="B144" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
     </row>
     <row r="145" spans="2:2">
       <c r="B145" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="146" spans="2:2">
       <c r="B146" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
     </row>
     <row r="147" spans="2:2">
       <c r="B147" t="s">
-        <v>266</v>
+        <v>633</v>
       </c>
     </row>
     <row r="148" spans="2:2">
       <c r="B148" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="149" spans="2:2">
       <c r="B149" t="s">
-        <v>592</v>
+        <v>273</v>
       </c>
     </row>
     <row r="150" spans="2:2">
       <c r="B150" t="s">
-        <v>270</v>
+        <v>721</v>
       </c>
     </row>
     <row r="151" spans="2:2">
       <c r="B151" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="152" spans="2:2">
       <c r="B152" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="153" spans="2:2">
       <c r="B153" t="s">
-        <v>594</v>
+        <v>279</v>
       </c>
     </row>
     <row r="154" spans="2:2">
       <c r="B154" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
     </row>
     <row r="155" spans="2:2">
       <c r="B155" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
     </row>
     <row r="156" spans="2:2">
       <c r="B156" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
     </row>
     <row r="157" spans="2:2">
       <c r="B157" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
     </row>
     <row r="158" spans="2:2">
       <c r="B158" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
     </row>
     <row r="159" spans="2:2">
       <c r="B159" t="s">
-        <v>286</v>
+        <v>636</v>
       </c>
     </row>
     <row r="160" spans="2:2">
       <c r="B160" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="161" spans="2:2">
       <c r="B161" t="s">
-        <v>597</v>
+        <v>294</v>
       </c>
     </row>
     <row r="162" spans="2:2">
       <c r="B162" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
     </row>
     <row r="163" spans="2:2">
       <c r="B163" t="s">
-        <v>292</v>
+        <v>638</v>
       </c>
     </row>
     <row r="164" spans="2:2">
       <c r="B164" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="165" spans="2:2">
       <c r="B165" t="s">
-        <v>688</v>
+        <v>300</v>
       </c>
     </row>
     <row r="166" spans="2:2">
       <c r="B166" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
     </row>
     <row r="167" spans="2:2">
       <c r="B167" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
     </row>
     <row r="168" spans="2:2">
       <c r="B168" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
     </row>
     <row r="169" spans="2:2">
       <c r="B169" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
     </row>
     <row r="170" spans="2:2">
       <c r="B170" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
     </row>
     <row r="171" spans="2:2">
       <c r="B171" t="s">
-        <v>600</v>
+        <v>641</v>
       </c>
     </row>
     <row r="172" spans="2:2">
       <c r="B172" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="173" spans="2:2">
       <c r="B173" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
     </row>
     <row r="174" spans="2:2">
       <c r="B174" t="s">
-        <v>602</v>
+        <v>316</v>
       </c>
     </row>
     <row r="175" spans="2:2">
       <c r="B175" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
     </row>
     <row r="176" spans="2:2">
       <c r="B176" t="s">
-        <v>311</v>
+        <v>732</v>
       </c>
     </row>
     <row r="177" spans="2:2">
       <c r="B177" t="s">
-        <v>605</v>
+        <v>320</v>
       </c>
     </row>
     <row r="178" spans="2:2">
       <c r="B178" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
     </row>
     <row r="179" spans="2:2">
       <c r="B179" t="s">
-        <v>608</v>
+        <v>324</v>
       </c>
     </row>
     <row r="180" spans="2:2">
       <c r="B180" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
     </row>
     <row r="181" spans="2:2">
       <c r="B181" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
     </row>
     <row r="182" spans="2:2">
       <c r="B182" t="s">
-        <v>318</v>
+        <v>644</v>
       </c>
     </row>
     <row r="183" spans="2:2">
       <c r="B183" t="s">
-        <v>320</v>
+        <v>330</v>
       </c>
     </row>
     <row r="184" spans="2:2">
       <c r="B184" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
     </row>
     <row r="185" spans="2:2">
       <c r="B185" t="s">
-        <v>325</v>
+        <v>646</v>
       </c>
     </row>
     <row r="186" spans="2:2">
       <c r="B186" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
     </row>
     <row r="187" spans="2:2">
       <c r="B187" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
     </row>
     <row r="188" spans="2:2">
       <c r="B188" t="s">
-        <v>331</v>
+        <v>649</v>
       </c>
     </row>
     <row r="189" spans="2:2">
       <c r="B189" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="190" spans="2:2">
       <c r="B190" t="s">
-        <v>335</v>
+        <v>652</v>
       </c>
     </row>
     <row r="191" spans="2:2">
       <c r="B191" t="s">
-        <v>610</v>
+        <v>338</v>
       </c>
     </row>
     <row r="192" spans="2:2">
       <c r="B192" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="193" spans="2:2">
       <c r="B193" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="195" spans="2:2">
       <c r="B195" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="196" spans="2:2">
       <c r="B196" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="197" spans="2:2">
       <c r="B197" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="198" spans="2:2">
       <c r="B198" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="199" spans="2:2">
       <c r="B199" t="s">
-        <v>613</v>
+        <v>355</v>
       </c>
     </row>
     <row r="200" spans="2:2">
       <c r="B200" t="s">
-        <v>616</v>
+        <v>357</v>
       </c>
     </row>
     <row r="201" spans="2:2">
       <c r="B201" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
     </row>
     <row r="202" spans="2:2">
       <c r="B202" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
     </row>
     <row r="203" spans="2:2">
       <c r="B203" t="s">
-        <v>354</v>
+        <v>654</v>
       </c>
     </row>
     <row r="204" spans="2:2">
       <c r="B204" t="s">
-        <v>679</v>
+        <v>363</v>
       </c>
     </row>
     <row r="205" spans="2:2">
       <c r="B205" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
     </row>
     <row r="206" spans="2:2">
       <c r="B206" t="s">
-        <v>692</v>
+        <v>367</v>
       </c>
     </row>
     <row r="207" spans="2:2">
       <c r="B207" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
     </row>
     <row r="208" spans="2:2">
       <c r="B208" t="s">
-        <v>360</v>
+        <v>371</v>
       </c>
     </row>
     <row r="209" spans="2:2">
       <c r="B209" t="s">
-        <v>362</v>
+        <v>373</v>
       </c>
     </row>
     <row r="210" spans="2:2">
       <c r="B210" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
     </row>
     <row r="211" spans="2:2">
       <c r="B211" t="s">
-        <v>366</v>
+        <v>657</v>
       </c>
     </row>
     <row r="212" spans="2:2">
       <c r="B212" t="s">
-        <v>368</v>
+        <v>660</v>
       </c>
     </row>
     <row r="213" spans="2:2">
       <c r="B213" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
     </row>
     <row r="214" spans="2:2">
       <c r="B214" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
     </row>
     <row r="215" spans="2:2">
       <c r="B215" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
     </row>
     <row r="216" spans="2:2">
       <c r="B216" t="s">
-        <v>619</v>
+        <v>723</v>
       </c>
     </row>
     <row r="217" spans="2:2">
       <c r="B217" t="s">
-        <v>622</v>
+        <v>382</v>
       </c>
     </row>
     <row r="218" spans="2:2">
       <c r="B218" t="s">
-        <v>376</v>
+        <v>736</v>
       </c>
     </row>
     <row r="219" spans="2:2">
       <c r="B219" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
     </row>
     <row r="220" spans="2:2">
       <c r="B220" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
     </row>
     <row r="221" spans="2:2">
       <c r="B221" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
     </row>
     <row r="222" spans="2:2">
       <c r="B222" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
     </row>
     <row r="223" spans="2:2">
       <c r="B223" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
     </row>
     <row r="224" spans="2:2">
       <c r="B224" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
     </row>
     <row r="225" spans="2:2">
       <c r="B225" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="226" spans="2:2">
       <c r="B226" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="227" spans="2:2">
       <c r="B227" t="s">
-        <v>625</v>
+        <v>400</v>
       </c>
     </row>
     <row r="228" spans="2:2">
       <c r="B228" t="s">
-        <v>395</v>
+        <v>663</v>
       </c>
     </row>
     <row r="229" spans="2:2">
       <c r="B229" t="s">
-        <v>397</v>
+        <v>666</v>
       </c>
     </row>
     <row r="230" spans="2:2">
       <c r="B230" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="231" spans="2:2">
       <c r="B231" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="232" spans="2:2">
       <c r="B232" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="233" spans="2:2">
       <c r="B233" t="s">
-        <v>627</v>
+        <v>409</v>
       </c>
     </row>
     <row r="234" spans="2:2">
       <c r="B234" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
     </row>
     <row r="235" spans="2:2">
       <c r="B235" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
     </row>
     <row r="236" spans="2:2">
       <c r="B236" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
     </row>
     <row r="237" spans="2:2">
       <c r="B237" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
     </row>
     <row r="238" spans="2:2">
       <c r="B238" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
     </row>
     <row r="239" spans="2:2">
       <c r="B239" t="s">
-        <v>415</v>
+        <v>669</v>
       </c>
     </row>
     <row r="240" spans="2:2">
       <c r="B240" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="241" spans="2:2">
       <c r="B241" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="242" spans="2:2">
       <c r="B242" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="243" spans="2:2">
       <c r="B243" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="244" spans="2:2">
       <c r="B244" t="s">
-        <v>629</v>
+        <v>429</v>
       </c>
     </row>
     <row r="245" spans="2:2">
       <c r="B245" t="s">
-        <v>426</v>
+        <v>671</v>
       </c>
     </row>
     <row r="246" spans="2:2">
       <c r="B246" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="247" spans="2:2">
       <c r="B247" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="248" spans="2:2">
       <c r="B248" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="249" spans="2:2">
       <c r="B249" t="s">
-        <v>632</v>
+        <v>437</v>
       </c>
     </row>
     <row r="250" spans="2:2">
       <c r="B250" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
     </row>
     <row r="251" spans="2:2">
       <c r="B251" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
     </row>
     <row r="252" spans="2:2">
       <c r="B252" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
     </row>
     <row r="253" spans="2:2">
       <c r="B253" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
     </row>
     <row r="254" spans="2:2">
       <c r="B254" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
     </row>
     <row r="255" spans="2:2">
       <c r="B255" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
     </row>
     <row r="256" spans="2:2">
       <c r="B256" t="s">
-        <v>445</v>
+        <v>673</v>
       </c>
     </row>
     <row r="257" spans="2:2">
       <c r="B257" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
     </row>
     <row r="258" spans="2:2">
       <c r="B258" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
     </row>
     <row r="259" spans="2:2">
       <c r="B259" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="260" spans="2:2">
       <c r="B260" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
     </row>
     <row r="261" spans="2:2">
       <c r="B261" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
     </row>
     <row r="262" spans="2:2">
       <c r="B262" t="s">
-        <v>457</v>
+        <v>676</v>
       </c>
     </row>
     <row r="263" spans="2:2">
       <c r="B263" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="264" spans="2:2">
       <c r="B264" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="265" spans="2:2">
       <c r="B265" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="266" spans="2:2">
       <c r="B266" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="267" spans="2:2">
@@ -8560,301 +9049,406 @@
     </row>
     <row r="268" spans="2:2">
       <c r="B268" t="s">
-        <v>696</v>
+        <v>471</v>
       </c>
     </row>
     <row r="269" spans="2:2">
       <c r="B269" t="s">
-        <v>700</v>
+        <v>473</v>
       </c>
     </row>
     <row r="270" spans="2:2">
       <c r="B270" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="271" spans="2:2">
       <c r="B271" t="s">
-        <v>702</v>
+        <v>477</v>
       </c>
     </row>
     <row r="272" spans="2:2">
       <c r="B272" t="s">
-        <v>635</v>
+        <v>479</v>
       </c>
     </row>
     <row r="273" spans="2:2">
       <c r="B273" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
     </row>
     <row r="274" spans="2:2">
       <c r="B274" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
     </row>
     <row r="275" spans="2:2">
       <c r="B275" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
     </row>
     <row r="276" spans="2:2">
       <c r="B276" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
     </row>
     <row r="277" spans="2:2">
       <c r="B277" t="s">
-        <v>655</v>
+        <v>489</v>
       </c>
     </row>
     <row r="278" spans="2:2">
       <c r="B278" t="s">
-        <v>481</v>
+        <v>491</v>
       </c>
     </row>
     <row r="279" spans="2:2">
       <c r="B279" t="s">
-        <v>483</v>
+        <v>493</v>
       </c>
     </row>
     <row r="280" spans="2:2">
       <c r="B280" t="s">
-        <v>485</v>
+        <v>495</v>
       </c>
     </row>
     <row r="281" spans="2:2">
       <c r="B281" t="s">
-        <v>487</v>
+        <v>498</v>
       </c>
     </row>
     <row r="282" spans="2:2">
       <c r="B282" t="s">
-        <v>489</v>
+        <v>500</v>
       </c>
     </row>
     <row r="283" spans="2:2">
       <c r="B283" t="s">
-        <v>491</v>
+        <v>503</v>
       </c>
     </row>
     <row r="284" spans="2:2">
       <c r="B284" t="s">
-        <v>493</v>
+        <v>740</v>
       </c>
     </row>
     <row r="285" spans="2:2">
       <c r="B285" t="s">
-        <v>495</v>
+        <v>744</v>
       </c>
     </row>
     <row r="286" spans="2:2">
       <c r="B286" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
     </row>
     <row r="287" spans="2:2">
       <c r="B287" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
     </row>
     <row r="288" spans="2:2">
       <c r="B288" t="s">
-        <v>501</v>
+        <v>746</v>
       </c>
     </row>
     <row r="289" spans="2:2">
       <c r="B289" t="s">
-        <v>503</v>
+        <v>679</v>
       </c>
     </row>
     <row r="290" spans="2:2">
       <c r="B290" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="291" spans="2:2">
       <c r="B291" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
     <row r="292" spans="2:2">
       <c r="B292" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
     </row>
     <row r="293" spans="2:2">
       <c r="B293" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
     </row>
     <row r="294" spans="2:2">
       <c r="B294" t="s">
-        <v>513</v>
+        <v>699</v>
       </c>
     </row>
     <row r="295" spans="2:2">
       <c r="B295" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="296" spans="2:2">
       <c r="B296" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="297" spans="2:2">
       <c r="B297" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="298" spans="2:2">
       <c r="B298" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="299" spans="2:2">
       <c r="B299" t="s">
-        <v>638</v>
+        <v>525</v>
       </c>
     </row>
     <row r="300" spans="2:2">
       <c r="B300" t="s">
-        <v>640</v>
+        <v>527</v>
       </c>
     </row>
     <row r="301" spans="2:2">
       <c r="B301" t="s">
-        <v>643</v>
+        <v>529</v>
       </c>
     </row>
     <row r="302" spans="2:2">
       <c r="B302" t="s">
-        <v>523</v>
+        <v>531</v>
       </c>
     </row>
     <row r="303" spans="2:2">
       <c r="B303" t="s">
-        <v>525</v>
+        <v>533</v>
       </c>
     </row>
     <row r="304" spans="2:2">
       <c r="B304" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="305" spans="1:2">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="305" spans="2:2">
       <c r="B305" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="306" spans="1:2">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="306" spans="2:2">
       <c r="B306" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="307" spans="1:2">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="307" spans="2:2">
       <c r="B307" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="308" spans="1:2">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="308" spans="2:2">
       <c r="B308" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="309" spans="1:2">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="309" spans="2:2">
       <c r="B309" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="310" spans="2:2">
+      <c r="B310" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="311" spans="2:2">
+      <c r="B311" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="312" spans="2:2">
+      <c r="B312" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="313" spans="2:2">
+      <c r="B313" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="314" spans="2:2">
+      <c r="B314" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="315" spans="2:2">
+      <c r="B315" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="316" spans="2:2">
+      <c r="B316" t="s">
         <v>682</v>
       </c>
     </row>
-    <row r="310" spans="1:2">
-      <c r="B310" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="311" spans="1:2">
-      <c r="B311" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="312" spans="1:2">
-      <c r="B312" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="313" spans="1:2">
-      <c r="B313" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="314" spans="1:2">
-      <c r="B314" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="315" spans="1:2">
-      <c r="B315" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="316" spans="1:2">
-      <c r="B316" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="317" spans="1:2">
+    <row r="317" spans="2:2">
       <c r="B317" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="318" spans="1:2">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="318" spans="2:2">
       <c r="B318" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="320" spans="1:2">
-      <c r="A320" t="s">
-        <v>708</v>
-      </c>
+        <v>687</v>
+      </c>
+    </row>
+    <row r="319" spans="2:2">
+      <c r="B319" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="320" spans="2:2">
       <c r="B320" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="322" spans="1:2">
-      <c r="A322" t="s">
-        <v>709</v>
-      </c>
+        <v>561</v>
+      </c>
+    </row>
+    <row r="321" spans="2:2">
+      <c r="B321" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="322" spans="2:2">
       <c r="B322" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="323" spans="1:2">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="323" spans="2:2">
       <c r="B323" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="325" spans="1:2">
-      <c r="A325" t="s">
-        <v>710</v>
-      </c>
+        <v>567</v>
+      </c>
+    </row>
+    <row r="324" spans="2:2">
+      <c r="B324" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="325" spans="2:2">
       <c r="B325" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="326" spans="2:2">
+      <c r="B326" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="327" spans="2:2">
+      <c r="B327" t="s">
         <v>575</v>
       </c>
     </row>
-    <row r="326" spans="1:2">
-      <c r="B326" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="327" spans="1:2">
-      <c r="B327" t="s">
+    <row r="328" spans="2:2">
+      <c r="B328" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="329" spans="2:2">
+      <c r="B329" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="330" spans="2:2">
+      <c r="B330" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="331" spans="2:2">
+      <c r="B331" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="332" spans="2:2">
+      <c r="B332" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="333" spans="2:2">
+      <c r="B333" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="334" spans="2:2">
+      <c r="B334" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="335" spans="2:2">
+      <c r="B335" t="s">
         <v>589</v>
       </c>
     </row>
-    <row r="328" spans="1:2">
-      <c r="B328" t="s">
-        <v>600</v>
+    <row r="336" spans="2:2">
+      <c r="B336" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2">
+      <c r="B337" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2">
+      <c r="B338" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2">
+      <c r="B339" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2">
+      <c r="A341" t="s">
+        <v>752</v>
+      </c>
+      <c r="B341" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2">
+      <c r="A343" t="s">
+        <v>753</v>
+      </c>
+      <c r="B343" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2">
+      <c r="B344" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2">
+      <c r="A346" t="s">
+        <v>754</v>
+      </c>
+      <c r="B346" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2">
+      <c r="B347" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2">
+      <c r="B348" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2">
+      <c r="B349" t="s">
+        <v>644</v>
       </c>
     </row>
   </sheetData>
@@ -8874,7 +9468,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>556</v>
+        <v>600</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -8896,166 +9490,166 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>557</v>
+        <v>601</v>
       </c>
       <c r="B3">
         <v>2.72</v>
       </c>
       <c r="C3" t="s">
-        <v>558</v>
+        <v>602</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>559</v>
+        <v>603</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>560</v>
+        <v>604</v>
       </c>
       <c r="B4">
         <v>2.02</v>
       </c>
       <c r="C4" t="s">
-        <v>561</v>
+        <v>605</v>
       </c>
       <c r="D4" t="s">
         <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>562</v>
+        <v>606</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>563</v>
+        <v>607</v>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>564</v>
+        <v>608</v>
       </c>
       <c r="D5" t="s">
         <v>8</v>
       </c>
       <c r="E5" t="s">
-        <v>565</v>
+        <v>609</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>566</v>
+        <v>610</v>
       </c>
       <c r="B6">
         <v>2.09</v>
       </c>
       <c r="C6" t="s">
-        <v>567</v>
+        <v>611</v>
       </c>
       <c r="D6" t="s">
         <v>8</v>
       </c>
       <c r="E6" t="s">
-        <v>568</v>
+        <v>612</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>569</v>
+        <v>613</v>
       </c>
       <c r="B7">
         <v>2.2</v>
       </c>
       <c r="C7" t="s">
-        <v>570</v>
+        <v>614</v>
       </c>
       <c r="D7" t="s">
         <v>8</v>
       </c>
       <c r="E7" t="s">
-        <v>571</v>
+        <v>615</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>572</v>
+        <v>616</v>
       </c>
       <c r="B8">
         <v>2.79</v>
       </c>
       <c r="C8" t="s">
-        <v>573</v>
+        <v>617</v>
       </c>
       <c r="D8" t="s">
         <v>8</v>
       </c>
       <c r="E8" t="s">
-        <v>574</v>
+        <v>618</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>575</v>
+        <v>619</v>
       </c>
       <c r="B9">
         <v>2.98</v>
       </c>
       <c r="C9" t="s">
-        <v>576</v>
+        <v>620</v>
       </c>
       <c r="D9" t="s">
         <v>8</v>
       </c>
       <c r="E9" t="s">
-        <v>577</v>
+        <v>621</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>578</v>
+        <v>622</v>
       </c>
       <c r="B10">
         <v>1.95</v>
       </c>
       <c r="C10" t="s">
-        <v>579</v>
+        <v>623</v>
       </c>
       <c r="D10" t="s">
         <v>8</v>
       </c>
       <c r="E10" t="s">
-        <v>580</v>
+        <v>624</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>581</v>
+        <v>625</v>
       </c>
       <c r="B11">
         <v>1.79</v>
       </c>
       <c r="C11" t="s">
-        <v>582</v>
+        <v>626</v>
       </c>
       <c r="D11" t="s">
         <v>8</v>
       </c>
       <c r="E11" t="s">
-        <v>583</v>
+        <v>627</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>584</v>
+        <v>628</v>
       </c>
       <c r="B12">
         <v>1.6</v>
       </c>
       <c r="C12" t="s">
-        <v>585</v>
+        <v>629</v>
       </c>
       <c r="D12" t="s">
         <v>8</v>
@@ -9066,376 +9660,376 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>586</v>
+        <v>630</v>
       </c>
       <c r="B13">
         <v>2.4</v>
       </c>
       <c r="C13" t="s">
-        <v>587</v>
+        <v>631</v>
       </c>
       <c r="D13" t="s">
         <v>8</v>
       </c>
       <c r="E13" t="s">
-        <v>588</v>
+        <v>632</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>589</v>
+        <v>633</v>
       </c>
       <c r="B14">
         <v>2.9</v>
       </c>
       <c r="C14" t="s">
-        <v>590</v>
+        <v>634</v>
       </c>
       <c r="D14" t="s">
         <v>8</v>
       </c>
       <c r="E14" t="s">
-        <v>591</v>
+        <v>635</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>592</v>
+        <v>636</v>
       </c>
       <c r="B15">
         <v>1.9</v>
       </c>
       <c r="C15" t="s">
-        <v>593</v>
+        <v>637</v>
       </c>
       <c r="D15" t="s">
         <v>8</v>
       </c>
       <c r="E15" t="s">
-        <v>580</v>
+        <v>624</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>594</v>
+        <v>638</v>
       </c>
       <c r="B16">
         <v>2</v>
       </c>
       <c r="C16" t="s">
-        <v>595</v>
+        <v>639</v>
       </c>
       <c r="D16" t="s">
         <v>8</v>
       </c>
       <c r="E16" t="s">
-        <v>596</v>
+        <v>640</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>597</v>
+        <v>641</v>
       </c>
       <c r="B17">
         <v>1.79</v>
       </c>
       <c r="C17" t="s">
-        <v>598</v>
+        <v>642</v>
       </c>
       <c r="D17" t="s">
         <v>8</v>
       </c>
       <c r="E17" t="s">
-        <v>599</v>
+        <v>643</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>600</v>
+        <v>644</v>
       </c>
       <c r="B18">
         <v>1.88</v>
       </c>
       <c r="C18" t="s">
-        <v>601</v>
+        <v>645</v>
       </c>
       <c r="D18" t="s">
         <v>8</v>
       </c>
       <c r="E18" t="s">
-        <v>577</v>
+        <v>621</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>602</v>
+        <v>646</v>
       </c>
       <c r="B19">
         <v>1.6</v>
       </c>
       <c r="C19" t="s">
-        <v>603</v>
+        <v>647</v>
       </c>
       <c r="D19" t="s">
         <v>8</v>
       </c>
       <c r="E19" t="s">
-        <v>604</v>
+        <v>648</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>605</v>
+        <v>649</v>
       </c>
       <c r="B20">
         <v>2.9</v>
       </c>
       <c r="C20" t="s">
-        <v>606</v>
+        <v>650</v>
       </c>
       <c r="D20" t="s">
         <v>8</v>
       </c>
       <c r="E20" t="s">
-        <v>607</v>
+        <v>651</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>608</v>
+        <v>652</v>
       </c>
       <c r="B21">
         <v>1.95</v>
       </c>
       <c r="C21" t="s">
-        <v>609</v>
+        <v>653</v>
       </c>
       <c r="D21" t="s">
         <v>8</v>
       </c>
       <c r="E21" t="s">
-        <v>568</v>
+        <v>612</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>610</v>
+        <v>654</v>
       </c>
       <c r="B22">
         <v>2.9</v>
       </c>
       <c r="C22" t="s">
-        <v>611</v>
+        <v>655</v>
       </c>
       <c r="D22" t="s">
         <v>8</v>
       </c>
       <c r="E22" t="s">
-        <v>612</v>
+        <v>656</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>613</v>
+        <v>657</v>
       </c>
       <c r="B23">
         <v>2.48</v>
       </c>
       <c r="C23" t="s">
-        <v>614</v>
+        <v>658</v>
       </c>
       <c r="D23" t="s">
         <v>8</v>
       </c>
       <c r="E23" t="s">
-        <v>615</v>
+        <v>659</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>616</v>
+        <v>660</v>
       </c>
       <c r="B24">
         <v>3.2</v>
       </c>
       <c r="C24" t="s">
-        <v>617</v>
+        <v>661</v>
       </c>
       <c r="D24" t="s">
         <v>8</v>
       </c>
       <c r="E24" t="s">
-        <v>618</v>
+        <v>662</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>619</v>
+        <v>663</v>
       </c>
       <c r="B25">
         <v>1.97</v>
       </c>
       <c r="C25" t="s">
-        <v>620</v>
+        <v>664</v>
       </c>
       <c r="D25" t="s">
         <v>8</v>
       </c>
       <c r="E25" t="s">
-        <v>621</v>
+        <v>665</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>622</v>
+        <v>666</v>
       </c>
       <c r="B26">
         <v>2.3</v>
       </c>
       <c r="C26" t="s">
-        <v>623</v>
+        <v>667</v>
       </c>
       <c r="D26" t="s">
         <v>8</v>
       </c>
       <c r="E26" t="s">
-        <v>624</v>
+        <v>668</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>625</v>
+        <v>669</v>
       </c>
       <c r="B27">
         <v>2.3</v>
       </c>
       <c r="C27" t="s">
-        <v>626</v>
+        <v>670</v>
       </c>
       <c r="D27" t="s">
         <v>8</v>
       </c>
       <c r="E27" t="s">
-        <v>568</v>
+        <v>612</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>627</v>
+        <v>671</v>
       </c>
       <c r="B28">
         <v>1.95</v>
       </c>
       <c r="C28" t="s">
-        <v>628</v>
+        <v>672</v>
       </c>
       <c r="D28" t="s">
         <v>8</v>
       </c>
       <c r="E28" t="s">
-        <v>599</v>
+        <v>643</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>629</v>
+        <v>673</v>
       </c>
       <c r="B29">
         <v>2.04</v>
       </c>
       <c r="C29" t="s">
-        <v>630</v>
+        <v>674</v>
       </c>
       <c r="D29" t="s">
         <v>8</v>
       </c>
       <c r="E29" t="s">
-        <v>631</v>
+        <v>675</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>632</v>
+        <v>676</v>
       </c>
       <c r="B30">
         <v>1.66</v>
       </c>
       <c r="C30" t="s">
-        <v>633</v>
+        <v>677</v>
       </c>
       <c r="D30" t="s">
         <v>8</v>
       </c>
       <c r="E30" t="s">
-        <v>634</v>
+        <v>678</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>635</v>
+        <v>679</v>
       </c>
       <c r="B31">
         <v>2.48</v>
       </c>
       <c r="C31" t="s">
-        <v>636</v>
+        <v>680</v>
       </c>
       <c r="D31" t="s">
         <v>8</v>
       </c>
       <c r="E31" t="s">
-        <v>637</v>
+        <v>681</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>638</v>
+        <v>682</v>
       </c>
       <c r="B32">
         <v>2.8</v>
       </c>
       <c r="C32" t="s">
-        <v>639</v>
+        <v>683</v>
       </c>
       <c r="D32" t="s">
         <v>8</v>
       </c>
       <c r="E32" t="s">
-        <v>571</v>
+        <v>615</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>640</v>
+        <v>684</v>
       </c>
       <c r="B33">
         <v>2.5</v>
       </c>
       <c r="C33" t="s">
-        <v>641</v>
+        <v>685</v>
       </c>
       <c r="D33" t="s">
         <v>8</v>
       </c>
       <c r="E33" t="s">
-        <v>642</v>
+        <v>686</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>643</v>
+        <v>687</v>
       </c>
       <c r="B34">
         <v>2.02</v>
       </c>
       <c r="C34" t="s">
-        <v>644</v>
+        <v>688</v>
       </c>
       <c r="D34" t="s">
         <v>8</v>
       </c>
       <c r="E34" t="s">
-        <v>565</v>
+        <v>609</v>
       </c>
     </row>
   </sheetData>
@@ -9455,7 +10049,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>645</v>
+        <v>689</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -9477,70 +10071,70 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>646</v>
+        <v>690</v>
       </c>
       <c r="B3">
         <v>2.7</v>
       </c>
       <c r="C3" t="s">
-        <v>647</v>
+        <v>691</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>648</v>
+        <v>692</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>649</v>
+        <v>693</v>
       </c>
       <c r="B4">
         <v>2.59</v>
       </c>
       <c r="C4" t="s">
-        <v>650</v>
+        <v>694</v>
       </c>
       <c r="D4" t="s">
         <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>651</v>
+        <v>695</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>652</v>
+        <v>696</v>
       </c>
       <c r="B5">
         <v>3.18</v>
       </c>
       <c r="C5" t="s">
-        <v>653</v>
+        <v>697</v>
       </c>
       <c r="D5" t="s">
         <v>8</v>
       </c>
       <c r="E5" t="s">
-        <v>654</v>
+        <v>698</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>655</v>
+        <v>699</v>
       </c>
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>656</v>
+        <v>700</v>
       </c>
       <c r="D6" t="s">
         <v>8</v>
       </c>
       <c r="E6" t="s">
-        <v>599</v>
+        <v>643</v>
       </c>
     </row>
   </sheetData>
@@ -9560,7 +10154,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>657</v>
+        <v>701</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -9582,19 +10176,19 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>658</v>
+        <v>702</v>
       </c>
       <c r="B3">
         <v>2.2</v>
       </c>
       <c r="C3" t="s">
-        <v>659</v>
+        <v>703</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>660</v>
+        <v>704</v>
       </c>
     </row>
   </sheetData>
@@ -9614,7 +10208,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>661</v>
+        <v>705</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -9636,19 +10230,19 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>662</v>
+        <v>706</v>
       </c>
       <c r="B3">
         <v>1.32</v>
       </c>
       <c r="C3" t="s">
-        <v>663</v>
+        <v>707</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>664</v>
+        <v>708</v>
       </c>
     </row>
   </sheetData>
@@ -9668,7 +10262,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>665</v>
+        <v>709</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -9690,19 +10284,19 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>666</v>
+        <v>710</v>
       </c>
       <c r="B3">
         <v>2.45</v>
       </c>
       <c r="C3" t="s">
-        <v>667</v>
+        <v>711</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>668</v>
+        <v>712</v>
       </c>
     </row>
   </sheetData>
@@ -9722,7 +10316,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>669</v>
+        <v>713</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -9744,104 +10338,104 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>670</v>
+        <v>714</v>
       </c>
       <c r="B3">
         <v>1.9</v>
       </c>
       <c r="C3" t="s">
-        <v>671</v>
+        <v>715</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>672</v>
+        <v>716</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>673</v>
+        <v>717</v>
       </c>
       <c r="B4">
         <v>2.11</v>
       </c>
       <c r="C4" t="s">
-        <v>674</v>
+        <v>718</v>
       </c>
       <c r="D4" t="s">
         <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>672</v>
+        <v>716</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>675</v>
+        <v>719</v>
       </c>
       <c r="B5">
         <v>2.7</v>
       </c>
       <c r="C5" t="s">
-        <v>676</v>
+        <v>720</v>
       </c>
       <c r="D5" t="s">
         <v>8</v>
       </c>
       <c r="E5" t="s">
-        <v>591</v>
+        <v>635</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>677</v>
+        <v>721</v>
       </c>
       <c r="B6">
         <v>2.58</v>
       </c>
       <c r="C6" t="s">
-        <v>678</v>
+        <v>722</v>
       </c>
       <c r="D6" t="s">
         <v>8</v>
       </c>
       <c r="E6" t="s">
-        <v>565</v>
+        <v>609</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>679</v>
+        <v>723</v>
       </c>
       <c r="B7">
         <v>1.93</v>
       </c>
       <c r="C7" t="s">
-        <v>680</v>
+        <v>724</v>
       </c>
       <c r="D7" t="s">
         <v>8</v>
       </c>
       <c r="E7" t="s">
-        <v>681</v>
+        <v>725</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>682</v>
+        <v>726</v>
       </c>
       <c r="B8">
         <v>2.05</v>
       </c>
       <c r="C8" t="s">
-        <v>683</v>
+        <v>727</v>
       </c>
       <c r="D8" t="s">
         <v>8</v>
       </c>
       <c r="E8" t="s">
-        <v>568</v>
+        <v>612</v>
       </c>
     </row>
   </sheetData>
@@ -9861,7 +10455,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>684</v>
+        <v>728</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -9883,19 +10477,19 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>685</v>
+        <v>729</v>
       </c>
       <c r="B3">
         <v>0.93</v>
       </c>
       <c r="C3" t="s">
-        <v>686</v>
+        <v>730</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>417</v>
+        <v>443</v>
       </c>
     </row>
   </sheetData>
@@ -9915,7 +10509,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>687</v>
+        <v>731</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -9937,19 +10531,19 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>688</v>
+        <v>732</v>
       </c>
       <c r="B3">
         <v>2.17</v>
       </c>
       <c r="C3" t="s">
-        <v>689</v>
+        <v>733</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>690</v>
+        <v>734</v>
       </c>
     </row>
   </sheetData>

--- a/pdb/nsp3/SARS-CoV-2/domains_and_infos_of_nsp3.xlsx
+++ b/pdb/nsp3/SARS-CoV-2/domains_and_infos_of_nsp3.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1771" uniqueCount="755">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1776" uniqueCount="758">
   <si>
     <t>nsp3_Macro1_</t>
   </si>
@@ -2123,6 +2123,15 @@
   </si>
   <si>
     <t>2020-04-28</t>
+  </si>
+  <si>
+    <t>7tzj</t>
+  </si>
+  <si>
+    <t>SARS COV-2 PLPRO IN COMPLEX WITH INHIBITOR 3K</t>
+  </si>
+  <si>
+    <t>2022-02-15</t>
   </si>
   <si>
     <t>7sgv</t>
@@ -7531,7 +7540,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -7553,19 +7562,19 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="B3">
         <v>2.72</v>
       </c>
       <c r="C3" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
     </row>
   </sheetData>
@@ -7585,7 +7594,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -7607,19 +7616,19 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="B3">
         <v>2.68</v>
       </c>
       <c r="C3" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
     </row>
   </sheetData>
@@ -7639,7 +7648,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -7661,13 +7670,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="B3">
         <v>3.21</v>
       </c>
       <c r="C3" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
@@ -7678,19 +7687,19 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="B4">
         <v>2.73</v>
       </c>
       <c r="C4" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="D4" t="s">
         <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
     </row>
   </sheetData>
@@ -7700,7 +7709,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B349"/>
+  <dimension ref="A1:B350"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.7109375" customWidth="1"/>
@@ -7708,12 +7717,12 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
@@ -7721,7 +7730,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="B3" t="s">
         <v>6</v>
@@ -7884,7 +7893,7 @@
     </row>
     <row r="35" spans="2:2">
       <c r="B35" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
     </row>
     <row r="36" spans="2:2">
@@ -7909,7 +7918,7 @@
     </row>
     <row r="40" spans="2:2">
       <c r="B40" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
     </row>
     <row r="41" spans="2:2">
@@ -7934,7 +7943,7 @@
     </row>
     <row r="45" spans="2:2">
       <c r="B45" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
     </row>
     <row r="46" spans="2:2">
@@ -7984,7 +7993,7 @@
     </row>
     <row r="55" spans="2:2">
       <c r="B55" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
     </row>
     <row r="56" spans="2:2">
@@ -8214,7 +8223,7 @@
     </row>
     <row r="101" spans="2:2">
       <c r="B101" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
     </row>
     <row r="102" spans="2:2">
@@ -8344,7 +8353,7 @@
     </row>
     <row r="127" spans="2:2">
       <c r="B127" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
     </row>
     <row r="128" spans="2:2">
@@ -8354,7 +8363,7 @@
     </row>
     <row r="129" spans="2:2">
       <c r="B129" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
     </row>
     <row r="130" spans="2:2">
@@ -8459,7 +8468,7 @@
     </row>
     <row r="150" spans="2:2">
       <c r="B150" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
     </row>
     <row r="151" spans="2:2">
@@ -8589,7 +8598,7 @@
     </row>
     <row r="176" spans="2:2">
       <c r="B176" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
     </row>
     <row r="177" spans="2:2">
@@ -8649,805 +8658,810 @@
     </row>
     <row r="188" spans="2:2">
       <c r="B188" t="s">
-        <v>649</v>
+        <v>699</v>
       </c>
     </row>
     <row r="189" spans="2:2">
       <c r="B189" t="s">
-        <v>337</v>
+        <v>649</v>
       </c>
     </row>
     <row r="190" spans="2:2">
       <c r="B190" t="s">
-        <v>652</v>
+        <v>337</v>
       </c>
     </row>
     <row r="191" spans="2:2">
       <c r="B191" t="s">
-        <v>338</v>
+        <v>652</v>
       </c>
     </row>
     <row r="192" spans="2:2">
       <c r="B192" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="193" spans="2:2">
       <c r="B193" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="195" spans="2:2">
       <c r="B195" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="196" spans="2:2">
       <c r="B196" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="197" spans="2:2">
       <c r="B197" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="198" spans="2:2">
       <c r="B198" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="199" spans="2:2">
       <c r="B199" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="200" spans="2:2">
       <c r="B200" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="201" spans="2:2">
       <c r="B201" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="202" spans="2:2">
       <c r="B202" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="203" spans="2:2">
       <c r="B203" t="s">
-        <v>654</v>
+        <v>361</v>
       </c>
     </row>
     <row r="204" spans="2:2">
       <c r="B204" t="s">
-        <v>363</v>
+        <v>654</v>
       </c>
     </row>
     <row r="205" spans="2:2">
       <c r="B205" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="206" spans="2:2">
       <c r="B206" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="207" spans="2:2">
       <c r="B207" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="208" spans="2:2">
       <c r="B208" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="209" spans="2:2">
       <c r="B209" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="210" spans="2:2">
       <c r="B210" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="211" spans="2:2">
       <c r="B211" t="s">
-        <v>657</v>
+        <v>374</v>
       </c>
     </row>
     <row r="212" spans="2:2">
       <c r="B212" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
     </row>
     <row r="213" spans="2:2">
       <c r="B213" t="s">
-        <v>377</v>
+        <v>660</v>
       </c>
     </row>
     <row r="214" spans="2:2">
       <c r="B214" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="215" spans="2:2">
       <c r="B215" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="216" spans="2:2">
       <c r="B216" t="s">
-        <v>723</v>
+        <v>380</v>
       </c>
     </row>
     <row r="217" spans="2:2">
       <c r="B217" t="s">
-        <v>382</v>
+        <v>726</v>
       </c>
     </row>
     <row r="218" spans="2:2">
       <c r="B218" t="s">
-        <v>736</v>
+        <v>382</v>
       </c>
     </row>
     <row r="219" spans="2:2">
       <c r="B219" t="s">
-        <v>384</v>
+        <v>739</v>
       </c>
     </row>
     <row r="220" spans="2:2">
       <c r="B220" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="221" spans="2:2">
       <c r="B221" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="222" spans="2:2">
       <c r="B222" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="223" spans="2:2">
       <c r="B223" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="224" spans="2:2">
       <c r="B224" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="225" spans="2:2">
       <c r="B225" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="226" spans="2:2">
       <c r="B226" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="227" spans="2:2">
       <c r="B227" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="228" spans="2:2">
       <c r="B228" t="s">
-        <v>663</v>
+        <v>400</v>
       </c>
     </row>
     <row r="229" spans="2:2">
       <c r="B229" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
     </row>
     <row r="230" spans="2:2">
       <c r="B230" t="s">
-        <v>402</v>
+        <v>666</v>
       </c>
     </row>
     <row r="231" spans="2:2">
       <c r="B231" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="232" spans="2:2">
       <c r="B232" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="233" spans="2:2">
       <c r="B233" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="234" spans="2:2">
       <c r="B234" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="235" spans="2:2">
       <c r="B235" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="236" spans="2:2">
       <c r="B236" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="237" spans="2:2">
       <c r="B237" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="238" spans="2:2">
       <c r="B238" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="239" spans="2:2">
       <c r="B239" t="s">
-        <v>669</v>
+        <v>420</v>
       </c>
     </row>
     <row r="240" spans="2:2">
       <c r="B240" t="s">
-        <v>421</v>
+        <v>669</v>
       </c>
     </row>
     <row r="241" spans="2:2">
       <c r="B241" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="242" spans="2:2">
       <c r="B242" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="243" spans="2:2">
       <c r="B243" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="244" spans="2:2">
       <c r="B244" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="245" spans="2:2">
       <c r="B245" t="s">
-        <v>671</v>
+        <v>429</v>
       </c>
     </row>
     <row r="246" spans="2:2">
       <c r="B246" t="s">
-        <v>431</v>
+        <v>671</v>
       </c>
     </row>
     <row r="247" spans="2:2">
       <c r="B247" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="248" spans="2:2">
       <c r="B248" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="249" spans="2:2">
       <c r="B249" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="250" spans="2:2">
       <c r="B250" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="251" spans="2:2">
       <c r="B251" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="252" spans="2:2">
       <c r="B252" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
     </row>
     <row r="253" spans="2:2">
       <c r="B253" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="254" spans="2:2">
       <c r="B254" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="255" spans="2:2">
       <c r="B255" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="256" spans="2:2">
       <c r="B256" t="s">
-        <v>673</v>
+        <v>450</v>
       </c>
     </row>
     <row r="257" spans="2:2">
       <c r="B257" t="s">
-        <v>452</v>
+        <v>673</v>
       </c>
     </row>
     <row r="258" spans="2:2">
       <c r="B258" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="259" spans="2:2">
       <c r="B259" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="260" spans="2:2">
       <c r="B260" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="261" spans="2:2">
       <c r="B261" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="262" spans="2:2">
       <c r="B262" t="s">
-        <v>676</v>
+        <v>460</v>
       </c>
     </row>
     <row r="263" spans="2:2">
       <c r="B263" t="s">
-        <v>462</v>
+        <v>676</v>
       </c>
     </row>
     <row r="264" spans="2:2">
       <c r="B264" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="265" spans="2:2">
       <c r="B265" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="266" spans="2:2">
       <c r="B266" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="267" spans="2:2">
       <c r="B267" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="268" spans="2:2">
       <c r="B268" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="269" spans="2:2">
       <c r="B269" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="270" spans="2:2">
       <c r="B270" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="271" spans="2:2">
       <c r="B271" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="272" spans="2:2">
       <c r="B272" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="273" spans="2:2">
       <c r="B273" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="274" spans="2:2">
       <c r="B274" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="275" spans="2:2">
       <c r="B275" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="276" spans="2:2">
       <c r="B276" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="277" spans="2:2">
       <c r="B277" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="278" spans="2:2">
       <c r="B278" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="279" spans="2:2">
       <c r="B279" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="280" spans="2:2">
       <c r="B280" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="281" spans="2:2">
       <c r="B281" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
     </row>
     <row r="282" spans="2:2">
       <c r="B282" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="283" spans="2:2">
       <c r="B283" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
     </row>
     <row r="284" spans="2:2">
       <c r="B284" t="s">
-        <v>740</v>
+        <v>503</v>
       </c>
     </row>
     <row r="285" spans="2:2">
       <c r="B285" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="286" spans="2:2">
       <c r="B286" t="s">
-        <v>505</v>
+        <v>747</v>
       </c>
     </row>
     <row r="287" spans="2:2">
       <c r="B287" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="288" spans="2:2">
       <c r="B288" t="s">
-        <v>746</v>
+        <v>507</v>
       </c>
     </row>
     <row r="289" spans="2:2">
       <c r="B289" t="s">
-        <v>679</v>
+        <v>749</v>
       </c>
     </row>
     <row r="290" spans="2:2">
       <c r="B290" t="s">
-        <v>509</v>
+        <v>679</v>
       </c>
     </row>
     <row r="291" spans="2:2">
       <c r="B291" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="292" spans="2:2">
       <c r="B292" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="293" spans="2:2">
       <c r="B293" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="294" spans="2:2">
       <c r="B294" t="s">
-        <v>699</v>
+        <v>515</v>
       </c>
     </row>
     <row r="295" spans="2:2">
       <c r="B295" t="s">
-        <v>517</v>
+        <v>702</v>
       </c>
     </row>
     <row r="296" spans="2:2">
       <c r="B296" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="297" spans="2:2">
       <c r="B297" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="298" spans="2:2">
       <c r="B298" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="299" spans="2:2">
       <c r="B299" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="300" spans="2:2">
       <c r="B300" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="301" spans="2:2">
       <c r="B301" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="302" spans="2:2">
       <c r="B302" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="303" spans="2:2">
       <c r="B303" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="304" spans="2:2">
       <c r="B304" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="305" spans="2:2">
       <c r="B305" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="306" spans="2:2">
       <c r="B306" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="307" spans="2:2">
       <c r="B307" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="308" spans="2:2">
       <c r="B308" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="309" spans="2:2">
       <c r="B309" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="310" spans="2:2">
       <c r="B310" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="311" spans="2:2">
       <c r="B311" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="312" spans="2:2">
       <c r="B312" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="313" spans="2:2">
       <c r="B313" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="314" spans="2:2">
       <c r="B314" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="315" spans="2:2">
       <c r="B315" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="316" spans="2:2">
       <c r="B316" t="s">
-        <v>682</v>
+        <v>557</v>
       </c>
     </row>
     <row r="317" spans="2:2">
       <c r="B317" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="318" spans="2:2">
       <c r="B318" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
     </row>
     <row r="319" spans="2:2">
       <c r="B319" t="s">
-        <v>559</v>
+        <v>687</v>
       </c>
     </row>
     <row r="320" spans="2:2">
       <c r="B320" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="321" spans="2:2">
       <c r="B321" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="322" spans="2:2">
       <c r="B322" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="323" spans="2:2">
       <c r="B323" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
     </row>
     <row r="324" spans="2:2">
       <c r="B324" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="325" spans="2:2">
       <c r="B325" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
     <row r="326" spans="2:2">
       <c r="B326" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="327" spans="2:2">
       <c r="B327" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="328" spans="2:2">
       <c r="B328" t="s">
-        <v>726</v>
+        <v>575</v>
       </c>
     </row>
     <row r="329" spans="2:2">
       <c r="B329" t="s">
-        <v>577</v>
+        <v>729</v>
       </c>
     </row>
     <row r="330" spans="2:2">
       <c r="B330" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="331" spans="2:2">
       <c r="B331" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
     </row>
     <row r="332" spans="2:2">
       <c r="B332" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
     </row>
     <row r="333" spans="2:2">
       <c r="B333" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
     </row>
     <row r="334" spans="2:2">
       <c r="B334" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
     </row>
     <row r="335" spans="2:2">
       <c r="B335" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
     </row>
     <row r="336" spans="2:2">
       <c r="B336" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="337" spans="1:2">
       <c r="B337" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
     </row>
     <row r="338" spans="1:2">
       <c r="B338" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
     </row>
     <row r="339" spans="1:2">
       <c r="B339" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2">
+      <c r="B340" t="s">
         <v>598</v>
       </c>
     </row>
-    <row r="341" spans="1:2">
-      <c r="A341" t="s">
-        <v>752</v>
-      </c>
-      <c r="B341" t="s">
+    <row r="342" spans="1:2">
+      <c r="A342" t="s">
+        <v>755</v>
+      </c>
+      <c r="B342" t="s">
         <v>696</v>
       </c>
     </row>
-    <row r="343" spans="1:2">
-      <c r="A343" t="s">
-        <v>753</v>
-      </c>
-      <c r="B343" t="s">
+    <row r="344" spans="1:2">
+      <c r="A344" t="s">
+        <v>756</v>
+      </c>
+      <c r="B344" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="344" spans="1:2">
-      <c r="B344" t="s">
+    <row r="345" spans="1:2">
+      <c r="B345" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="346" spans="1:2">
-      <c r="A346" t="s">
-        <v>754</v>
-      </c>
-      <c r="B346" t="s">
+    <row r="347" spans="1:2">
+      <c r="A347" t="s">
+        <v>757</v>
+      </c>
+      <c r="B347" t="s">
         <v>619</v>
-      </c>
-    </row>
-    <row r="347" spans="1:2">
-      <c r="B347" t="s">
-        <v>719</v>
       </c>
     </row>
     <row r="348" spans="1:2">
       <c r="B348" t="s">
-        <v>633</v>
+        <v>722</v>
       </c>
     </row>
     <row r="349" spans="1:2">
       <c r="B349" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2">
+      <c r="B350" t="s">
         <v>644</v>
       </c>
     </row>
@@ -10039,7 +10053,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="110.7109375" customWidth="1"/>
@@ -10125,7 +10139,7 @@
         <v>699</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>2.66</v>
       </c>
       <c r="C6" t="s">
         <v>700</v>
@@ -10134,6 +10148,23 @@
         <v>8</v>
       </c>
       <c r="E6" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>702</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7" t="s">
+        <v>703</v>
+      </c>
+      <c r="D7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" t="s">
         <v>643</v>
       </c>
     </row>
@@ -10154,7 +10185,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -10176,19 +10207,19 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="B3">
         <v>2.2</v>
       </c>
       <c r="C3" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
     </row>
   </sheetData>
@@ -10208,7 +10239,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -10230,19 +10261,19 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="B3">
         <v>1.32</v>
       </c>
       <c r="C3" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
     </row>
   </sheetData>
@@ -10262,7 +10293,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -10284,19 +10315,19 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="B3">
         <v>2.45</v>
       </c>
       <c r="C3" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
     </row>
   </sheetData>
@@ -10316,7 +10347,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -10338,47 +10369,47 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="B3">
         <v>1.9</v>
       </c>
       <c r="C3" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="B4">
         <v>2.11</v>
       </c>
       <c r="C4" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="D4" t="s">
         <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="B5">
         <v>2.7</v>
       </c>
       <c r="C5" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="D5" t="s">
         <v>8</v>
@@ -10389,13 +10420,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="B6">
         <v>2.58</v>
       </c>
       <c r="C6" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="D6" t="s">
         <v>8</v>
@@ -10406,30 +10437,30 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="B7">
         <v>1.93</v>
       </c>
       <c r="C7" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="D7" t="s">
         <v>8</v>
       </c>
       <c r="E7" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="B8">
         <v>2.05</v>
       </c>
       <c r="C8" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="D8" t="s">
         <v>8</v>
@@ -10455,7 +10486,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -10477,13 +10508,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="B3">
         <v>0.93</v>
       </c>
       <c r="C3" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
@@ -10509,7 +10540,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -10531,19 +10562,19 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="B3">
         <v>2.17</v>
       </c>
       <c r="C3" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
     </row>
   </sheetData>

--- a/pdb/nsp3/SARS-CoV-2/domains_and_infos_of_nsp3.xlsx
+++ b/pdb/nsp3/SARS-CoV-2/domains_and_infos_of_nsp3.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1776" uniqueCount="758">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1801" uniqueCount="769">
   <si>
     <t>nsp3_Macro1_</t>
   </si>
@@ -2125,6 +2125,15 @@
     <t>2020-04-28</t>
   </si>
   <si>
+    <t>7qch</t>
+  </si>
+  <si>
+    <t>STRUCTURE OF SARS-COV-2 PAPAIN-LIKE PROTEASE BOUND TO N-(3,5- DIMETHOXY-4-HYDROXYBENZYLIDEN)THIOSEMICARBAZONE</t>
+  </si>
+  <si>
+    <t>2021-11-24</t>
+  </si>
+  <si>
     <t>7tzj</t>
   </si>
   <si>
@@ -2134,10 +2143,34 @@
     <t>2022-02-15</t>
   </si>
   <si>
+    <t>7qci</t>
+  </si>
+  <si>
+    <t>STRUCTURE OF SARS-COV-2 PAPAIN-LIKE PROTEASE BOUND TO N-(3,4- DIHYDROXYBENZYLIDENE)-THIOSEMICARBAZONE</t>
+  </si>
+  <si>
+    <t>7qcj</t>
+  </si>
+  <si>
+    <t>STRUCTURE OF SARS-COV-2 PAPAIN-LIKE PROTEASE BOUND TO N-(2,4- DIHYDROXYBENZYLIDENE)-THIOSEMICARBAZONE</t>
+  </si>
+  <si>
     <t>7sgv</t>
   </si>
   <si>
     <t>PAPAIN-LIKE PROTEASE OF SARS COV-2, C111S MUTANT, IN COMPLEX WITH PLP_SNYDER630 INHIBITOR</t>
+  </si>
+  <si>
+    <t>7qck</t>
+  </si>
+  <si>
+    <t>STRUCTURE OF SARS-COV-2 PAPAIN-LIKE PROTEASE BOUND TO N-(2,5- DIHYDROXYBENZYLIDENE)-THIOSEMICARBAZONE</t>
+  </si>
+  <si>
+    <t>7qcm</t>
+  </si>
+  <si>
+    <t>STRUCTURE OF SARS-COV-2 PAPAIN-LIKE PROTEASE BOUND TO N-(3-METHOXY-4- HYDROXY-ACETOPHENONE)THIOSEMICARBAZONE</t>
   </si>
   <si>
     <t>nsp3_betaSM-M_</t>
@@ -7540,7 +7573,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>738</v>
+        <v>749</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -7562,19 +7595,19 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>739</v>
+        <v>750</v>
       </c>
       <c r="B3">
         <v>2.72</v>
       </c>
       <c r="C3" t="s">
-        <v>740</v>
+        <v>751</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>741</v>
+        <v>752</v>
       </c>
     </row>
   </sheetData>
@@ -7594,7 +7627,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>742</v>
+        <v>753</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -7616,19 +7649,19 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>743</v>
+        <v>754</v>
       </c>
       <c r="B3">
         <v>2.68</v>
       </c>
       <c r="C3" t="s">
-        <v>744</v>
+        <v>755</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>745</v>
+        <v>756</v>
       </c>
     </row>
   </sheetData>
@@ -7648,7 +7681,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>746</v>
+        <v>757</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -7670,13 +7703,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>747</v>
+        <v>758</v>
       </c>
       <c r="B3">
         <v>3.21</v>
       </c>
       <c r="C3" t="s">
-        <v>748</v>
+        <v>759</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
@@ -7687,19 +7720,19 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>749</v>
+        <v>760</v>
       </c>
       <c r="B4">
         <v>2.73</v>
       </c>
       <c r="C4" t="s">
-        <v>750</v>
+        <v>761</v>
       </c>
       <c r="D4" t="s">
         <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>751</v>
+        <v>762</v>
       </c>
     </row>
   </sheetData>
@@ -7709,7 +7742,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B350"/>
+  <dimension ref="A1:B355"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.7109375" customWidth="1"/>
@@ -7717,12 +7750,12 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>752</v>
+        <v>763</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>753</v>
+        <v>764</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
@@ -7730,7 +7763,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>754</v>
+        <v>765</v>
       </c>
       <c r="B3" t="s">
         <v>6</v>
@@ -7893,7 +7926,7 @@
     </row>
     <row r="35" spans="2:2">
       <c r="B35" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
     </row>
     <row r="36" spans="2:2">
@@ -7918,7 +7951,7 @@
     </row>
     <row r="40" spans="2:2">
       <c r="B40" t="s">
-        <v>709</v>
+        <v>720</v>
       </c>
     </row>
     <row r="41" spans="2:2">
@@ -7943,7 +7976,7 @@
     </row>
     <row r="45" spans="2:2">
       <c r="B45" t="s">
-        <v>713</v>
+        <v>724</v>
       </c>
     </row>
     <row r="46" spans="2:2">
@@ -7993,7 +8026,7 @@
     </row>
     <row r="55" spans="2:2">
       <c r="B55" t="s">
-        <v>717</v>
+        <v>728</v>
       </c>
     </row>
     <row r="56" spans="2:2">
@@ -8223,7 +8256,7 @@
     </row>
     <row r="101" spans="2:2">
       <c r="B101" t="s">
-        <v>720</v>
+        <v>731</v>
       </c>
     </row>
     <row r="102" spans="2:2">
@@ -8353,7 +8386,7 @@
     </row>
     <row r="127" spans="2:2">
       <c r="B127" t="s">
-        <v>732</v>
+        <v>743</v>
       </c>
     </row>
     <row r="128" spans="2:2">
@@ -8363,7 +8396,7 @@
     </row>
     <row r="129" spans="2:2">
       <c r="B129" t="s">
-        <v>722</v>
+        <v>733</v>
       </c>
     </row>
     <row r="130" spans="2:2">
@@ -8468,7 +8501,7 @@
     </row>
     <row r="150" spans="2:2">
       <c r="B150" t="s">
-        <v>724</v>
+        <v>735</v>
       </c>
     </row>
     <row r="151" spans="2:2">
@@ -8478,990 +8511,1015 @@
     </row>
     <row r="152" spans="2:2">
       <c r="B152" t="s">
-        <v>277</v>
+        <v>699</v>
       </c>
     </row>
     <row r="153" spans="2:2">
       <c r="B153" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="154" spans="2:2">
       <c r="B154" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="155" spans="2:2">
       <c r="B155" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="156" spans="2:2">
       <c r="B156" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="157" spans="2:2">
       <c r="B157" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
     <row r="158" spans="2:2">
       <c r="B158" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="159" spans="2:2">
       <c r="B159" t="s">
-        <v>636</v>
+        <v>290</v>
       </c>
     </row>
     <row r="160" spans="2:2">
       <c r="B160" t="s">
-        <v>292</v>
+        <v>636</v>
       </c>
     </row>
     <row r="161" spans="2:2">
       <c r="B161" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="162" spans="2:2">
       <c r="B162" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="163" spans="2:2">
       <c r="B163" t="s">
-        <v>638</v>
+        <v>296</v>
       </c>
     </row>
     <row r="164" spans="2:2">
       <c r="B164" t="s">
-        <v>298</v>
+        <v>638</v>
       </c>
     </row>
     <row r="165" spans="2:2">
       <c r="B165" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="166" spans="2:2">
       <c r="B166" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="167" spans="2:2">
       <c r="B167" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="168" spans="2:2">
       <c r="B168" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="169" spans="2:2">
       <c r="B169" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="170" spans="2:2">
       <c r="B170" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="171" spans="2:2">
       <c r="B171" t="s">
-        <v>641</v>
+        <v>310</v>
       </c>
     </row>
     <row r="172" spans="2:2">
       <c r="B172" t="s">
-        <v>312</v>
+        <v>641</v>
       </c>
     </row>
     <row r="173" spans="2:2">
       <c r="B173" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="174" spans="2:2">
       <c r="B174" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="175" spans="2:2">
       <c r="B175" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="176" spans="2:2">
       <c r="B176" t="s">
-        <v>735</v>
+        <v>318</v>
       </c>
     </row>
     <row r="177" spans="2:2">
       <c r="B177" t="s">
-        <v>320</v>
+        <v>746</v>
       </c>
     </row>
     <row r="178" spans="2:2">
       <c r="B178" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="179" spans="2:2">
       <c r="B179" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="180" spans="2:2">
       <c r="B180" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="181" spans="2:2">
       <c r="B181" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="182" spans="2:2">
       <c r="B182" t="s">
-        <v>644</v>
+        <v>328</v>
       </c>
     </row>
     <row r="183" spans="2:2">
       <c r="B183" t="s">
-        <v>330</v>
+        <v>644</v>
       </c>
     </row>
     <row r="184" spans="2:2">
       <c r="B184" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="185" spans="2:2">
       <c r="B185" t="s">
-        <v>646</v>
+        <v>332</v>
       </c>
     </row>
     <row r="186" spans="2:2">
       <c r="B186" t="s">
-        <v>333</v>
+        <v>646</v>
       </c>
     </row>
     <row r="187" spans="2:2">
       <c r="B187" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="188" spans="2:2">
       <c r="B188" t="s">
-        <v>699</v>
+        <v>335</v>
       </c>
     </row>
     <row r="189" spans="2:2">
       <c r="B189" t="s">
-        <v>649</v>
+        <v>702</v>
       </c>
     </row>
     <row r="190" spans="2:2">
       <c r="B190" t="s">
-        <v>337</v>
+        <v>649</v>
       </c>
     </row>
     <row r="191" spans="2:2">
       <c r="B191" t="s">
-        <v>652</v>
+        <v>337</v>
       </c>
     </row>
     <row r="192" spans="2:2">
       <c r="B192" t="s">
-        <v>338</v>
+        <v>652</v>
       </c>
     </row>
     <row r="193" spans="2:2">
       <c r="B193" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="195" spans="2:2">
       <c r="B195" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="196" spans="2:2">
       <c r="B196" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="197" spans="2:2">
       <c r="B197" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="198" spans="2:2">
       <c r="B198" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="199" spans="2:2">
       <c r="B199" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="200" spans="2:2">
       <c r="B200" t="s">
-        <v>355</v>
+        <v>705</v>
       </c>
     </row>
     <row r="201" spans="2:2">
       <c r="B201" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
     </row>
     <row r="202" spans="2:2">
       <c r="B202" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
     </row>
     <row r="203" spans="2:2">
       <c r="B203" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
     </row>
     <row r="204" spans="2:2">
       <c r="B204" t="s">
-        <v>654</v>
+        <v>359</v>
       </c>
     </row>
     <row r="205" spans="2:2">
       <c r="B205" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="206" spans="2:2">
       <c r="B206" t="s">
-        <v>365</v>
+        <v>654</v>
       </c>
     </row>
     <row r="207" spans="2:2">
       <c r="B207" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
     </row>
     <row r="208" spans="2:2">
       <c r="B208" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
     </row>
     <row r="209" spans="2:2">
       <c r="B209" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
     </row>
     <row r="210" spans="2:2">
       <c r="B210" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
     </row>
     <row r="211" spans="2:2">
       <c r="B211" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
     </row>
     <row r="212" spans="2:2">
       <c r="B212" t="s">
-        <v>657</v>
+        <v>373</v>
       </c>
     </row>
     <row r="213" spans="2:2">
       <c r="B213" t="s">
-        <v>660</v>
+        <v>374</v>
       </c>
     </row>
     <row r="214" spans="2:2">
       <c r="B214" t="s">
-        <v>377</v>
+        <v>657</v>
       </c>
     </row>
     <row r="215" spans="2:2">
       <c r="B215" t="s">
-        <v>379</v>
+        <v>660</v>
       </c>
     </row>
     <row r="216" spans="2:2">
       <c r="B216" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="217" spans="2:2">
       <c r="B217" t="s">
-        <v>726</v>
+        <v>379</v>
       </c>
     </row>
     <row r="218" spans="2:2">
       <c r="B218" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="219" spans="2:2">
       <c r="B219" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
     </row>
     <row r="220" spans="2:2">
       <c r="B220" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="221" spans="2:2">
       <c r="B221" t="s">
-        <v>386</v>
+        <v>750</v>
       </c>
     </row>
     <row r="222" spans="2:2">
       <c r="B222" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
     </row>
     <row r="223" spans="2:2">
       <c r="B223" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
     </row>
     <row r="224" spans="2:2">
       <c r="B224" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
     </row>
     <row r="225" spans="2:2">
       <c r="B225" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
     </row>
     <row r="226" spans="2:2">
       <c r="B226" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="227" spans="2:2">
       <c r="B227" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
     </row>
     <row r="228" spans="2:2">
       <c r="B228" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
     </row>
     <row r="229" spans="2:2">
       <c r="B229" t="s">
-        <v>663</v>
+        <v>398</v>
       </c>
     </row>
     <row r="230" spans="2:2">
       <c r="B230" t="s">
-        <v>666</v>
+        <v>400</v>
       </c>
     </row>
     <row r="231" spans="2:2">
       <c r="B231" t="s">
-        <v>402</v>
+        <v>663</v>
       </c>
     </row>
     <row r="232" spans="2:2">
       <c r="B232" t="s">
-        <v>404</v>
+        <v>666</v>
       </c>
     </row>
     <row r="233" spans="2:2">
       <c r="B233" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
     </row>
     <row r="234" spans="2:2">
       <c r="B234" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
     </row>
     <row r="235" spans="2:2">
       <c r="B235" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
     </row>
     <row r="236" spans="2:2">
       <c r="B236" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
     </row>
     <row r="237" spans="2:2">
       <c r="B237" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
     </row>
     <row r="238" spans="2:2">
       <c r="B238" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
     </row>
     <row r="239" spans="2:2">
       <c r="B239" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
     </row>
     <row r="240" spans="2:2">
       <c r="B240" t="s">
-        <v>669</v>
+        <v>417</v>
       </c>
     </row>
     <row r="241" spans="2:2">
       <c r="B241" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="242" spans="2:2">
       <c r="B242" t="s">
-        <v>423</v>
+        <v>707</v>
       </c>
     </row>
     <row r="243" spans="2:2">
       <c r="B243" t="s">
-        <v>425</v>
+        <v>669</v>
       </c>
     </row>
     <row r="244" spans="2:2">
       <c r="B244" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
     </row>
     <row r="245" spans="2:2">
       <c r="B245" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
     </row>
     <row r="246" spans="2:2">
       <c r="B246" t="s">
-        <v>671</v>
+        <v>425</v>
       </c>
     </row>
     <row r="247" spans="2:2">
       <c r="B247" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="248" spans="2:2">
       <c r="B248" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
     </row>
     <row r="249" spans="2:2">
       <c r="B249" t="s">
-        <v>435</v>
+        <v>671</v>
       </c>
     </row>
     <row r="250" spans="2:2">
       <c r="B250" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
     </row>
     <row r="251" spans="2:2">
       <c r="B251" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
     </row>
     <row r="252" spans="2:2">
       <c r="B252" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
     </row>
     <row r="253" spans="2:2">
       <c r="B253" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
     </row>
     <row r="254" spans="2:2">
       <c r="B254" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
     </row>
     <row r="255" spans="2:2">
       <c r="B255" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
     </row>
     <row r="256" spans="2:2">
       <c r="B256" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
     </row>
     <row r="257" spans="2:2">
       <c r="B257" t="s">
-        <v>673</v>
+        <v>446</v>
       </c>
     </row>
     <row r="258" spans="2:2">
       <c r="B258" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
     </row>
     <row r="259" spans="2:2">
       <c r="B259" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="260" spans="2:2">
       <c r="B260" t="s">
-        <v>456</v>
+        <v>673</v>
       </c>
     </row>
     <row r="261" spans="2:2">
       <c r="B261" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
     </row>
     <row r="262" spans="2:2">
       <c r="B262" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
     </row>
     <row r="263" spans="2:2">
       <c r="B263" t="s">
-        <v>676</v>
+        <v>456</v>
       </c>
     </row>
     <row r="264" spans="2:2">
       <c r="B264" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
     </row>
     <row r="265" spans="2:2">
       <c r="B265" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
     </row>
     <row r="266" spans="2:2">
       <c r="B266" t="s">
-        <v>465</v>
+        <v>676</v>
       </c>
     </row>
     <row r="267" spans="2:2">
       <c r="B267" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
     </row>
     <row r="268" spans="2:2">
       <c r="B268" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
     </row>
     <row r="269" spans="2:2">
       <c r="B269" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
     </row>
     <row r="270" spans="2:2">
       <c r="B270" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
     </row>
     <row r="271" spans="2:2">
       <c r="B271" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
     </row>
     <row r="272" spans="2:2">
       <c r="B272" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
     </row>
     <row r="273" spans="2:2">
       <c r="B273" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
     </row>
     <row r="274" spans="2:2">
       <c r="B274" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
     </row>
     <row r="275" spans="2:2">
       <c r="B275" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
     </row>
     <row r="276" spans="2:2">
       <c r="B276" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
     </row>
     <row r="277" spans="2:2">
       <c r="B277" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
     </row>
     <row r="278" spans="2:2">
       <c r="B278" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
     </row>
     <row r="279" spans="2:2">
       <c r="B279" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
     </row>
     <row r="280" spans="2:2">
       <c r="B280" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
     </row>
     <row r="281" spans="2:2">
       <c r="B281" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
     </row>
     <row r="282" spans="2:2">
       <c r="B282" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
     </row>
     <row r="283" spans="2:2">
       <c r="B283" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
     </row>
     <row r="284" spans="2:2">
       <c r="B284" t="s">
-        <v>503</v>
+        <v>495</v>
       </c>
     </row>
     <row r="285" spans="2:2">
       <c r="B285" t="s">
-        <v>743</v>
+        <v>498</v>
       </c>
     </row>
     <row r="286" spans="2:2">
       <c r="B286" t="s">
-        <v>747</v>
+        <v>500</v>
       </c>
     </row>
     <row r="287" spans="2:2">
       <c r="B287" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="288" spans="2:2">
       <c r="B288" t="s">
-        <v>507</v>
+        <v>754</v>
       </c>
     </row>
     <row r="289" spans="2:2">
       <c r="B289" t="s">
-        <v>749</v>
+        <v>758</v>
       </c>
     </row>
     <row r="290" spans="2:2">
       <c r="B290" t="s">
-        <v>679</v>
+        <v>505</v>
       </c>
     </row>
     <row r="291" spans="2:2">
       <c r="B291" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="292" spans="2:2">
       <c r="B292" t="s">
-        <v>511</v>
+        <v>760</v>
       </c>
     </row>
     <row r="293" spans="2:2">
       <c r="B293" t="s">
-        <v>513</v>
+        <v>679</v>
       </c>
     </row>
     <row r="294" spans="2:2">
       <c r="B294" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
     </row>
     <row r="295" spans="2:2">
       <c r="B295" t="s">
-        <v>702</v>
+        <v>511</v>
       </c>
     </row>
     <row r="296" spans="2:2">
       <c r="B296" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
     </row>
     <row r="297" spans="2:2">
       <c r="B297" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
     </row>
     <row r="298" spans="2:2">
       <c r="B298" t="s">
-        <v>521</v>
+        <v>709</v>
       </c>
     </row>
     <row r="299" spans="2:2">
       <c r="B299" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
     </row>
     <row r="300" spans="2:2">
       <c r="B300" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
     </row>
     <row r="301" spans="2:2">
       <c r="B301" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
     </row>
     <row r="302" spans="2:2">
       <c r="B302" t="s">
-        <v>529</v>
+        <v>711</v>
       </c>
     </row>
     <row r="303" spans="2:2">
       <c r="B303" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
     </row>
     <row r="304" spans="2:2">
       <c r="B304" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
     </row>
     <row r="305" spans="2:2">
       <c r="B305" t="s">
-        <v>535</v>
+        <v>527</v>
       </c>
     </row>
     <row r="306" spans="2:2">
       <c r="B306" t="s">
-        <v>537</v>
+        <v>529</v>
       </c>
     </row>
     <row r="307" spans="2:2">
       <c r="B307" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
     </row>
     <row r="308" spans="2:2">
       <c r="B308" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
     </row>
     <row r="309" spans="2:2">
       <c r="B309" t="s">
-        <v>543</v>
+        <v>713</v>
       </c>
     </row>
     <row r="310" spans="2:2">
       <c r="B310" t="s">
-        <v>545</v>
+        <v>535</v>
       </c>
     </row>
     <row r="311" spans="2:2">
       <c r="B311" t="s">
-        <v>547</v>
+        <v>537</v>
       </c>
     </row>
     <row r="312" spans="2:2">
       <c r="B312" t="s">
-        <v>549</v>
+        <v>539</v>
       </c>
     </row>
     <row r="313" spans="2:2">
       <c r="B313" t="s">
-        <v>551</v>
+        <v>541</v>
       </c>
     </row>
     <row r="314" spans="2:2">
       <c r="B314" t="s">
-        <v>553</v>
+        <v>543</v>
       </c>
     </row>
     <row r="315" spans="2:2">
       <c r="B315" t="s">
-        <v>555</v>
+        <v>545</v>
       </c>
     </row>
     <row r="316" spans="2:2">
       <c r="B316" t="s">
-        <v>557</v>
+        <v>547</v>
       </c>
     </row>
     <row r="317" spans="2:2">
       <c r="B317" t="s">
-        <v>682</v>
+        <v>549</v>
       </c>
     </row>
     <row r="318" spans="2:2">
       <c r="B318" t="s">
-        <v>684</v>
+        <v>551</v>
       </c>
     </row>
     <row r="319" spans="2:2">
       <c r="B319" t="s">
-        <v>687</v>
+        <v>553</v>
       </c>
     </row>
     <row r="320" spans="2:2">
       <c r="B320" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
     </row>
     <row r="321" spans="2:2">
       <c r="B321" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
     </row>
     <row r="322" spans="2:2">
       <c r="B322" t="s">
-        <v>563</v>
+        <v>682</v>
       </c>
     </row>
     <row r="323" spans="2:2">
       <c r="B323" t="s">
-        <v>565</v>
+        <v>684</v>
       </c>
     </row>
     <row r="324" spans="2:2">
       <c r="B324" t="s">
-        <v>567</v>
+        <v>687</v>
       </c>
     </row>
     <row r="325" spans="2:2">
       <c r="B325" t="s">
-        <v>569</v>
+        <v>559</v>
       </c>
     </row>
     <row r="326" spans="2:2">
       <c r="B326" t="s">
-        <v>571</v>
+        <v>561</v>
       </c>
     </row>
     <row r="327" spans="2:2">
       <c r="B327" t="s">
-        <v>573</v>
+        <v>563</v>
       </c>
     </row>
     <row r="328" spans="2:2">
       <c r="B328" t="s">
-        <v>575</v>
+        <v>565</v>
       </c>
     </row>
     <row r="329" spans="2:2">
       <c r="B329" t="s">
-        <v>729</v>
+        <v>567</v>
       </c>
     </row>
     <row r="330" spans="2:2">
       <c r="B330" t="s">
-        <v>577</v>
+        <v>569</v>
       </c>
     </row>
     <row r="331" spans="2:2">
       <c r="B331" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
     </row>
     <row r="332" spans="2:2">
       <c r="B332" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
     </row>
     <row r="333" spans="2:2">
       <c r="B333" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
     </row>
     <row r="334" spans="2:2">
       <c r="B334" t="s">
-        <v>585</v>
+        <v>740</v>
       </c>
     </row>
     <row r="335" spans="2:2">
       <c r="B335" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
     </row>
     <row r="336" spans="2:2">
       <c r="B336" t="s">
-        <v>589</v>
+        <v>579</v>
       </c>
     </row>
     <row r="337" spans="1:2">
       <c r="B337" t="s">
-        <v>591</v>
+        <v>581</v>
       </c>
     </row>
     <row r="338" spans="1:2">
       <c r="B338" t="s">
-        <v>593</v>
+        <v>583</v>
       </c>
     </row>
     <row r="339" spans="1:2">
       <c r="B339" t="s">
-        <v>596</v>
+        <v>585</v>
       </c>
     </row>
     <row r="340" spans="1:2">
       <c r="B340" t="s">
-        <v>598</v>
+        <v>587</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2">
+      <c r="B341" t="s">
+        <v>589</v>
       </c>
     </row>
     <row r="342" spans="1:2">
-      <c r="A342" t="s">
-        <v>755</v>
-      </c>
       <c r="B342" t="s">
-        <v>696</v>
+        <v>591</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2">
+      <c r="B343" t="s">
+        <v>593</v>
       </c>
     </row>
     <row r="344" spans="1:2">
-      <c r="A344" t="s">
-        <v>756</v>
-      </c>
       <c r="B344" t="s">
-        <v>616</v>
+        <v>596</v>
       </c>
     </row>
     <row r="345" spans="1:2">
       <c r="B345" t="s">
-        <v>676</v>
+        <v>598</v>
       </c>
     </row>
     <row r="347" spans="1:2">
       <c r="A347" t="s">
-        <v>757</v>
+        <v>766</v>
       </c>
       <c r="B347" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="348" spans="1:2">
-      <c r="B348" t="s">
-        <v>722</v>
+        <v>696</v>
       </c>
     </row>
     <row r="349" spans="1:2">
+      <c r="A349" t="s">
+        <v>767</v>
+      </c>
       <c r="B349" t="s">
-        <v>633</v>
+        <v>616</v>
       </c>
     </row>
     <row r="350" spans="1:2">
       <c r="B350" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2">
+      <c r="A352" t="s">
+        <v>768</v>
+      </c>
+      <c r="B352" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="353" spans="2:2">
+      <c r="B353" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="354" spans="2:2">
+      <c r="B354" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="355" spans="2:2">
+      <c r="B355" t="s">
         <v>644</v>
       </c>
     </row>
@@ -10053,7 +10111,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="110.7109375" customWidth="1"/>
@@ -10139,7 +10197,7 @@
         <v>699</v>
       </c>
       <c r="B6">
-        <v>2.66</v>
+        <v>1.88</v>
       </c>
       <c r="C6" t="s">
         <v>700</v>
@@ -10156,7 +10214,7 @@
         <v>702</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>2.66</v>
       </c>
       <c r="C7" t="s">
         <v>703</v>
@@ -10165,7 +10223,92 @@
         <v>8</v>
       </c>
       <c r="E7" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>705</v>
+      </c>
+      <c r="B8">
+        <v>1.76</v>
+      </c>
+      <c r="C8" t="s">
+        <v>706</v>
+      </c>
+      <c r="D8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>707</v>
+      </c>
+      <c r="B9">
+        <v>1.84</v>
+      </c>
+      <c r="C9" t="s">
+        <v>708</v>
+      </c>
+      <c r="D9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>709</v>
+      </c>
+      <c r="B10">
+        <v>2</v>
+      </c>
+      <c r="C10" t="s">
+        <v>710</v>
+      </c>
+      <c r="D10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" t="s">
         <v>643</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>711</v>
+      </c>
+      <c r="B11">
+        <v>1.92</v>
+      </c>
+      <c r="C11" t="s">
+        <v>712</v>
+      </c>
+      <c r="D11" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>713</v>
+      </c>
+      <c r="B12">
+        <v>1.77</v>
+      </c>
+      <c r="C12" t="s">
+        <v>714</v>
+      </c>
+      <c r="D12" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" t="s">
+        <v>701</v>
       </c>
     </row>
   </sheetData>
@@ -10185,7 +10328,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>704</v>
+        <v>715</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -10207,19 +10350,19 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="B3">
         <v>2.2</v>
       </c>
       <c r="C3" t="s">
-        <v>706</v>
+        <v>717</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>707</v>
+        <v>718</v>
       </c>
     </row>
   </sheetData>
@@ -10239,7 +10382,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>708</v>
+        <v>719</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -10261,19 +10404,19 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>709</v>
+        <v>720</v>
       </c>
       <c r="B3">
         <v>1.32</v>
       </c>
       <c r="C3" t="s">
-        <v>710</v>
+        <v>721</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>711</v>
+        <v>722</v>
       </c>
     </row>
   </sheetData>
@@ -10293,7 +10436,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>712</v>
+        <v>723</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -10315,19 +10458,19 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>713</v>
+        <v>724</v>
       </c>
       <c r="B3">
         <v>2.45</v>
       </c>
       <c r="C3" t="s">
-        <v>714</v>
+        <v>725</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>715</v>
+        <v>726</v>
       </c>
     </row>
   </sheetData>
@@ -10347,7 +10490,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>716</v>
+        <v>727</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -10369,47 +10512,47 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>717</v>
+        <v>728</v>
       </c>
       <c r="B3">
         <v>1.9</v>
       </c>
       <c r="C3" t="s">
-        <v>718</v>
+        <v>729</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>719</v>
+        <v>730</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>720</v>
+        <v>731</v>
       </c>
       <c r="B4">
         <v>2.11</v>
       </c>
       <c r="C4" t="s">
-        <v>721</v>
+        <v>732</v>
       </c>
       <c r="D4" t="s">
         <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>719</v>
+        <v>730</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>722</v>
+        <v>733</v>
       </c>
       <c r="B5">
         <v>2.7</v>
       </c>
       <c r="C5" t="s">
-        <v>723</v>
+        <v>734</v>
       </c>
       <c r="D5" t="s">
         <v>8</v>
@@ -10420,13 +10563,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>724</v>
+        <v>735</v>
       </c>
       <c r="B6">
         <v>2.58</v>
       </c>
       <c r="C6" t="s">
-        <v>725</v>
+        <v>736</v>
       </c>
       <c r="D6" t="s">
         <v>8</v>
@@ -10437,30 +10580,30 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>726</v>
+        <v>737</v>
       </c>
       <c r="B7">
         <v>1.93</v>
       </c>
       <c r="C7" t="s">
-        <v>727</v>
+        <v>738</v>
       </c>
       <c r="D7" t="s">
         <v>8</v>
       </c>
       <c r="E7" t="s">
-        <v>728</v>
+        <v>739</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>729</v>
+        <v>740</v>
       </c>
       <c r="B8">
         <v>2.05</v>
       </c>
       <c r="C8" t="s">
-        <v>730</v>
+        <v>741</v>
       </c>
       <c r="D8" t="s">
         <v>8</v>
@@ -10486,7 +10629,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>731</v>
+        <v>742</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -10508,13 +10651,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>732</v>
+        <v>743</v>
       </c>
       <c r="B3">
         <v>0.93</v>
       </c>
       <c r="C3" t="s">
-        <v>733</v>
+        <v>744</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
@@ -10540,7 +10683,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>734</v>
+        <v>745</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -10562,19 +10705,19 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>735</v>
+        <v>746</v>
       </c>
       <c r="B3">
         <v>2.17</v>
       </c>
       <c r="C3" t="s">
-        <v>736</v>
+        <v>747</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>737</v>
+        <v>748</v>
       </c>
     </row>
   </sheetData>

--- a/pdb/nsp3/SARS-CoV-2/domains_and_infos_of_nsp3.xlsx
+++ b/pdb/nsp3/SARS-CoV-2/domains_and_infos_of_nsp3.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1801" uniqueCount="769">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1806" uniqueCount="772">
   <si>
     <t>nsp3_Macro1_</t>
   </si>
@@ -2123,6 +2123,15 @@
   </si>
   <si>
     <t>2020-04-28</t>
+  </si>
+  <si>
+    <t>7qcg</t>
+  </si>
+  <si>
+    <t>STRUCTURE OF SARS-COV-2 PAPAIN-LIKE PROTEASE BOUND TO N-(2- PYRROLIDYL)-3,4,5-TRIHYDROXYBENZOYLHYDRAZONE</t>
+  </si>
+  <si>
+    <t>2021-11-23</t>
   </si>
   <si>
     <t>7qch</t>
@@ -7573,7 +7582,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -7595,19 +7604,19 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="B3">
         <v>2.72</v>
       </c>
       <c r="C3" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
     </row>
   </sheetData>
@@ -7627,7 +7636,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -7649,19 +7658,19 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="B3">
         <v>2.68</v>
       </c>
       <c r="C3" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
     </row>
   </sheetData>
@@ -7681,7 +7690,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -7703,13 +7712,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="B3">
         <v>3.21</v>
       </c>
       <c r="C3" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
@@ -7720,19 +7729,19 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B4">
         <v>2.73</v>
       </c>
       <c r="C4" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="D4" t="s">
         <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
     </row>
   </sheetData>
@@ -7742,7 +7751,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B355"/>
+  <dimension ref="A1:B356"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.7109375" customWidth="1"/>
@@ -7750,12 +7759,12 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
@@ -7763,7 +7772,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="B3" t="s">
         <v>6</v>
@@ -7926,7 +7935,7 @@
     </row>
     <row r="35" spans="2:2">
       <c r="B35" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
     </row>
     <row r="36" spans="2:2">
@@ -7951,7 +7960,7 @@
     </row>
     <row r="40" spans="2:2">
       <c r="B40" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
     </row>
     <row r="41" spans="2:2">
@@ -7976,7 +7985,7 @@
     </row>
     <row r="45" spans="2:2">
       <c r="B45" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
     </row>
     <row r="46" spans="2:2">
@@ -8026,7 +8035,7 @@
     </row>
     <row r="55" spans="2:2">
       <c r="B55" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
     </row>
     <row r="56" spans="2:2">
@@ -8241,1285 +8250,1290 @@
     </row>
     <row r="98" spans="2:2">
       <c r="B98" t="s">
-        <v>177</v>
+        <v>699</v>
       </c>
     </row>
     <row r="99" spans="2:2">
       <c r="B99" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="100" spans="2:2">
       <c r="B100" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="101" spans="2:2">
       <c r="B101" t="s">
-        <v>731</v>
+        <v>181</v>
       </c>
     </row>
     <row r="102" spans="2:2">
       <c r="B102" t="s">
-        <v>183</v>
+        <v>734</v>
       </c>
     </row>
     <row r="103" spans="2:2">
       <c r="B103" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="104" spans="2:2">
       <c r="B104" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="105" spans="2:2">
       <c r="B105" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="106" spans="2:2">
       <c r="B106" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="107" spans="2:2">
       <c r="B107" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="108" spans="2:2">
       <c r="B108" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="109" spans="2:2">
       <c r="B109" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="110" spans="2:2">
       <c r="B110" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="111" spans="2:2">
       <c r="B111" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="112" spans="2:2">
       <c r="B112" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="113" spans="2:2">
       <c r="B113" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="114" spans="2:2">
       <c r="B114" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="115" spans="2:2">
       <c r="B115" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="116" spans="2:2">
       <c r="B116" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="117" spans="2:2">
       <c r="B117" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="118" spans="2:2">
       <c r="B118" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="119" spans="2:2">
       <c r="B119" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="120" spans="2:2">
       <c r="B120" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="121" spans="2:2">
       <c r="B121" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="122" spans="2:2">
       <c r="B122" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="123" spans="2:2">
       <c r="B123" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="124" spans="2:2">
       <c r="B124" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="125" spans="2:2">
       <c r="B125" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="126" spans="2:2">
       <c r="B126" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="127" spans="2:2">
       <c r="B127" t="s">
-        <v>743</v>
+        <v>234</v>
       </c>
     </row>
     <row r="128" spans="2:2">
       <c r="B128" t="s">
-        <v>236</v>
+        <v>746</v>
       </c>
     </row>
     <row r="129" spans="2:2">
       <c r="B129" t="s">
-        <v>733</v>
+        <v>236</v>
       </c>
     </row>
     <row r="130" spans="2:2">
       <c r="B130" t="s">
-        <v>238</v>
+        <v>736</v>
       </c>
     </row>
     <row r="131" spans="2:2">
       <c r="B131" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="132" spans="2:2">
       <c r="B132" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="133" spans="2:2">
       <c r="B133" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="134" spans="2:2">
       <c r="B134" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="135" spans="2:2">
       <c r="B135" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="136" spans="2:2">
       <c r="B136" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="137" spans="2:2">
       <c r="B137" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="138" spans="2:2">
       <c r="B138" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="139" spans="2:2">
       <c r="B139" t="s">
-        <v>628</v>
+        <v>255</v>
       </c>
     </row>
     <row r="140" spans="2:2">
       <c r="B140" t="s">
-        <v>257</v>
+        <v>628</v>
       </c>
     </row>
     <row r="141" spans="2:2">
       <c r="B141" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="142" spans="2:2">
       <c r="B142" t="s">
-        <v>630</v>
+        <v>259</v>
       </c>
     </row>
     <row r="143" spans="2:2">
       <c r="B143" t="s">
-        <v>261</v>
+        <v>630</v>
       </c>
     </row>
     <row r="144" spans="2:2">
       <c r="B144" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="145" spans="2:2">
       <c r="B145" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="146" spans="2:2">
       <c r="B146" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="147" spans="2:2">
       <c r="B147" t="s">
-        <v>633</v>
+        <v>269</v>
       </c>
     </row>
     <row r="148" spans="2:2">
       <c r="B148" t="s">
-        <v>271</v>
+        <v>633</v>
       </c>
     </row>
     <row r="149" spans="2:2">
       <c r="B149" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="150" spans="2:2">
       <c r="B150" t="s">
-        <v>735</v>
+        <v>273</v>
       </c>
     </row>
     <row r="151" spans="2:2">
       <c r="B151" t="s">
-        <v>275</v>
+        <v>738</v>
       </c>
     </row>
     <row r="152" spans="2:2">
       <c r="B152" t="s">
-        <v>699</v>
+        <v>275</v>
       </c>
     </row>
     <row r="153" spans="2:2">
       <c r="B153" t="s">
-        <v>277</v>
+        <v>702</v>
       </c>
     </row>
     <row r="154" spans="2:2">
       <c r="B154" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="155" spans="2:2">
       <c r="B155" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="156" spans="2:2">
       <c r="B156" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="157" spans="2:2">
       <c r="B157" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="158" spans="2:2">
       <c r="B158" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
     <row r="159" spans="2:2">
       <c r="B159" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="160" spans="2:2">
       <c r="B160" t="s">
-        <v>636</v>
+        <v>290</v>
       </c>
     </row>
     <row r="161" spans="2:2">
       <c r="B161" t="s">
-        <v>292</v>
+        <v>636</v>
       </c>
     </row>
     <row r="162" spans="2:2">
       <c r="B162" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="163" spans="2:2">
       <c r="B163" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="164" spans="2:2">
       <c r="B164" t="s">
-        <v>638</v>
+        <v>296</v>
       </c>
     </row>
     <row r="165" spans="2:2">
       <c r="B165" t="s">
-        <v>298</v>
+        <v>638</v>
       </c>
     </row>
     <row r="166" spans="2:2">
       <c r="B166" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="167" spans="2:2">
       <c r="B167" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="168" spans="2:2">
       <c r="B168" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="169" spans="2:2">
       <c r="B169" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="170" spans="2:2">
       <c r="B170" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="171" spans="2:2">
       <c r="B171" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="172" spans="2:2">
       <c r="B172" t="s">
-        <v>641</v>
+        <v>310</v>
       </c>
     </row>
     <row r="173" spans="2:2">
       <c r="B173" t="s">
-        <v>312</v>
+        <v>641</v>
       </c>
     </row>
     <row r="174" spans="2:2">
       <c r="B174" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="175" spans="2:2">
       <c r="B175" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="176" spans="2:2">
       <c r="B176" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="177" spans="2:2">
       <c r="B177" t="s">
-        <v>746</v>
+        <v>318</v>
       </c>
     </row>
     <row r="178" spans="2:2">
       <c r="B178" t="s">
-        <v>320</v>
+        <v>749</v>
       </c>
     </row>
     <row r="179" spans="2:2">
       <c r="B179" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="180" spans="2:2">
       <c r="B180" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="181" spans="2:2">
       <c r="B181" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="182" spans="2:2">
       <c r="B182" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="183" spans="2:2">
       <c r="B183" t="s">
-        <v>644</v>
+        <v>328</v>
       </c>
     </row>
     <row r="184" spans="2:2">
       <c r="B184" t="s">
-        <v>330</v>
+        <v>644</v>
       </c>
     </row>
     <row r="185" spans="2:2">
       <c r="B185" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="186" spans="2:2">
       <c r="B186" t="s">
-        <v>646</v>
+        <v>332</v>
       </c>
     </row>
     <row r="187" spans="2:2">
       <c r="B187" t="s">
-        <v>333</v>
+        <v>646</v>
       </c>
     </row>
     <row r="188" spans="2:2">
       <c r="B188" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="189" spans="2:2">
       <c r="B189" t="s">
-        <v>702</v>
+        <v>335</v>
       </c>
     </row>
     <row r="190" spans="2:2">
       <c r="B190" t="s">
-        <v>649</v>
+        <v>705</v>
       </c>
     </row>
     <row r="191" spans="2:2">
       <c r="B191" t="s">
-        <v>337</v>
+        <v>649</v>
       </c>
     </row>
     <row r="192" spans="2:2">
       <c r="B192" t="s">
-        <v>652</v>
+        <v>337</v>
       </c>
     </row>
     <row r="193" spans="2:2">
       <c r="B193" t="s">
-        <v>338</v>
+        <v>652</v>
       </c>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="195" spans="2:2">
       <c r="B195" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="196" spans="2:2">
       <c r="B196" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="197" spans="2:2">
       <c r="B197" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="198" spans="2:2">
       <c r="B198" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="199" spans="2:2">
       <c r="B199" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="200" spans="2:2">
       <c r="B200" t="s">
-        <v>705</v>
+        <v>351</v>
       </c>
     </row>
     <row r="201" spans="2:2">
       <c r="B201" t="s">
-        <v>353</v>
+        <v>708</v>
       </c>
     </row>
     <row r="202" spans="2:2">
       <c r="B202" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="203" spans="2:2">
       <c r="B203" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="204" spans="2:2">
       <c r="B204" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="205" spans="2:2">
       <c r="B205" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="206" spans="2:2">
       <c r="B206" t="s">
-        <v>654</v>
+        <v>361</v>
       </c>
     </row>
     <row r="207" spans="2:2">
       <c r="B207" t="s">
-        <v>363</v>
+        <v>654</v>
       </c>
     </row>
     <row r="208" spans="2:2">
       <c r="B208" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="209" spans="2:2">
       <c r="B209" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="210" spans="2:2">
       <c r="B210" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="211" spans="2:2">
       <c r="B211" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="212" spans="2:2">
       <c r="B212" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="213" spans="2:2">
       <c r="B213" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="214" spans="2:2">
       <c r="B214" t="s">
-        <v>657</v>
+        <v>374</v>
       </c>
     </row>
     <row r="215" spans="2:2">
       <c r="B215" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
     </row>
     <row r="216" spans="2:2">
       <c r="B216" t="s">
-        <v>377</v>
+        <v>660</v>
       </c>
     </row>
     <row r="217" spans="2:2">
       <c r="B217" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="218" spans="2:2">
       <c r="B218" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="219" spans="2:2">
       <c r="B219" t="s">
-        <v>737</v>
+        <v>380</v>
       </c>
     </row>
     <row r="220" spans="2:2">
       <c r="B220" t="s">
-        <v>382</v>
+        <v>740</v>
       </c>
     </row>
     <row r="221" spans="2:2">
       <c r="B221" t="s">
-        <v>750</v>
+        <v>382</v>
       </c>
     </row>
     <row r="222" spans="2:2">
       <c r="B222" t="s">
-        <v>384</v>
+        <v>753</v>
       </c>
     </row>
     <row r="223" spans="2:2">
       <c r="B223" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="224" spans="2:2">
       <c r="B224" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="225" spans="2:2">
       <c r="B225" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="226" spans="2:2">
       <c r="B226" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="227" spans="2:2">
       <c r="B227" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="228" spans="2:2">
       <c r="B228" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="229" spans="2:2">
       <c r="B229" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="230" spans="2:2">
       <c r="B230" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="231" spans="2:2">
       <c r="B231" t="s">
-        <v>663</v>
+        <v>400</v>
       </c>
     </row>
     <row r="232" spans="2:2">
       <c r="B232" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
     </row>
     <row r="233" spans="2:2">
       <c r="B233" t="s">
-        <v>402</v>
+        <v>666</v>
       </c>
     </row>
     <row r="234" spans="2:2">
       <c r="B234" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="235" spans="2:2">
       <c r="B235" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="236" spans="2:2">
       <c r="B236" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="237" spans="2:2">
       <c r="B237" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="238" spans="2:2">
       <c r="B238" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="239" spans="2:2">
       <c r="B239" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="240" spans="2:2">
       <c r="B240" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="241" spans="2:2">
       <c r="B241" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="242" spans="2:2">
       <c r="B242" t="s">
-        <v>707</v>
+        <v>420</v>
       </c>
     </row>
     <row r="243" spans="2:2">
       <c r="B243" t="s">
-        <v>669</v>
+        <v>710</v>
       </c>
     </row>
     <row r="244" spans="2:2">
       <c r="B244" t="s">
-        <v>421</v>
+        <v>669</v>
       </c>
     </row>
     <row r="245" spans="2:2">
       <c r="B245" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="246" spans="2:2">
       <c r="B246" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="247" spans="2:2">
       <c r="B247" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="248" spans="2:2">
       <c r="B248" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="249" spans="2:2">
       <c r="B249" t="s">
-        <v>671</v>
+        <v>429</v>
       </c>
     </row>
     <row r="250" spans="2:2">
       <c r="B250" t="s">
-        <v>431</v>
+        <v>671</v>
       </c>
     </row>
     <row r="251" spans="2:2">
       <c r="B251" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="252" spans="2:2">
       <c r="B252" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="253" spans="2:2">
       <c r="B253" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="254" spans="2:2">
       <c r="B254" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="255" spans="2:2">
       <c r="B255" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="256" spans="2:2">
       <c r="B256" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
     </row>
     <row r="257" spans="2:2">
       <c r="B257" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="258" spans="2:2">
       <c r="B258" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="259" spans="2:2">
       <c r="B259" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="260" spans="2:2">
       <c r="B260" t="s">
-        <v>673</v>
+        <v>450</v>
       </c>
     </row>
     <row r="261" spans="2:2">
       <c r="B261" t="s">
-        <v>452</v>
+        <v>673</v>
       </c>
     </row>
     <row r="262" spans="2:2">
       <c r="B262" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="263" spans="2:2">
       <c r="B263" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="264" spans="2:2">
       <c r="B264" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="265" spans="2:2">
       <c r="B265" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="266" spans="2:2">
       <c r="B266" t="s">
-        <v>676</v>
+        <v>460</v>
       </c>
     </row>
     <row r="267" spans="2:2">
       <c r="B267" t="s">
-        <v>462</v>
+        <v>676</v>
       </c>
     </row>
     <row r="268" spans="2:2">
       <c r="B268" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="269" spans="2:2">
       <c r="B269" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="270" spans="2:2">
       <c r="B270" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="271" spans="2:2">
       <c r="B271" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="272" spans="2:2">
       <c r="B272" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="273" spans="2:2">
       <c r="B273" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="274" spans="2:2">
       <c r="B274" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="275" spans="2:2">
       <c r="B275" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="276" spans="2:2">
       <c r="B276" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="277" spans="2:2">
       <c r="B277" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="278" spans="2:2">
       <c r="B278" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="279" spans="2:2">
       <c r="B279" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="280" spans="2:2">
       <c r="B280" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="281" spans="2:2">
       <c r="B281" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="282" spans="2:2">
       <c r="B282" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="283" spans="2:2">
       <c r="B283" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="284" spans="2:2">
       <c r="B284" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="285" spans="2:2">
       <c r="B285" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
     </row>
     <row r="286" spans="2:2">
       <c r="B286" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="287" spans="2:2">
       <c r="B287" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
     </row>
     <row r="288" spans="2:2">
       <c r="B288" t="s">
-        <v>754</v>
+        <v>503</v>
       </c>
     </row>
     <row r="289" spans="2:2">
       <c r="B289" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="290" spans="2:2">
       <c r="B290" t="s">
-        <v>505</v>
+        <v>761</v>
       </c>
     </row>
     <row r="291" spans="2:2">
       <c r="B291" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="292" spans="2:2">
       <c r="B292" t="s">
-        <v>760</v>
+        <v>507</v>
       </c>
     </row>
     <row r="293" spans="2:2">
       <c r="B293" t="s">
-        <v>679</v>
+        <v>763</v>
       </c>
     </row>
     <row r="294" spans="2:2">
       <c r="B294" t="s">
-        <v>509</v>
+        <v>679</v>
       </c>
     </row>
     <row r="295" spans="2:2">
       <c r="B295" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="296" spans="2:2">
       <c r="B296" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="297" spans="2:2">
       <c r="B297" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="298" spans="2:2">
       <c r="B298" t="s">
-        <v>709</v>
+        <v>515</v>
       </c>
     </row>
     <row r="299" spans="2:2">
       <c r="B299" t="s">
-        <v>517</v>
+        <v>712</v>
       </c>
     </row>
     <row r="300" spans="2:2">
       <c r="B300" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="301" spans="2:2">
       <c r="B301" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="302" spans="2:2">
       <c r="B302" t="s">
-        <v>711</v>
+        <v>521</v>
       </c>
     </row>
     <row r="303" spans="2:2">
       <c r="B303" t="s">
-        <v>523</v>
+        <v>714</v>
       </c>
     </row>
     <row r="304" spans="2:2">
       <c r="B304" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="305" spans="2:2">
       <c r="B305" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="306" spans="2:2">
       <c r="B306" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="307" spans="2:2">
       <c r="B307" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="308" spans="2:2">
       <c r="B308" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="309" spans="2:2">
       <c r="B309" t="s">
-        <v>713</v>
+        <v>533</v>
       </c>
     </row>
     <row r="310" spans="2:2">
       <c r="B310" t="s">
-        <v>535</v>
+        <v>716</v>
       </c>
     </row>
     <row r="311" spans="2:2">
       <c r="B311" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="312" spans="2:2">
       <c r="B312" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="313" spans="2:2">
       <c r="B313" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="314" spans="2:2">
       <c r="B314" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="315" spans="2:2">
       <c r="B315" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="316" spans="2:2">
       <c r="B316" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="317" spans="2:2">
       <c r="B317" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="318" spans="2:2">
       <c r="B318" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="319" spans="2:2">
       <c r="B319" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="320" spans="2:2">
       <c r="B320" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="321" spans="2:2">
       <c r="B321" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="322" spans="2:2">
       <c r="B322" t="s">
-        <v>682</v>
+        <v>557</v>
       </c>
     </row>
     <row r="323" spans="2:2">
       <c r="B323" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="324" spans="2:2">
       <c r="B324" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
     </row>
     <row r="325" spans="2:2">
       <c r="B325" t="s">
-        <v>559</v>
+        <v>687</v>
       </c>
     </row>
     <row r="326" spans="2:2">
       <c r="B326" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="327" spans="2:2">
       <c r="B327" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="328" spans="2:2">
       <c r="B328" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="329" spans="2:2">
       <c r="B329" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
     </row>
     <row r="330" spans="2:2">
       <c r="B330" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="331" spans="2:2">
       <c r="B331" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
     <row r="332" spans="2:2">
       <c r="B332" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="333" spans="2:2">
       <c r="B333" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="334" spans="2:2">
       <c r="B334" t="s">
-        <v>740</v>
+        <v>575</v>
       </c>
     </row>
     <row r="335" spans="2:2">
       <c r="B335" t="s">
-        <v>577</v>
+        <v>743</v>
       </c>
     </row>
     <row r="336" spans="2:2">
       <c r="B336" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="337" spans="1:2">
       <c r="B337" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
     </row>
     <row r="338" spans="1:2">
       <c r="B338" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
     </row>
     <row r="339" spans="1:2">
       <c r="B339" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
     </row>
     <row r="340" spans="1:2">
       <c r="B340" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
     </row>
     <row r="341" spans="1:2">
       <c r="B341" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
     </row>
     <row r="342" spans="1:2">
       <c r="B342" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="343" spans="1:2">
       <c r="B343" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
     </row>
     <row r="344" spans="1:2">
       <c r="B344" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
     </row>
     <row r="345" spans="1:2">
       <c r="B345" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2">
+      <c r="B346" t="s">
         <v>598</v>
       </c>
     </row>
-    <row r="347" spans="1:2">
-      <c r="A347" t="s">
-        <v>766</v>
-      </c>
-      <c r="B347" t="s">
+    <row r="348" spans="1:2">
+      <c r="A348" t="s">
+        <v>769</v>
+      </c>
+      <c r="B348" t="s">
         <v>696</v>
       </c>
     </row>
-    <row r="349" spans="1:2">
-      <c r="A349" t="s">
-        <v>767</v>
-      </c>
-      <c r="B349" t="s">
+    <row r="350" spans="1:2">
+      <c r="A350" t="s">
+        <v>770</v>
+      </c>
+      <c r="B350" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="350" spans="1:2">
-      <c r="B350" t="s">
+    <row r="351" spans="1:2">
+      <c r="B351" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="352" spans="1:2">
-      <c r="A352" t="s">
-        <v>768</v>
-      </c>
-      <c r="B352" t="s">
+    <row r="353" spans="1:2">
+      <c r="A353" t="s">
+        <v>771</v>
+      </c>
+      <c r="B353" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="353" spans="2:2">
-      <c r="B353" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="354" spans="2:2">
+    <row r="354" spans="1:2">
       <c r="B354" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2">
+      <c r="B355" t="s">
         <v>633</v>
       </c>
     </row>
-    <row r="355" spans="2:2">
-      <c r="B355" t="s">
+    <row r="356" spans="1:2">
+      <c r="B356" t="s">
         <v>644</v>
       </c>
     </row>
@@ -10111,7 +10125,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="110.7109375" customWidth="1"/>
@@ -10197,7 +10211,7 @@
         <v>699</v>
       </c>
       <c r="B6">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="C6" t="s">
         <v>700</v>
@@ -10214,7 +10228,7 @@
         <v>702</v>
       </c>
       <c r="B7">
-        <v>2.66</v>
+        <v>1.88</v>
       </c>
       <c r="C7" t="s">
         <v>703</v>
@@ -10231,7 +10245,7 @@
         <v>705</v>
       </c>
       <c r="B8">
-        <v>1.76</v>
+        <v>2.66</v>
       </c>
       <c r="C8" t="s">
         <v>706</v>
@@ -10240,75 +10254,92 @@
         <v>8</v>
       </c>
       <c r="E8" t="s">
-        <v>701</v>
+        <v>707</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B9">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="C9" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="D9" t="s">
         <v>8</v>
       </c>
       <c r="E9" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="C10" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="D10" t="s">
         <v>8</v>
       </c>
       <c r="E10" t="s">
-        <v>643</v>
+        <v>704</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B11">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="D11" t="s">
         <v>8</v>
       </c>
       <c r="E11" t="s">
-        <v>701</v>
+        <v>643</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B12">
+        <v>1.92</v>
+      </c>
+      <c r="C12" t="s">
+        <v>715</v>
+      </c>
+      <c r="D12" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>716</v>
+      </c>
+      <c r="B13">
         <v>1.77</v>
       </c>
-      <c r="C12" t="s">
-        <v>714</v>
-      </c>
-      <c r="D12" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" t="s">
-        <v>701</v>
+      <c r="C13" t="s">
+        <v>717</v>
+      </c>
+      <c r="D13" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" t="s">
+        <v>704</v>
       </c>
     </row>
   </sheetData>
@@ -10328,7 +10359,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -10350,19 +10381,19 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="B3">
         <v>2.2</v>
       </c>
       <c r="C3" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
     </row>
   </sheetData>
@@ -10382,7 +10413,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -10404,19 +10435,19 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="B3">
         <v>1.32</v>
       </c>
       <c r="C3" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
     </row>
   </sheetData>
@@ -10436,7 +10467,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -10458,19 +10489,19 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="B3">
         <v>2.45</v>
       </c>
       <c r="C3" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
     </row>
   </sheetData>
@@ -10490,7 +10521,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -10512,47 +10543,47 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="B3">
         <v>1.9</v>
       </c>
       <c r="C3" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="B4">
         <v>2.11</v>
       </c>
       <c r="C4" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="D4" t="s">
         <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="B5">
         <v>2.7</v>
       </c>
       <c r="C5" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="D5" t="s">
         <v>8</v>
@@ -10563,13 +10594,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="B6">
         <v>2.58</v>
       </c>
       <c r="C6" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="D6" t="s">
         <v>8</v>
@@ -10580,30 +10611,30 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="B7">
         <v>1.93</v>
       </c>
       <c r="C7" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="D7" t="s">
         <v>8</v>
       </c>
       <c r="E7" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="B8">
         <v>2.05</v>
       </c>
       <c r="C8" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="D8" t="s">
         <v>8</v>
@@ -10629,7 +10660,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -10651,13 +10682,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="B3">
         <v>0.93</v>
       </c>
       <c r="C3" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
@@ -10683,7 +10714,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -10705,19 +10736,19 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="B3">
         <v>2.17</v>
       </c>
       <c r="C3" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
     </row>
   </sheetData>

--- a/pdb/nsp3/SARS-CoV-2/domains_and_infos_of_nsp3.xlsx
+++ b/pdb/nsp3/SARS-CoV-2/domains_and_infos_of_nsp3.xlsx
@@ -13,20 +13,21 @@
     <sheet name="nsp3_betaSM-M_" sheetId="4" r:id="rId4"/>
     <sheet name="nsp3_DPUP_nsp3_Ubl2_" sheetId="5" r:id="rId5"/>
     <sheet name="nsp3_NAB_" sheetId="6" r:id="rId6"/>
-    <sheet name="nsp3_PL2pro_" sheetId="7" r:id="rId7"/>
-    <sheet name="nsp3_Macro1_nsp3_PL2pro_" sheetId="8" r:id="rId8"/>
-    <sheet name="nsp3_Y3_" sheetId="9" r:id="rId9"/>
-    <sheet name="None" sheetId="10" r:id="rId10"/>
-    <sheet name="nsp3_PL2pro_nsp3_Ubl2_" sheetId="11" r:id="rId11"/>
-    <sheet name="nsp3_Ubl1_" sheetId="12" r:id="rId12"/>
-    <sheet name="Organisms" sheetId="13" r:id="rId13"/>
+    <sheet name="multi-domain1" sheetId="7" r:id="rId7"/>
+    <sheet name="nsp3_PL2pro_" sheetId="8" r:id="rId8"/>
+    <sheet name="nsp3_Macro1_nsp3_PL2pro_" sheetId="9" r:id="rId9"/>
+    <sheet name="nsp3_Y3_" sheetId="10" r:id="rId10"/>
+    <sheet name="None" sheetId="11" r:id="rId11"/>
+    <sheet name="nsp3_PL2pro_nsp3_Ubl2_" sheetId="12" r:id="rId12"/>
+    <sheet name="nsp3_Ubl1_" sheetId="13" r:id="rId13"/>
+    <sheet name="Organisms" sheetId="14" r:id="rId14"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1806" uniqueCount="772">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1819" uniqueCount="776">
   <si>
     <t>nsp3_Macro1_</t>
   </si>
@@ -2218,6 +2219,18 @@
     <t>2021-01-20</t>
   </si>
   <si>
+    <t>nsp3_PL2pro_nsp3_HVR_nsp3_Macro1_nsp3_Macro2_nsp3_Macro3_nsp3_Ubl2_nsp3_betaSM-C_nsp3_pred_Ecto_nsp3_Y1-CoV-Y-N_nsp3_Y3_</t>
+  </si>
+  <si>
+    <t>7uv5</t>
+  </si>
+  <si>
+    <t>THE CRYSTAL STRUCTURE OF PAPAIN-LIKE PROTEASE OF SARS COV-2, C111S/D286N MUTANT, IN COMPLEX WITH A LYS48-LINKED DI-UBIQUITIN</t>
+  </si>
+  <si>
+    <t>2022-04-29</t>
+  </si>
+  <si>
     <t>nsp3_PL2pro_</t>
   </si>
   <si>
@@ -2335,13 +2348,13 @@
     <t xml:space="preserve">severe acute respiratory syndrome coronavirus2 </t>
   </si>
   <si>
+    <t>homo sapiens</t>
+  </si>
+  <si>
     <t>mus musculus</t>
   </si>
   <si>
     <t>synthetic construct</t>
-  </si>
-  <si>
-    <t>homo sapiens</t>
   </si>
 </sst>
 </file>
@@ -7607,7 +7620,7 @@
         <v>753</v>
       </c>
       <c r="B3">
-        <v>2.72</v>
+        <v>2.17</v>
       </c>
       <c r="C3" t="s">
         <v>754</v>
@@ -7661,7 +7674,7 @@
         <v>757</v>
       </c>
       <c r="B3">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="C3" t="s">
         <v>758</v>
@@ -7679,6 +7692,60 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="3" max="3" width="110.7109375" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>761</v>
+      </c>
+      <c r="B3">
+        <v>2.68</v>
+      </c>
+      <c r="C3" t="s">
+        <v>762</v>
+      </c>
+      <c r="D3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" t="s">
+        <v>763</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7690,7 +7757,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -7712,13 +7779,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="B3">
         <v>3.21</v>
       </c>
       <c r="C3" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
@@ -7729,19 +7796,19 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="B4">
         <v>2.73</v>
       </c>
       <c r="C4" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="D4" t="s">
         <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
     </row>
   </sheetData>
@@ -7749,9 +7816,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B356"/>
+  <dimension ref="A1:B359"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.7109375" customWidth="1"/>
@@ -7759,12 +7826,12 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
@@ -7772,7 +7839,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="B3" t="s">
         <v>6</v>
@@ -8005,1207 +8072,1207 @@
     </row>
     <row r="49" spans="2:2">
       <c r="B49" t="s">
-        <v>90</v>
+        <v>731</v>
       </c>
     </row>
     <row r="50" spans="2:2">
       <c r="B50" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="51" spans="2:2">
       <c r="B51" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="52" spans="2:2">
       <c r="B52" t="s">
-        <v>696</v>
+        <v>94</v>
       </c>
     </row>
     <row r="53" spans="2:2">
       <c r="B53" t="s">
-        <v>96</v>
+        <v>696</v>
       </c>
     </row>
     <row r="54" spans="2:2">
       <c r="B54" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="55" spans="2:2">
       <c r="B55" t="s">
-        <v>731</v>
+        <v>98</v>
       </c>
     </row>
     <row r="56" spans="2:2">
       <c r="B56" t="s">
-        <v>100</v>
+        <v>735</v>
       </c>
     </row>
     <row r="57" spans="2:2">
       <c r="B57" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="58" spans="2:2">
       <c r="B58" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="59" spans="2:2">
       <c r="B59" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="60" spans="2:2">
       <c r="B60" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="61" spans="2:2">
       <c r="B61" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="62" spans="2:2">
       <c r="B62" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="63" spans="2:2">
       <c r="B63" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="64" spans="2:2">
       <c r="B64" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="65" spans="2:2">
       <c r="B65" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="66" spans="2:2">
       <c r="B66" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="67" spans="2:2">
       <c r="B67" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="68" spans="2:2">
       <c r="B68" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="69" spans="2:2">
       <c r="B69" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="70" spans="2:2">
       <c r="B70" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="71" spans="2:2">
       <c r="B71" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="72" spans="2:2">
       <c r="B72" t="s">
-        <v>613</v>
+        <v>131</v>
       </c>
     </row>
     <row r="73" spans="2:2">
       <c r="B73" t="s">
-        <v>134</v>
+        <v>613</v>
       </c>
     </row>
     <row r="74" spans="2:2">
       <c r="B74" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="75" spans="2:2">
       <c r="B75" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="76" spans="2:2">
       <c r="B76" t="s">
-        <v>616</v>
+        <v>138</v>
       </c>
     </row>
     <row r="77" spans="2:2">
       <c r="B77" t="s">
-        <v>140</v>
+        <v>616</v>
       </c>
     </row>
     <row r="78" spans="2:2">
       <c r="B78" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="79" spans="2:2">
       <c r="B79" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="80" spans="2:2">
       <c r="B80" t="s">
-        <v>619</v>
+        <v>144</v>
       </c>
     </row>
     <row r="81" spans="2:2">
       <c r="B81" t="s">
-        <v>146</v>
+        <v>619</v>
       </c>
     </row>
     <row r="82" spans="2:2">
       <c r="B82" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="83" spans="2:2">
       <c r="B83" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="84" spans="2:2">
       <c r="B84" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="85" spans="2:2">
       <c r="B85" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="86" spans="2:2">
       <c r="B86" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="87" spans="2:2">
       <c r="B87" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="88" spans="2:2">
       <c r="B88" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="89" spans="2:2">
       <c r="B89" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="90" spans="2:2">
       <c r="B90" t="s">
-        <v>622</v>
+        <v>163</v>
       </c>
     </row>
     <row r="91" spans="2:2">
       <c r="B91" t="s">
-        <v>165</v>
+        <v>622</v>
       </c>
     </row>
     <row r="92" spans="2:2">
       <c r="B92" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="93" spans="2:2">
       <c r="B93" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="94" spans="2:2">
       <c r="B94" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="95" spans="2:2">
       <c r="B95" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="96" spans="2:2">
       <c r="B96" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="97" spans="2:2">
       <c r="B97" t="s">
-        <v>625</v>
+        <v>175</v>
       </c>
     </row>
     <row r="98" spans="2:2">
       <c r="B98" t="s">
-        <v>699</v>
+        <v>625</v>
       </c>
     </row>
     <row r="99" spans="2:2">
       <c r="B99" t="s">
-        <v>177</v>
+        <v>699</v>
       </c>
     </row>
     <row r="100" spans="2:2">
       <c r="B100" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="101" spans="2:2">
       <c r="B101" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="102" spans="2:2">
       <c r="B102" t="s">
-        <v>734</v>
+        <v>181</v>
       </c>
     </row>
     <row r="103" spans="2:2">
       <c r="B103" t="s">
-        <v>183</v>
+        <v>738</v>
       </c>
     </row>
     <row r="104" spans="2:2">
       <c r="B104" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="105" spans="2:2">
       <c r="B105" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="106" spans="2:2">
       <c r="B106" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="107" spans="2:2">
       <c r="B107" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="108" spans="2:2">
       <c r="B108" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="109" spans="2:2">
       <c r="B109" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="110" spans="2:2">
       <c r="B110" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="111" spans="2:2">
       <c r="B111" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="112" spans="2:2">
       <c r="B112" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="113" spans="2:2">
       <c r="B113" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="114" spans="2:2">
       <c r="B114" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="115" spans="2:2">
       <c r="B115" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="116" spans="2:2">
       <c r="B116" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="117" spans="2:2">
       <c r="B117" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="118" spans="2:2">
       <c r="B118" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="119" spans="2:2">
       <c r="B119" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="120" spans="2:2">
       <c r="B120" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="121" spans="2:2">
       <c r="B121" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="122" spans="2:2">
       <c r="B122" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="123" spans="2:2">
       <c r="B123" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="124" spans="2:2">
       <c r="B124" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="125" spans="2:2">
       <c r="B125" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="126" spans="2:2">
       <c r="B126" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="127" spans="2:2">
       <c r="B127" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="128" spans="2:2">
       <c r="B128" t="s">
-        <v>746</v>
+        <v>234</v>
       </c>
     </row>
     <row r="129" spans="2:2">
       <c r="B129" t="s">
-        <v>236</v>
+        <v>750</v>
       </c>
     </row>
     <row r="130" spans="2:2">
       <c r="B130" t="s">
-        <v>736</v>
+        <v>236</v>
       </c>
     </row>
     <row r="131" spans="2:2">
       <c r="B131" t="s">
-        <v>238</v>
+        <v>740</v>
       </c>
     </row>
     <row r="132" spans="2:2">
       <c r="B132" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="133" spans="2:2">
       <c r="B133" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="134" spans="2:2">
       <c r="B134" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="135" spans="2:2">
       <c r="B135" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="136" spans="2:2">
       <c r="B136" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="137" spans="2:2">
       <c r="B137" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="138" spans="2:2">
       <c r="B138" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="139" spans="2:2">
       <c r="B139" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="140" spans="2:2">
       <c r="B140" t="s">
-        <v>628</v>
+        <v>255</v>
       </c>
     </row>
     <row r="141" spans="2:2">
       <c r="B141" t="s">
-        <v>257</v>
+        <v>628</v>
       </c>
     </row>
     <row r="142" spans="2:2">
       <c r="B142" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="143" spans="2:2">
       <c r="B143" t="s">
-        <v>630</v>
+        <v>259</v>
       </c>
     </row>
     <row r="144" spans="2:2">
       <c r="B144" t="s">
-        <v>261</v>
+        <v>630</v>
       </c>
     </row>
     <row r="145" spans="2:2">
       <c r="B145" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="146" spans="2:2">
       <c r="B146" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="147" spans="2:2">
       <c r="B147" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="148" spans="2:2">
       <c r="B148" t="s">
-        <v>633</v>
+        <v>269</v>
       </c>
     </row>
     <row r="149" spans="2:2">
       <c r="B149" t="s">
-        <v>271</v>
+        <v>633</v>
       </c>
     </row>
     <row r="150" spans="2:2">
       <c r="B150" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="151" spans="2:2">
       <c r="B151" t="s">
-        <v>738</v>
+        <v>273</v>
       </c>
     </row>
     <row r="152" spans="2:2">
       <c r="B152" t="s">
-        <v>275</v>
+        <v>742</v>
       </c>
     </row>
     <row r="153" spans="2:2">
       <c r="B153" t="s">
-        <v>702</v>
+        <v>275</v>
       </c>
     </row>
     <row r="154" spans="2:2">
       <c r="B154" t="s">
-        <v>277</v>
+        <v>702</v>
       </c>
     </row>
     <row r="155" spans="2:2">
       <c r="B155" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="156" spans="2:2">
       <c r="B156" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="157" spans="2:2">
       <c r="B157" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="158" spans="2:2">
       <c r="B158" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="159" spans="2:2">
       <c r="B159" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
     <row r="160" spans="2:2">
       <c r="B160" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="161" spans="2:2">
       <c r="B161" t="s">
-        <v>636</v>
+        <v>290</v>
       </c>
     </row>
     <row r="162" spans="2:2">
       <c r="B162" t="s">
-        <v>292</v>
+        <v>636</v>
       </c>
     </row>
     <row r="163" spans="2:2">
       <c r="B163" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="164" spans="2:2">
       <c r="B164" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="165" spans="2:2">
       <c r="B165" t="s">
-        <v>638</v>
+        <v>296</v>
       </c>
     </row>
     <row r="166" spans="2:2">
       <c r="B166" t="s">
-        <v>298</v>
+        <v>638</v>
       </c>
     </row>
     <row r="167" spans="2:2">
       <c r="B167" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="168" spans="2:2">
       <c r="B168" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="169" spans="2:2">
       <c r="B169" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="170" spans="2:2">
       <c r="B170" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="171" spans="2:2">
       <c r="B171" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="172" spans="2:2">
       <c r="B172" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="173" spans="2:2">
       <c r="B173" t="s">
-        <v>641</v>
+        <v>310</v>
       </c>
     </row>
     <row r="174" spans="2:2">
       <c r="B174" t="s">
-        <v>312</v>
+        <v>641</v>
       </c>
     </row>
     <row r="175" spans="2:2">
       <c r="B175" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="176" spans="2:2">
       <c r="B176" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="177" spans="2:2">
       <c r="B177" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="178" spans="2:2">
       <c r="B178" t="s">
-        <v>749</v>
+        <v>318</v>
       </c>
     </row>
     <row r="179" spans="2:2">
       <c r="B179" t="s">
-        <v>320</v>
+        <v>753</v>
       </c>
     </row>
     <row r="180" spans="2:2">
       <c r="B180" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="181" spans="2:2">
       <c r="B181" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="182" spans="2:2">
       <c r="B182" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="183" spans="2:2">
       <c r="B183" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="184" spans="2:2">
       <c r="B184" t="s">
-        <v>644</v>
+        <v>328</v>
       </c>
     </row>
     <row r="185" spans="2:2">
       <c r="B185" t="s">
-        <v>330</v>
+        <v>644</v>
       </c>
     </row>
     <row r="186" spans="2:2">
       <c r="B186" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="187" spans="2:2">
       <c r="B187" t="s">
-        <v>646</v>
+        <v>332</v>
       </c>
     </row>
     <row r="188" spans="2:2">
       <c r="B188" t="s">
-        <v>333</v>
+        <v>646</v>
       </c>
     </row>
     <row r="189" spans="2:2">
       <c r="B189" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="190" spans="2:2">
       <c r="B190" t="s">
-        <v>705</v>
+        <v>335</v>
       </c>
     </row>
     <row r="191" spans="2:2">
       <c r="B191" t="s">
-        <v>649</v>
+        <v>705</v>
       </c>
     </row>
     <row r="192" spans="2:2">
       <c r="B192" t="s">
-        <v>337</v>
+        <v>649</v>
       </c>
     </row>
     <row r="193" spans="2:2">
       <c r="B193" t="s">
-        <v>652</v>
+        <v>337</v>
       </c>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" t="s">
-        <v>338</v>
+        <v>652</v>
       </c>
     </row>
     <row r="195" spans="2:2">
       <c r="B195" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="196" spans="2:2">
       <c r="B196" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="197" spans="2:2">
       <c r="B197" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="198" spans="2:2">
       <c r="B198" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="199" spans="2:2">
       <c r="B199" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="200" spans="2:2">
       <c r="B200" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="201" spans="2:2">
       <c r="B201" t="s">
-        <v>708</v>
+        <v>351</v>
       </c>
     </row>
     <row r="202" spans="2:2">
       <c r="B202" t="s">
-        <v>353</v>
+        <v>708</v>
       </c>
     </row>
     <row r="203" spans="2:2">
       <c r="B203" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="204" spans="2:2">
       <c r="B204" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="205" spans="2:2">
       <c r="B205" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="206" spans="2:2">
       <c r="B206" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="207" spans="2:2">
       <c r="B207" t="s">
-        <v>654</v>
+        <v>361</v>
       </c>
     </row>
     <row r="208" spans="2:2">
       <c r="B208" t="s">
-        <v>363</v>
+        <v>654</v>
       </c>
     </row>
     <row r="209" spans="2:2">
       <c r="B209" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="210" spans="2:2">
       <c r="B210" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="211" spans="2:2">
       <c r="B211" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="212" spans="2:2">
       <c r="B212" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="213" spans="2:2">
       <c r="B213" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="214" spans="2:2">
       <c r="B214" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="215" spans="2:2">
       <c r="B215" t="s">
-        <v>657</v>
+        <v>374</v>
       </c>
     </row>
     <row r="216" spans="2:2">
       <c r="B216" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
     </row>
     <row r="217" spans="2:2">
       <c r="B217" t="s">
-        <v>377</v>
+        <v>660</v>
       </c>
     </row>
     <row r="218" spans="2:2">
       <c r="B218" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="219" spans="2:2">
       <c r="B219" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="220" spans="2:2">
       <c r="B220" t="s">
-        <v>740</v>
+        <v>380</v>
       </c>
     </row>
     <row r="221" spans="2:2">
       <c r="B221" t="s">
-        <v>382</v>
+        <v>744</v>
       </c>
     </row>
     <row r="222" spans="2:2">
       <c r="B222" t="s">
-        <v>753</v>
+        <v>382</v>
       </c>
     </row>
     <row r="223" spans="2:2">
       <c r="B223" t="s">
-        <v>384</v>
+        <v>757</v>
       </c>
     </row>
     <row r="224" spans="2:2">
       <c r="B224" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="225" spans="2:2">
       <c r="B225" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="226" spans="2:2">
       <c r="B226" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="227" spans="2:2">
       <c r="B227" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="228" spans="2:2">
       <c r="B228" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="229" spans="2:2">
       <c r="B229" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="230" spans="2:2">
       <c r="B230" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="231" spans="2:2">
       <c r="B231" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="232" spans="2:2">
       <c r="B232" t="s">
-        <v>663</v>
+        <v>400</v>
       </c>
     </row>
     <row r="233" spans="2:2">
       <c r="B233" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
     </row>
     <row r="234" spans="2:2">
       <c r="B234" t="s">
-        <v>402</v>
+        <v>666</v>
       </c>
     </row>
     <row r="235" spans="2:2">
       <c r="B235" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="236" spans="2:2">
       <c r="B236" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="237" spans="2:2">
       <c r="B237" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="238" spans="2:2">
       <c r="B238" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="239" spans="2:2">
       <c r="B239" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="240" spans="2:2">
       <c r="B240" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="241" spans="2:2">
       <c r="B241" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="242" spans="2:2">
       <c r="B242" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="243" spans="2:2">
       <c r="B243" t="s">
-        <v>710</v>
+        <v>420</v>
       </c>
     </row>
     <row r="244" spans="2:2">
       <c r="B244" t="s">
-        <v>669</v>
+        <v>710</v>
       </c>
     </row>
     <row r="245" spans="2:2">
       <c r="B245" t="s">
-        <v>421</v>
+        <v>669</v>
       </c>
     </row>
     <row r="246" spans="2:2">
       <c r="B246" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="247" spans="2:2">
       <c r="B247" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="248" spans="2:2">
       <c r="B248" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="249" spans="2:2">
       <c r="B249" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="250" spans="2:2">
       <c r="B250" t="s">
-        <v>671</v>
+        <v>429</v>
       </c>
     </row>
     <row r="251" spans="2:2">
       <c r="B251" t="s">
-        <v>431</v>
+        <v>671</v>
       </c>
     </row>
     <row r="252" spans="2:2">
       <c r="B252" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="253" spans="2:2">
       <c r="B253" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="254" spans="2:2">
       <c r="B254" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="255" spans="2:2">
       <c r="B255" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="256" spans="2:2">
       <c r="B256" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="257" spans="2:2">
       <c r="B257" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
     </row>
     <row r="258" spans="2:2">
       <c r="B258" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="259" spans="2:2">
       <c r="B259" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="260" spans="2:2">
       <c r="B260" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="261" spans="2:2">
       <c r="B261" t="s">
-        <v>673</v>
+        <v>450</v>
       </c>
     </row>
     <row r="262" spans="2:2">
       <c r="B262" t="s">
-        <v>452</v>
+        <v>673</v>
       </c>
     </row>
     <row r="263" spans="2:2">
       <c r="B263" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="264" spans="2:2">
       <c r="B264" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="265" spans="2:2">
       <c r="B265" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="266" spans="2:2">
       <c r="B266" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="267" spans="2:2">
       <c r="B267" t="s">
-        <v>676</v>
+        <v>460</v>
       </c>
     </row>
     <row r="268" spans="2:2">
       <c r="B268" t="s">
-        <v>462</v>
+        <v>676</v>
       </c>
     </row>
     <row r="269" spans="2:2">
       <c r="B269" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="270" spans="2:2">
       <c r="B270" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="271" spans="2:2">
       <c r="B271" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="272" spans="2:2">
       <c r="B272" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="273" spans="2:2">
       <c r="B273" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="274" spans="2:2">
       <c r="B274" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="275" spans="2:2">
       <c r="B275" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="276" spans="2:2">
       <c r="B276" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="277" spans="2:2">
       <c r="B277" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="278" spans="2:2">
       <c r="B278" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="279" spans="2:2">
       <c r="B279" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="280" spans="2:2">
       <c r="B280" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="281" spans="2:2">
       <c r="B281" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="282" spans="2:2">
       <c r="B282" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="283" spans="2:2">
       <c r="B283" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="284" spans="2:2">
       <c r="B284" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="285" spans="2:2">
       <c r="B285" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="286" spans="2:2">
       <c r="B286" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
     </row>
     <row r="287" spans="2:2">
       <c r="B287" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="288" spans="2:2">
       <c r="B288" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
     </row>
     <row r="289" spans="2:2">
       <c r="B289" t="s">
-        <v>757</v>
+        <v>503</v>
       </c>
     </row>
     <row r="290" spans="2:2">
@@ -9215,326 +9282,341 @@
     </row>
     <row r="291" spans="2:2">
       <c r="B291" t="s">
-        <v>505</v>
+        <v>765</v>
       </c>
     </row>
     <row r="292" spans="2:2">
       <c r="B292" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="293" spans="2:2">
       <c r="B293" t="s">
-        <v>763</v>
+        <v>507</v>
       </c>
     </row>
     <row r="294" spans="2:2">
       <c r="B294" t="s">
-        <v>679</v>
+        <v>767</v>
       </c>
     </row>
     <row r="295" spans="2:2">
       <c r="B295" t="s">
-        <v>509</v>
+        <v>679</v>
       </c>
     </row>
     <row r="296" spans="2:2">
       <c r="B296" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="297" spans="2:2">
       <c r="B297" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="298" spans="2:2">
       <c r="B298" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="299" spans="2:2">
       <c r="B299" t="s">
-        <v>712</v>
+        <v>515</v>
       </c>
     </row>
     <row r="300" spans="2:2">
       <c r="B300" t="s">
-        <v>517</v>
+        <v>712</v>
       </c>
     </row>
     <row r="301" spans="2:2">
       <c r="B301" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="302" spans="2:2">
       <c r="B302" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="303" spans="2:2">
       <c r="B303" t="s">
-        <v>714</v>
+        <v>521</v>
       </c>
     </row>
     <row r="304" spans="2:2">
       <c r="B304" t="s">
-        <v>523</v>
+        <v>714</v>
       </c>
     </row>
     <row r="305" spans="2:2">
       <c r="B305" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="306" spans="2:2">
       <c r="B306" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="307" spans="2:2">
       <c r="B307" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="308" spans="2:2">
       <c r="B308" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="309" spans="2:2">
       <c r="B309" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="310" spans="2:2">
       <c r="B310" t="s">
-        <v>716</v>
+        <v>533</v>
       </c>
     </row>
     <row r="311" spans="2:2">
       <c r="B311" t="s">
-        <v>535</v>
+        <v>716</v>
       </c>
     </row>
     <row r="312" spans="2:2">
       <c r="B312" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="313" spans="2:2">
       <c r="B313" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="314" spans="2:2">
       <c r="B314" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="315" spans="2:2">
       <c r="B315" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="316" spans="2:2">
       <c r="B316" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="317" spans="2:2">
       <c r="B317" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="318" spans="2:2">
       <c r="B318" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="319" spans="2:2">
       <c r="B319" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="320" spans="2:2">
       <c r="B320" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="321" spans="2:2">
       <c r="B321" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="322" spans="2:2">
       <c r="B322" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="323" spans="2:2">
       <c r="B323" t="s">
-        <v>682</v>
+        <v>557</v>
       </c>
     </row>
     <row r="324" spans="2:2">
       <c r="B324" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="325" spans="2:2">
       <c r="B325" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
     </row>
     <row r="326" spans="2:2">
       <c r="B326" t="s">
-        <v>559</v>
+        <v>687</v>
       </c>
     </row>
     <row r="327" spans="2:2">
       <c r="B327" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="328" spans="2:2">
       <c r="B328" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="329" spans="2:2">
       <c r="B329" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="330" spans="2:2">
       <c r="B330" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
     </row>
     <row r="331" spans="2:2">
       <c r="B331" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="332" spans="2:2">
       <c r="B332" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
     <row r="333" spans="2:2">
       <c r="B333" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="334" spans="2:2">
       <c r="B334" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="335" spans="2:2">
       <c r="B335" t="s">
-        <v>743</v>
+        <v>575</v>
       </c>
     </row>
     <row r="336" spans="2:2">
       <c r="B336" t="s">
-        <v>577</v>
+        <v>747</v>
       </c>
     </row>
     <row r="337" spans="1:2">
       <c r="B337" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="338" spans="1:2">
       <c r="B338" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
     </row>
     <row r="339" spans="1:2">
       <c r="B339" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
     </row>
     <row r="340" spans="1:2">
       <c r="B340" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
     </row>
     <row r="341" spans="1:2">
       <c r="B341" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
     </row>
     <row r="342" spans="1:2">
       <c r="B342" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
     </row>
     <row r="343" spans="1:2">
       <c r="B343" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="344" spans="1:2">
       <c r="B344" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
     </row>
     <row r="345" spans="1:2">
       <c r="B345" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
     </row>
     <row r="346" spans="1:2">
       <c r="B346" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2">
+      <c r="B347" t="s">
         <v>598</v>
       </c>
     </row>
-    <row r="348" spans="1:2">
-      <c r="A348" t="s">
-        <v>769</v>
-      </c>
-      <c r="B348" t="s">
-        <v>696</v>
+    <row r="349" spans="1:2">
+      <c r="A349" t="s">
+        <v>773</v>
+      </c>
+      <c r="B349" t="s">
+        <v>731</v>
       </c>
     </row>
     <row r="350" spans="1:2">
-      <c r="A350" t="s">
-        <v>770</v>
-      </c>
       <c r="B350" t="s">
-        <v>616</v>
+        <v>731</v>
       </c>
     </row>
     <row r="351" spans="1:2">
       <c r="B351" t="s">
-        <v>676</v>
+        <v>619</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2">
+      <c r="B352" t="s">
+        <v>740</v>
       </c>
     </row>
     <row r="353" spans="1:2">
-      <c r="A353" t="s">
-        <v>771</v>
-      </c>
       <c r="B353" t="s">
-        <v>619</v>
+        <v>633</v>
       </c>
     </row>
     <row r="354" spans="1:2">
       <c r="B354" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="355" spans="1:2">
-      <c r="B355" t="s">
-        <v>633</v>
+        <v>644</v>
       </c>
     </row>
     <row r="356" spans="1:2">
+      <c r="A356" t="s">
+        <v>774</v>
+      </c>
       <c r="B356" t="s">
-        <v>644</v>
+        <v>696</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2">
+      <c r="A358" t="s">
+        <v>775</v>
+      </c>
+      <c r="B358" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2">
+      <c r="B359" t="s">
+        <v>676</v>
       </c>
     </row>
   </sheetData>
@@ -10511,6 +10593,60 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="3" max="3" width="110.7109375" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>731</v>
+      </c>
+      <c r="B3">
+        <v>1.45</v>
+      </c>
+      <c r="C3" t="s">
+        <v>732</v>
+      </c>
+      <c r="D3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" t="s">
+        <v>733</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -10521,7 +10657,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -10543,47 +10679,47 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="B3">
         <v>1.9</v>
       </c>
       <c r="C3" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="B4">
         <v>2.11</v>
       </c>
       <c r="C4" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="D4" t="s">
         <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="B5">
         <v>2.7</v>
       </c>
       <c r="C5" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="D5" t="s">
         <v>8</v>
@@ -10594,13 +10730,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="B6">
         <v>2.58</v>
       </c>
       <c r="C6" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="D6" t="s">
         <v>8</v>
@@ -10611,90 +10747,36 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="B7">
         <v>1.93</v>
       </c>
       <c r="C7" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="D7" t="s">
         <v>8</v>
       </c>
       <c r="E7" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="B8">
         <v>2.05</v>
       </c>
       <c r="C8" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="D8" t="s">
         <v>8</v>
       </c>
       <c r="E8" t="s">
         <v>612</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="3" max="3" width="110.7109375" customWidth="1"/>
-    <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
-        <v>746</v>
-      </c>
-      <c r="B3">
-        <v>0.93</v>
-      </c>
-      <c r="C3" t="s">
-        <v>747</v>
-      </c>
-      <c r="D3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" t="s">
-        <v>443</v>
       </c>
     </row>
   </sheetData>
@@ -10714,7 +10796,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -10736,19 +10818,19 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B3">
-        <v>2.17</v>
+        <v>0.93</v>
       </c>
       <c r="C3" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>751</v>
+        <v>443</v>
       </c>
     </row>
   </sheetData>

--- a/pdb/nsp3/SARS-CoV-2/domains_and_infos_of_nsp3.xlsx
+++ b/pdb/nsp3/SARS-CoV-2/domains_and_infos_of_nsp3.xlsx
@@ -16,19 +16,20 @@
     <sheet name="multi-domain1" sheetId="7" r:id="rId7"/>
     <sheet name="nsp3_PL2pro_" sheetId="8" r:id="rId8"/>
     <sheet name="nsp3_Macro1_nsp3_PL2pro_" sheetId="9" r:id="rId9"/>
-    <sheet name="nsp3_Y3_" sheetId="10" r:id="rId10"/>
-    <sheet name="None" sheetId="11" r:id="rId11"/>
-    <sheet name="nsp3_DPUP_" sheetId="12" r:id="rId12"/>
-    <sheet name="nsp3_PL2pro_nsp3_Ubl2_" sheetId="13" r:id="rId13"/>
-    <sheet name="nsp3_Ubl1_" sheetId="14" r:id="rId14"/>
-    <sheet name="Organisms" sheetId="15" r:id="rId15"/>
+    <sheet name="nsp3_Macro3_" sheetId="10" r:id="rId10"/>
+    <sheet name="nsp3_Y3_" sheetId="11" r:id="rId11"/>
+    <sheet name="None" sheetId="12" r:id="rId12"/>
+    <sheet name="nsp3_DPUP_" sheetId="13" r:id="rId13"/>
+    <sheet name="nsp3_PL2pro_nsp3_Ubl2_" sheetId="14" r:id="rId14"/>
+    <sheet name="nsp3_Ubl1_" sheetId="15" r:id="rId15"/>
+    <sheet name="Organisms" sheetId="16" r:id="rId16"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2670" uniqueCount="1119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2686" uniqueCount="1125">
   <si>
     <t>nsp3_Macro1_</t>
   </si>
@@ -3301,6 +3302,24 @@
   </si>
   <si>
     <t>CRYSTAL STRUCTURE OF SARS-COV-2 NSP3 MACRODOMAIN (C2 CRYSTAL FORM, METHYLATED)</t>
+  </si>
+  <si>
+    <t>nsp3_Macro3_</t>
+  </si>
+  <si>
+    <t>7xc3</t>
+  </si>
+  <si>
+    <t>CRYSTAL STRUCTURE OF SARS-COV-2 NSP3 MACRODOMAIN 3 (SARS-UNIQUE DOMAIN-M)</t>
+  </si>
+  <si>
+    <t>2022-03-22</t>
+  </si>
+  <si>
+    <t>7xc4</t>
+  </si>
+  <si>
+    <t>CRYSTAL STRUCTURE OF SARS-COV-2 NSP3 MACRODOMAIN 3 (SARS-UNIQUE DOMAIN-M) IN COMPLEX WITH OXAPROZIN</t>
   </si>
   <si>
     <t>nsp3_Y3_</t>
@@ -11471,7 +11490,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="110.7109375" customWidth="1"/>
@@ -11506,7 +11525,7 @@
         <v>1092</v>
       </c>
       <c r="B3">
-        <v>2.17</v>
+        <v>1.7</v>
       </c>
       <c r="C3" t="s">
         <v>1093</v>
@@ -11515,6 +11534,23 @@
         <v>8</v>
       </c>
       <c r="E3" t="s">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B4">
+        <v>2.1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1096</v>
+      </c>
+      <c r="D4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" t="s">
         <v>1094</v>
       </c>
     </row>
@@ -11535,7 +11571,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -11557,19 +11593,19 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="B3">
-        <v>2.72</v>
+        <v>2.17</v>
       </c>
       <c r="C3" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
     </row>
   </sheetData>
@@ -11589,7 +11625,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -11611,19 +11647,19 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="C3" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="D3" t="s">
-        <v>1102</v>
+        <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>960</v>
+        <v>1104</v>
       </c>
     </row>
   </sheetData>
@@ -11643,7 +11679,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -11665,19 +11701,19 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="B3">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>1108</v>
       </c>
       <c r="E3" t="s">
-        <v>1106</v>
+        <v>960</v>
       </c>
     </row>
   </sheetData>
@@ -11686,6 +11722,60 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="3" max="3" width="110.7109375" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B3">
+        <v>2.68</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -11697,7 +11787,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>1107</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -11719,13 +11809,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>1108</v>
+        <v>1114</v>
       </c>
       <c r="B3">
         <v>3.21</v>
       </c>
       <c r="C3" t="s">
-        <v>1109</v>
+        <v>1115</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
@@ -11736,19 +11826,19 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>1110</v>
+        <v>1116</v>
       </c>
       <c r="B4">
         <v>2.73</v>
       </c>
       <c r="C4" t="s">
-        <v>1111</v>
+        <v>1117</v>
       </c>
       <c r="D4" t="s">
         <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>1112</v>
+        <v>1118</v>
       </c>
     </row>
   </sheetData>
@@ -11756,9 +11846,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B528"/>
+  <dimension ref="A1:B530"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.7109375" customWidth="1"/>
@@ -11766,12 +11856,12 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>1113</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>1114</v>
+        <v>1120</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
@@ -11779,7 +11869,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>1115</v>
+        <v>1121</v>
       </c>
       <c r="B3" t="s">
         <v>6</v>
@@ -12727,1680 +12817,1690 @@
     </row>
     <row r="192" spans="2:2">
       <c r="B192" t="s">
-        <v>361</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="193" spans="2:2">
       <c r="B193" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="195" spans="2:2">
       <c r="B195" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="196" spans="2:2">
       <c r="B196" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="197" spans="2:2">
       <c r="B197" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="198" spans="2:2">
       <c r="B198" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="199" spans="2:2">
       <c r="B199" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="200" spans="2:2">
       <c r="B200" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="201" spans="2:2">
       <c r="B201" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="202" spans="2:2">
       <c r="B202" t="s">
-        <v>967</v>
+        <v>379</v>
       </c>
     </row>
     <row r="203" spans="2:2">
       <c r="B203" t="s">
-        <v>381</v>
+        <v>967</v>
       </c>
     </row>
     <row r="204" spans="2:2">
       <c r="B204" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="205" spans="2:2">
       <c r="B205" t="s">
-        <v>969</v>
+        <v>383</v>
       </c>
     </row>
     <row r="206" spans="2:2">
       <c r="B206" t="s">
-        <v>385</v>
+        <v>969</v>
       </c>
     </row>
     <row r="207" spans="2:2">
       <c r="B207" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="208" spans="2:2">
       <c r="B208" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
     </row>
     <row r="209" spans="2:2">
       <c r="B209" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="210" spans="2:2">
       <c r="B210" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="211" spans="2:2">
       <c r="B211" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="212" spans="2:2">
       <c r="B212" t="s">
-        <v>972</v>
+        <v>397</v>
       </c>
     </row>
     <row r="213" spans="2:2">
       <c r="B213" t="s">
-        <v>399</v>
+        <v>972</v>
       </c>
     </row>
     <row r="214" spans="2:2">
       <c r="B214" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="215" spans="2:2">
       <c r="B215" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="216" spans="2:2">
       <c r="B216" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="217" spans="2:2">
       <c r="B217" t="s">
-        <v>1081</v>
+        <v>405</v>
       </c>
     </row>
     <row r="218" spans="2:2">
       <c r="B218" t="s">
-        <v>407</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="219" spans="2:2">
       <c r="B219" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="220" spans="2:2">
       <c r="B220" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="221" spans="2:2">
       <c r="B221" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="222" spans="2:2">
       <c r="B222" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="223" spans="2:2">
       <c r="B223" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="224" spans="2:2">
       <c r="B224" t="s">
-        <v>1041</v>
+        <v>417</v>
       </c>
     </row>
     <row r="225" spans="2:2">
       <c r="B225" t="s">
-        <v>419</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="226" spans="2:2">
       <c r="B226" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="227" spans="2:2">
       <c r="B227" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="228" spans="2:2">
       <c r="B228" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="229" spans="2:2">
       <c r="B229" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="230" spans="2:2">
       <c r="B230" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="231" spans="2:2">
       <c r="B231" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="232" spans="2:2">
       <c r="B232" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
     </row>
     <row r="233" spans="2:2">
       <c r="B233" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="234" spans="2:2">
       <c r="B234" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="235" spans="2:2">
       <c r="B235" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="236" spans="2:2">
       <c r="B236" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="237" spans="2:2">
       <c r="B237" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="238" spans="2:2">
       <c r="B238" t="s">
-        <v>975</v>
+        <v>444</v>
       </c>
     </row>
     <row r="239" spans="2:2">
       <c r="B239" t="s">
-        <v>446</v>
+        <v>975</v>
       </c>
     </row>
     <row r="240" spans="2:2">
       <c r="B240" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="241" spans="2:2">
       <c r="B241" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="242" spans="2:2">
       <c r="B242" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="243" spans="2:2">
       <c r="B243" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="244" spans="2:2">
       <c r="B244" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="245" spans="2:2">
       <c r="B245" t="s">
-        <v>977</v>
+        <v>456</v>
       </c>
     </row>
     <row r="246" spans="2:2">
       <c r="B246" t="s">
-        <v>458</v>
+        <v>977</v>
       </c>
     </row>
     <row r="247" spans="2:2">
       <c r="B247" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="248" spans="2:2">
       <c r="B248" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="249" spans="2:2">
       <c r="B249" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="250" spans="2:2">
       <c r="B250" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="251" spans="2:2">
       <c r="B251" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="252" spans="2:2">
       <c r="B252" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="253" spans="2:2">
       <c r="B253" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="254" spans="2:2">
       <c r="B254" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="255" spans="2:2">
       <c r="B255" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="256" spans="2:2">
       <c r="B256" t="s">
-        <v>980</v>
+        <v>476</v>
       </c>
     </row>
     <row r="257" spans="2:2">
       <c r="B257" t="s">
-        <v>478</v>
+        <v>980</v>
       </c>
     </row>
     <row r="258" spans="2:2">
       <c r="B258" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="259" spans="2:2">
       <c r="B259" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="260" spans="2:2">
       <c r="B260" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="261" spans="2:2">
       <c r="B261" t="s">
-        <v>1092</v>
+        <v>484</v>
       </c>
     </row>
     <row r="262" spans="2:2">
       <c r="B262" t="s">
-        <v>486</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="263" spans="2:2">
       <c r="B263" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="264" spans="2:2">
       <c r="B264" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="265" spans="2:2">
       <c r="B265" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="266" spans="2:2">
       <c r="B266" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="267" spans="2:2">
       <c r="B267" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="268" spans="2:2">
       <c r="B268" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="269" spans="2:2">
       <c r="B269" t="s">
-        <v>983</v>
+        <v>498</v>
       </c>
     </row>
     <row r="270" spans="2:2">
       <c r="B270" t="s">
-        <v>500</v>
+        <v>983</v>
       </c>
     </row>
     <row r="271" spans="2:2">
       <c r="B271" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="272" spans="2:2">
       <c r="B272" t="s">
-        <v>985</v>
+        <v>502</v>
       </c>
     </row>
     <row r="273" spans="2:2">
       <c r="B273" t="s">
-        <v>503</v>
+        <v>985</v>
       </c>
     </row>
     <row r="274" spans="2:2">
       <c r="B274" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="275" spans="2:2">
       <c r="B275" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="276" spans="2:2">
       <c r="B276" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="277" spans="2:2">
       <c r="B277" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="278" spans="2:2">
       <c r="B278" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="279" spans="2:2">
       <c r="B279" t="s">
-        <v>1044</v>
+        <v>513</v>
       </c>
     </row>
     <row r="280" spans="2:2">
       <c r="B280" t="s">
-        <v>988</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="281" spans="2:2">
       <c r="B281" t="s">
-        <v>515</v>
+        <v>988</v>
       </c>
     </row>
     <row r="282" spans="2:2">
       <c r="B282" t="s">
-        <v>991</v>
+        <v>515</v>
       </c>
     </row>
     <row r="283" spans="2:2">
       <c r="B283" t="s">
-        <v>516</v>
+        <v>991</v>
       </c>
     </row>
     <row r="284" spans="2:2">
       <c r="B284" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="285" spans="2:2">
       <c r="B285" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="286" spans="2:2">
       <c r="B286" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="287" spans="2:2">
       <c r="B287" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="288" spans="2:2">
       <c r="B288" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="289" spans="2:2">
       <c r="B289" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="290" spans="2:2">
       <c r="B290" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="291" spans="2:2">
       <c r="B291" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="292" spans="2:2">
       <c r="B292" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="293" spans="2:2">
       <c r="B293" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="294" spans="2:2">
       <c r="B294" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="295" spans="2:2">
       <c r="B295" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
     </row>
     <row r="296" spans="2:2">
       <c r="B296" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="297" spans="2:2">
       <c r="B297" t="s">
-        <v>1047</v>
+        <v>543</v>
       </c>
     </row>
     <row r="298" spans="2:2">
       <c r="B298" t="s">
-        <v>545</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="299" spans="2:2">
       <c r="B299" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="300" spans="2:2">
       <c r="B300" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="301" spans="2:2">
       <c r="B301" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="302" spans="2:2">
       <c r="B302" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="303" spans="2:2">
       <c r="B303" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="304" spans="2:2">
       <c r="B304" t="s">
-        <v>993</v>
+        <v>555</v>
       </c>
     </row>
     <row r="305" spans="2:2">
       <c r="B305" t="s">
-        <v>557</v>
+        <v>993</v>
       </c>
     </row>
     <row r="306" spans="2:2">
       <c r="B306" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
     </row>
     <row r="307" spans="2:2">
       <c r="B307" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="308" spans="2:2">
       <c r="B308" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="309" spans="2:2">
       <c r="B309" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="310" spans="2:2">
       <c r="B310" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
     </row>
     <row r="311" spans="2:2">
       <c r="B311" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="312" spans="2:2">
       <c r="B312" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
     <row r="313" spans="2:2">
       <c r="B313" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="314" spans="2:2">
       <c r="B314" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="315" spans="2:2">
       <c r="B315" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="316" spans="2:2">
       <c r="B316" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="317" spans="2:2">
       <c r="B317" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
     </row>
     <row r="318" spans="2:2">
       <c r="B318" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="319" spans="2:2">
       <c r="B319" t="s">
-        <v>996</v>
+        <v>582</v>
       </c>
     </row>
     <row r="320" spans="2:2">
       <c r="B320" t="s">
-        <v>585</v>
+        <v>996</v>
       </c>
     </row>
     <row r="321" spans="2:2">
       <c r="B321" t="s">
-        <v>999</v>
+        <v>585</v>
       </c>
     </row>
     <row r="322" spans="2:2">
       <c r="B322" t="s">
-        <v>587</v>
+        <v>999</v>
       </c>
     </row>
     <row r="323" spans="2:2">
       <c r="B323" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
     </row>
     <row r="324" spans="2:2">
       <c r="B324" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="325" spans="2:2">
       <c r="B325" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
     </row>
     <row r="326" spans="2:2">
       <c r="B326" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="327" spans="2:2">
       <c r="B327" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
     </row>
     <row r="328" spans="2:2">
       <c r="B328" t="s">
-        <v>1083</v>
+        <v>596</v>
       </c>
     </row>
     <row r="329" spans="2:2">
       <c r="B329" t="s">
-        <v>598</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="330" spans="2:2">
       <c r="B330" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
     </row>
     <row r="331" spans="2:2">
       <c r="B331" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="332" spans="2:2">
       <c r="B332" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="333" spans="2:2">
       <c r="B333" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
     </row>
     <row r="334" spans="2:2">
       <c r="B334" t="s">
-        <v>1096</v>
+        <v>606</v>
       </c>
     </row>
     <row r="335" spans="2:2">
       <c r="B335" t="s">
-        <v>608</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="336" spans="2:2">
       <c r="B336" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="337" spans="2:2">
       <c r="B337" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="338" spans="2:2">
       <c r="B338" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="339" spans="2:2">
       <c r="B339" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="340" spans="2:2">
       <c r="B340" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="341" spans="2:2">
       <c r="B341" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="342" spans="2:2">
       <c r="B342" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="343" spans="2:2">
       <c r="B343" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
     </row>
     <row r="344" spans="2:2">
       <c r="B344" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
     </row>
     <row r="345" spans="2:2">
       <c r="B345" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
     </row>
     <row r="346" spans="2:2">
       <c r="B346" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
     </row>
     <row r="347" spans="2:2">
       <c r="B347" t="s">
-        <v>1002</v>
+        <v>630</v>
       </c>
     </row>
     <row r="348" spans="2:2">
       <c r="B348" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="349" spans="2:2">
       <c r="B349" t="s">
-        <v>632</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="350" spans="2:2">
       <c r="B350" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="351" spans="2:2">
       <c r="B351" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
     </row>
     <row r="352" spans="2:2">
       <c r="B352" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
     </row>
     <row r="353" spans="2:2">
       <c r="B353" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
     </row>
     <row r="354" spans="2:2">
       <c r="B354" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
     </row>
     <row r="355" spans="2:2">
       <c r="B355" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
     </row>
     <row r="356" spans="2:2">
       <c r="B356" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
     </row>
     <row r="357" spans="2:2">
       <c r="B357" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
     </row>
     <row r="358" spans="2:2">
       <c r="B358" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
     </row>
     <row r="359" spans="2:2">
       <c r="B359" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
     </row>
     <row r="360" spans="2:2">
       <c r="B360" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
     </row>
     <row r="361" spans="2:2">
       <c r="B361" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
     </row>
     <row r="362" spans="2:2">
       <c r="B362" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
     </row>
     <row r="363" spans="2:2">
       <c r="B363" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
     </row>
     <row r="364" spans="2:2">
       <c r="B364" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
     </row>
     <row r="365" spans="2:2">
       <c r="B365" t="s">
-        <v>1049</v>
+        <v>664</v>
       </c>
     </row>
     <row r="366" spans="2:2">
       <c r="B366" t="s">
-        <v>1008</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="367" spans="2:2">
       <c r="B367" t="s">
-        <v>665</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="368" spans="2:2">
       <c r="B368" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
     </row>
     <row r="369" spans="2:2">
       <c r="B369" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="370" spans="2:2">
       <c r="B370" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
     </row>
     <row r="371" spans="2:2">
       <c r="B371" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
     </row>
     <row r="372" spans="2:2">
       <c r="B372" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
     </row>
     <row r="373" spans="2:2">
       <c r="B373" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
     </row>
     <row r="374" spans="2:2">
       <c r="B374" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
     </row>
     <row r="375" spans="2:2">
       <c r="B375" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
     </row>
     <row r="376" spans="2:2">
       <c r="B376" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
     </row>
     <row r="377" spans="2:2">
       <c r="B377" t="s">
-        <v>1010</v>
+        <v>683</v>
       </c>
     </row>
     <row r="378" spans="2:2">
       <c r="B378" t="s">
-        <v>685</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="379" spans="2:2">
       <c r="B379" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
     </row>
     <row r="380" spans="2:2">
       <c r="B380" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
     </row>
     <row r="381" spans="2:2">
       <c r="B381" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
     </row>
     <row r="382" spans="2:2">
       <c r="B382" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
     </row>
     <row r="383" spans="2:2">
       <c r="B383" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
     </row>
     <row r="384" spans="2:2">
       <c r="B384" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
     </row>
     <row r="385" spans="2:2">
       <c r="B385" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
     </row>
     <row r="386" spans="2:2">
       <c r="B386" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="387" spans="2:2">
       <c r="B387" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
     </row>
     <row r="388" spans="2:2">
       <c r="B388" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
     </row>
     <row r="389" spans="2:2">
       <c r="B389" t="s">
-        <v>1012</v>
+        <v>706</v>
       </c>
     </row>
     <row r="390" spans="2:2">
       <c r="B390" t="s">
-        <v>708</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="391" spans="2:2">
       <c r="B391" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
     </row>
     <row r="392" spans="2:2">
       <c r="B392" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
     </row>
     <row r="393" spans="2:2">
       <c r="B393" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="394" spans="2:2">
       <c r="B394" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
     </row>
     <row r="395" spans="2:2">
       <c r="B395" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
     </row>
     <row r="396" spans="2:2">
       <c r="B396" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
     </row>
     <row r="397" spans="2:2">
       <c r="B397" t="s">
-        <v>1015</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="398" spans="2:2">
       <c r="B398" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
     </row>
     <row r="399" spans="2:2">
       <c r="B399" t="s">
-        <v>723</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="400" spans="2:2">
       <c r="B400" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
     </row>
     <row r="401" spans="2:2">
       <c r="B401" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
     </row>
     <row r="402" spans="2:2">
       <c r="B402" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
     </row>
     <row r="403" spans="2:2">
       <c r="B403" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
     </row>
     <row r="404" spans="2:2">
       <c r="B404" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
     </row>
     <row r="405" spans="2:2">
       <c r="B405" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
     </row>
     <row r="406" spans="2:2">
       <c r="B406" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
     </row>
     <row r="407" spans="2:2">
       <c r="B407" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
     </row>
     <row r="408" spans="2:2">
       <c r="B408" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
     </row>
     <row r="409" spans="2:2">
       <c r="B409" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
     </row>
     <row r="410" spans="2:2">
       <c r="B410" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
     </row>
     <row r="411" spans="2:2">
       <c r="B411" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
     </row>
     <row r="412" spans="2:2">
       <c r="B412" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
     </row>
     <row r="413" spans="2:2">
       <c r="B413" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
     </row>
     <row r="414" spans="2:2">
       <c r="B414" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
     </row>
     <row r="415" spans="2:2">
       <c r="B415" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
     </row>
     <row r="416" spans="2:2">
       <c r="B416" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
     </row>
     <row r="417" spans="2:2">
       <c r="B417" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
     </row>
     <row r="418" spans="2:2">
       <c r="B418" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
     </row>
     <row r="419" spans="2:2">
       <c r="B419" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
     </row>
     <row r="420" spans="2:2">
       <c r="B420" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
     </row>
     <row r="421" spans="2:2">
       <c r="B421" t="s">
-        <v>1100</v>
+        <v>763</v>
       </c>
     </row>
     <row r="422" spans="2:2">
       <c r="B422" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
     </row>
     <row r="423" spans="2:2">
       <c r="B423" t="s">
-        <v>769</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="424" spans="2:2">
       <c r="B424" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
     </row>
     <row r="425" spans="2:2">
       <c r="B425" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
     </row>
     <row r="426" spans="2:2">
       <c r="B426" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
     </row>
     <row r="427" spans="2:2">
       <c r="B427" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
     </row>
     <row r="428" spans="2:2">
       <c r="B428" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
     </row>
     <row r="429" spans="2:2">
       <c r="B429" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
     </row>
     <row r="430" spans="2:2">
       <c r="B430" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
     </row>
     <row r="431" spans="2:2">
       <c r="B431" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
     </row>
     <row r="432" spans="2:2">
       <c r="B432" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
     </row>
     <row r="433" spans="2:2">
       <c r="B433" t="s">
-        <v>790</v>
+        <v>785</v>
       </c>
     </row>
     <row r="434" spans="2:2">
       <c r="B434" t="s">
-        <v>793</v>
+        <v>788</v>
       </c>
     </row>
     <row r="435" spans="2:2">
       <c r="B435" t="s">
-        <v>795</v>
+        <v>790</v>
       </c>
     </row>
     <row r="436" spans="2:2">
       <c r="B436" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
     </row>
     <row r="437" spans="2:2">
       <c r="B437" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
     </row>
     <row r="438" spans="2:2">
       <c r="B438" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
     </row>
     <row r="439" spans="2:2">
       <c r="B439" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
     </row>
     <row r="440" spans="2:2">
       <c r="B440" t="s">
-        <v>1104</v>
+        <v>801</v>
       </c>
     </row>
     <row r="441" spans="2:2">
       <c r="B441" t="s">
-        <v>1108</v>
+        <v>803</v>
       </c>
     </row>
     <row r="442" spans="2:2">
       <c r="B442" t="s">
-        <v>805</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="443" spans="2:2">
       <c r="B443" t="s">
-        <v>807</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="444" spans="2:2">
       <c r="B444" t="s">
-        <v>1110</v>
+        <v>805</v>
       </c>
     </row>
     <row r="445" spans="2:2">
       <c r="B445" t="s">
-        <v>1018</v>
+        <v>807</v>
       </c>
     </row>
     <row r="446" spans="2:2">
       <c r="B446" t="s">
-        <v>809</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="447" spans="2:2">
       <c r="B447" t="s">
-        <v>811</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="448" spans="2:2">
       <c r="B448" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
     </row>
     <row r="449" spans="2:2">
       <c r="B449" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
     </row>
     <row r="450" spans="2:2">
       <c r="B450" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
     </row>
     <row r="451" spans="2:2">
       <c r="B451" t="s">
-        <v>1051</v>
+        <v>815</v>
       </c>
     </row>
     <row r="452" spans="2:2">
       <c r="B452" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
     </row>
     <row r="453" spans="2:2">
       <c r="B453" t="s">
-        <v>821</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="454" spans="2:2">
       <c r="B454" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
     </row>
     <row r="455" spans="2:2">
       <c r="B455" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
     </row>
     <row r="456" spans="2:2">
       <c r="B456" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
     </row>
     <row r="457" spans="2:2">
       <c r="B457" t="s">
-        <v>1053</v>
+        <v>825</v>
       </c>
     </row>
     <row r="458" spans="2:2">
       <c r="B458" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
     </row>
     <row r="459" spans="2:2">
       <c r="B459" t="s">
-        <v>831</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="460" spans="2:2">
       <c r="B460" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
     </row>
     <row r="461" spans="2:2">
       <c r="B461" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
     </row>
     <row r="462" spans="2:2">
       <c r="B462" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
     </row>
     <row r="463" spans="2:2">
       <c r="B463" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
     </row>
     <row r="464" spans="2:2">
       <c r="B464" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
     </row>
     <row r="465" spans="2:2">
       <c r="B465" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
     </row>
     <row r="466" spans="2:2">
       <c r="B466" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
     </row>
     <row r="467" spans="2:2">
       <c r="B467" t="s">
-        <v>1055</v>
+        <v>843</v>
       </c>
     </row>
     <row r="468" spans="2:2">
       <c r="B468" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="469" spans="2:2">
       <c r="B469" t="s">
-        <v>849</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="470" spans="2:2">
       <c r="B470" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
     </row>
     <row r="471" spans="2:2">
       <c r="B471" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
     </row>
     <row r="472" spans="2:2">
       <c r="B472" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
     </row>
     <row r="473" spans="2:2">
       <c r="B473" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
     </row>
     <row r="474" spans="2:2">
       <c r="B474" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
     </row>
     <row r="475" spans="2:2">
       <c r="B475" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
     </row>
     <row r="476" spans="2:2">
       <c r="B476" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
     </row>
     <row r="477" spans="2:2">
       <c r="B477" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
     </row>
     <row r="478" spans="2:2">
       <c r="B478" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
     </row>
     <row r="479" spans="2:2">
       <c r="B479" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
     </row>
     <row r="480" spans="2:2">
       <c r="B480" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
     </row>
     <row r="481" spans="2:2">
       <c r="B481" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
     </row>
     <row r="482" spans="2:2">
       <c r="B482" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
     </row>
     <row r="483" spans="2:2">
       <c r="B483" t="s">
-        <v>1021</v>
+        <v>873</v>
       </c>
     </row>
     <row r="484" spans="2:2">
       <c r="B484" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
     </row>
     <row r="485" spans="2:2">
       <c r="B485" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="486" spans="2:2">
       <c r="B486" t="s">
-        <v>1026</v>
+        <v>877</v>
       </c>
     </row>
     <row r="487" spans="2:2">
       <c r="B487" t="s">
-        <v>879</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="488" spans="2:2">
       <c r="B488" t="s">
-        <v>881</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="489" spans="2:2">
       <c r="B489" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="490" spans="2:2">
       <c r="B490" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
     </row>
     <row r="491" spans="2:2">
       <c r="B491" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
     </row>
     <row r="492" spans="2:2">
       <c r="B492" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
     </row>
     <row r="493" spans="2:2">
       <c r="B493" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
     </row>
     <row r="494" spans="2:2">
       <c r="B494" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
     </row>
     <row r="495" spans="2:2">
       <c r="B495" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
     </row>
     <row r="496" spans="2:2">
       <c r="B496" t="s">
-        <v>897</v>
+        <v>893</v>
       </c>
     </row>
     <row r="497" spans="2:2">
       <c r="B497" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
     </row>
     <row r="498" spans="2:2">
       <c r="B498" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
     </row>
     <row r="499" spans="2:2">
       <c r="B499" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
     </row>
     <row r="500" spans="2:2">
       <c r="B500" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
     </row>
     <row r="501" spans="2:2">
       <c r="B501" t="s">
-        <v>908</v>
+        <v>903</v>
       </c>
     </row>
     <row r="502" spans="2:2">
       <c r="B502" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
     </row>
     <row r="503" spans="2:2">
       <c r="B503" t="s">
-        <v>1086</v>
+        <v>908</v>
       </c>
     </row>
     <row r="504" spans="2:2">
       <c r="B504" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
     </row>
     <row r="505" spans="2:2">
       <c r="B505" t="s">
-        <v>914</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="506" spans="2:2">
       <c r="B506" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
     </row>
     <row r="507" spans="2:2">
       <c r="B507" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
     </row>
     <row r="508" spans="2:2">
       <c r="B508" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
     </row>
     <row r="509" spans="2:2">
       <c r="B509" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
     </row>
     <row r="510" spans="2:2">
       <c r="B510" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
     </row>
     <row r="511" spans="2:2">
       <c r="B511" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
     </row>
     <row r="512" spans="2:2">
       <c r="B512" t="s">
-        <v>928</v>
+        <v>924</v>
       </c>
     </row>
     <row r="513" spans="1:2">
       <c r="B513" t="s">
-        <v>930</v>
+        <v>926</v>
       </c>
     </row>
     <row r="514" spans="1:2">
       <c r="B514" t="s">
-        <v>933</v>
+        <v>928</v>
       </c>
     </row>
     <row r="515" spans="1:2">
       <c r="B515" t="s">
-        <v>935</v>
+        <v>930</v>
       </c>
     </row>
     <row r="516" spans="1:2">
       <c r="B516" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="517" spans="1:2">
+      <c r="B517" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="518" spans="1:2">
+      <c r="B518" t="s">
         <v>937</v>
       </c>
     </row>
-    <row r="518" spans="1:2">
-      <c r="A518" t="s">
-        <v>1116</v>
-      </c>
-      <c r="B518" t="s">
+    <row r="520" spans="1:2">
+      <c r="A520" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B520" t="s">
         <v>1070</v>
-      </c>
-    </row>
-    <row r="519" spans="1:2">
-      <c r="B519" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="520" spans="1:2">
-      <c r="B520" t="s">
-        <v>958</v>
       </c>
     </row>
     <row r="521" spans="1:2">
       <c r="B521" t="s">
-        <v>1079</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="522" spans="1:2">
       <c r="B522" t="s">
-        <v>972</v>
+        <v>958</v>
       </c>
     </row>
     <row r="523" spans="1:2">
       <c r="B523" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="524" spans="1:2">
+      <c r="B524" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="525" spans="1:2">
+      <c r="B525" t="s">
         <v>983</v>
-      </c>
-    </row>
-    <row r="525" spans="1:2">
-      <c r="A525" t="s">
-        <v>1117</v>
-      </c>
-      <c r="B525" t="s">
-        <v>1035</v>
       </c>
     </row>
     <row r="527" spans="1:2">
       <c r="A527" t="s">
-        <v>1118</v>
+        <v>1123</v>
       </c>
       <c r="B527" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="529" spans="1:2">
+      <c r="A529" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B529" t="s">
         <v>955</v>
       </c>
     </row>
-    <row r="528" spans="1:2">
-      <c r="B528" t="s">
+    <row r="530" spans="1:2">
+      <c r="B530" t="s">
         <v>1015</v>
       </c>
     </row>

--- a/pdb/nsp3/SARS-CoV-2/domains_and_infos_of_nsp3.xlsx
+++ b/pdb/nsp3/SARS-CoV-2/domains_and_infos_of_nsp3.xlsx
@@ -17,11 +17,11 @@
     <sheet name="nsp3_PL2pro_" sheetId="8" r:id="rId8"/>
     <sheet name="nsp3_Macro1_nsp3_PL2pro_" sheetId="9" r:id="rId9"/>
     <sheet name="nsp3_Macro3_" sheetId="10" r:id="rId10"/>
-    <sheet name="nsp3_Y3_" sheetId="11" r:id="rId11"/>
-    <sheet name="None" sheetId="12" r:id="rId12"/>
-    <sheet name="nsp3_DPUP_" sheetId="13" r:id="rId13"/>
-    <sheet name="nsp3_PL2pro_nsp3_Ubl2_" sheetId="14" r:id="rId14"/>
-    <sheet name="nsp3_Ubl1_" sheetId="15" r:id="rId15"/>
+    <sheet name="nsp3_Ubl1_" sheetId="11" r:id="rId11"/>
+    <sheet name="nsp3_Y3_" sheetId="12" r:id="rId12"/>
+    <sheet name="None" sheetId="13" r:id="rId13"/>
+    <sheet name="nsp3_DPUP_" sheetId="14" r:id="rId14"/>
+    <sheet name="nsp3_PL2pro_nsp3_Ubl2_" sheetId="15" r:id="rId15"/>
     <sheet name="Organisms" sheetId="16" r:id="rId16"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2686" uniqueCount="1125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2691" uniqueCount="1128">
   <si>
     <t>nsp3_Macro1_</t>
   </si>
@@ -3322,6 +3322,33 @@
     <t>CRYSTAL STRUCTURE OF SARS-COV-2 NSP3 MACRODOMAIN 3 (SARS-UNIQUE DOMAIN-M) IN COMPLEX WITH OXAPROZIN</t>
   </si>
   <si>
+    <t>nsp3_Ubl1_</t>
+  </si>
+  <si>
+    <t>8hda</t>
+  </si>
+  <si>
+    <t>CRYSTAL STRUCTURE OF UBL1 (RESIDUES 18-111) OF SARS-COV-2</t>
+  </si>
+  <si>
+    <t>2022-11-03</t>
+  </si>
+  <si>
+    <t>7kag</t>
+  </si>
+  <si>
+    <t>CRYSTAL STRUCTURE OF THE UBIQUITIN-LIKE DOMAIN 1 (UBL1) OF NSP3 FROM SARS-COV-2</t>
+  </si>
+  <si>
+    <t>7ti9</t>
+  </si>
+  <si>
+    <t>CRYSTAL STRUCTURE OF THE UBIQUITIN-LIKE DOMAIN 1 (UBL1) OF NSP3 FROM SARS-COV-2, FORM 2</t>
+  </si>
+  <si>
+    <t>2022-01-13</t>
+  </si>
+  <si>
     <t>nsp3_Y3_</t>
   </si>
   <si>
@@ -3368,24 +3395,6 @@
   </si>
   <si>
     <t>2021-03-09</t>
-  </si>
-  <si>
-    <t>nsp3_Ubl1_</t>
-  </si>
-  <si>
-    <t>7kag</t>
-  </si>
-  <si>
-    <t>CRYSTAL STRUCTURE OF THE UBIQUITIN-LIKE DOMAIN 1 (UBL1) OF NSP3 FROM SARS-COV-2</t>
-  </si>
-  <si>
-    <t>7ti9</t>
-  </si>
-  <si>
-    <t>CRYSTAL STRUCTURE OF THE UBIQUITIN-LIKE DOMAIN 1 (UBL1) OF NSP3 FROM SARS-COV-2, FORM 2</t>
-  </si>
-  <si>
-    <t>2022-01-13</t>
   </si>
   <si>
     <t>Lists all PDBs which contain sequences of a certain organism.</t>
@@ -11561,7 +11570,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="110.7109375" customWidth="1"/>
@@ -11596,7 +11605,7 @@
         <v>1098</v>
       </c>
       <c r="B3">
-        <v>2.17</v>
+        <v>1.93</v>
       </c>
       <c r="C3" t="s">
         <v>1099</v>
@@ -11606,6 +11615,40 @@
       </c>
       <c r="E3" t="s">
         <v>1100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B4">
+        <v>3.21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1102</v>
+      </c>
+      <c r="D4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B5">
+        <v>2.73</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" t="s">
+        <v>1105</v>
       </c>
     </row>
   </sheetData>
@@ -11625,7 +11668,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>1101</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -11647,19 +11690,19 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>1102</v>
+        <v>1107</v>
       </c>
       <c r="B3">
-        <v>2.72</v>
+        <v>2.17</v>
       </c>
       <c r="C3" t="s">
-        <v>1103</v>
+        <v>1108</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>1104</v>
+        <v>1109</v>
       </c>
     </row>
   </sheetData>
@@ -11679,7 +11722,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>1105</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -11701,19 +11744,19 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>1106</v>
+        <v>1111</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="C3" t="s">
-        <v>1107</v>
+        <v>1112</v>
       </c>
       <c r="D3" t="s">
-        <v>1108</v>
+        <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>960</v>
+        <v>1113</v>
       </c>
     </row>
   </sheetData>
@@ -11733,7 +11776,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>1109</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -11755,19 +11798,19 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>1110</v>
+        <v>1115</v>
       </c>
       <c r="B3">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>1111</v>
+        <v>1116</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>1117</v>
       </c>
       <c r="E3" t="s">
-        <v>1112</v>
+        <v>960</v>
       </c>
     </row>
   </sheetData>
@@ -11777,7 +11820,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="110.7109375" customWidth="1"/>
@@ -11787,7 +11830,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>1113</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -11809,36 +11852,19 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>1114</v>
+        <v>1119</v>
       </c>
       <c r="B3">
-        <v>3.21</v>
+        <v>2.68</v>
       </c>
       <c r="C3" t="s">
-        <v>1115</v>
+        <v>1120</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>987</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" t="s">
-        <v>1116</v>
-      </c>
-      <c r="B4">
-        <v>2.73</v>
-      </c>
-      <c r="C4" t="s">
-        <v>1117</v>
-      </c>
-      <c r="D4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" t="s">
-        <v>1118</v>
+        <v>1121</v>
       </c>
     </row>
   </sheetData>
@@ -11848,7 +11874,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B530"/>
+  <dimension ref="A1:B531"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.7109375" customWidth="1"/>
@@ -11856,12 +11882,12 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>1119</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>1120</v>
+        <v>1123</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
@@ -11869,7 +11895,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>1121</v>
+        <v>1124</v>
       </c>
       <c r="B3" t="s">
         <v>6</v>
@@ -12872,1635 +12898,1640 @@
     </row>
     <row r="203" spans="2:2">
       <c r="B203" t="s">
-        <v>967</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="204" spans="2:2">
       <c r="B204" t="s">
-        <v>381</v>
+        <v>967</v>
       </c>
     </row>
     <row r="205" spans="2:2">
       <c r="B205" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="206" spans="2:2">
       <c r="B206" t="s">
-        <v>969</v>
+        <v>383</v>
       </c>
     </row>
     <row r="207" spans="2:2">
       <c r="B207" t="s">
-        <v>385</v>
+        <v>969</v>
       </c>
     </row>
     <row r="208" spans="2:2">
       <c r="B208" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="209" spans="2:2">
       <c r="B209" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
     </row>
     <row r="210" spans="2:2">
       <c r="B210" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="211" spans="2:2">
       <c r="B211" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="212" spans="2:2">
       <c r="B212" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="213" spans="2:2">
       <c r="B213" t="s">
-        <v>972</v>
+        <v>397</v>
       </c>
     </row>
     <row r="214" spans="2:2">
       <c r="B214" t="s">
-        <v>399</v>
+        <v>972</v>
       </c>
     </row>
     <row r="215" spans="2:2">
       <c r="B215" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="216" spans="2:2">
       <c r="B216" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="217" spans="2:2">
       <c r="B217" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="218" spans="2:2">
       <c r="B218" t="s">
-        <v>1081</v>
+        <v>405</v>
       </c>
     </row>
     <row r="219" spans="2:2">
       <c r="B219" t="s">
-        <v>407</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="220" spans="2:2">
       <c r="B220" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="221" spans="2:2">
       <c r="B221" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="222" spans="2:2">
       <c r="B222" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="223" spans="2:2">
       <c r="B223" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="224" spans="2:2">
       <c r="B224" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="225" spans="2:2">
       <c r="B225" t="s">
-        <v>1041</v>
+        <v>417</v>
       </c>
     </row>
     <row r="226" spans="2:2">
       <c r="B226" t="s">
-        <v>419</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="227" spans="2:2">
       <c r="B227" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="228" spans="2:2">
       <c r="B228" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="229" spans="2:2">
       <c r="B229" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="230" spans="2:2">
       <c r="B230" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="231" spans="2:2">
       <c r="B231" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="232" spans="2:2">
       <c r="B232" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="233" spans="2:2">
       <c r="B233" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
     </row>
     <row r="234" spans="2:2">
       <c r="B234" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="235" spans="2:2">
       <c r="B235" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="236" spans="2:2">
       <c r="B236" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="237" spans="2:2">
       <c r="B237" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="238" spans="2:2">
       <c r="B238" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="239" spans="2:2">
       <c r="B239" t="s">
-        <v>975</v>
+        <v>444</v>
       </c>
     </row>
     <row r="240" spans="2:2">
       <c r="B240" t="s">
-        <v>446</v>
+        <v>975</v>
       </c>
     </row>
     <row r="241" spans="2:2">
       <c r="B241" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="242" spans="2:2">
       <c r="B242" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="243" spans="2:2">
       <c r="B243" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="244" spans="2:2">
       <c r="B244" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="245" spans="2:2">
       <c r="B245" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="246" spans="2:2">
       <c r="B246" t="s">
-        <v>977</v>
+        <v>456</v>
       </c>
     </row>
     <row r="247" spans="2:2">
       <c r="B247" t="s">
-        <v>458</v>
+        <v>977</v>
       </c>
     </row>
     <row r="248" spans="2:2">
       <c r="B248" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="249" spans="2:2">
       <c r="B249" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="250" spans="2:2">
       <c r="B250" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="251" spans="2:2">
       <c r="B251" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="252" spans="2:2">
       <c r="B252" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="253" spans="2:2">
       <c r="B253" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="254" spans="2:2">
       <c r="B254" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="255" spans="2:2">
       <c r="B255" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="256" spans="2:2">
       <c r="B256" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="257" spans="2:2">
       <c r="B257" t="s">
-        <v>980</v>
+        <v>476</v>
       </c>
     </row>
     <row r="258" spans="2:2">
       <c r="B258" t="s">
-        <v>478</v>
+        <v>980</v>
       </c>
     </row>
     <row r="259" spans="2:2">
       <c r="B259" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="260" spans="2:2">
       <c r="B260" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="261" spans="2:2">
       <c r="B261" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="262" spans="2:2">
       <c r="B262" t="s">
-        <v>1098</v>
+        <v>484</v>
       </c>
     </row>
     <row r="263" spans="2:2">
       <c r="B263" t="s">
-        <v>486</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="264" spans="2:2">
       <c r="B264" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="265" spans="2:2">
       <c r="B265" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="266" spans="2:2">
       <c r="B266" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="267" spans="2:2">
       <c r="B267" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="268" spans="2:2">
       <c r="B268" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="269" spans="2:2">
       <c r="B269" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="270" spans="2:2">
       <c r="B270" t="s">
-        <v>983</v>
+        <v>498</v>
       </c>
     </row>
     <row r="271" spans="2:2">
       <c r="B271" t="s">
-        <v>500</v>
+        <v>983</v>
       </c>
     </row>
     <row r="272" spans="2:2">
       <c r="B272" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="273" spans="2:2">
       <c r="B273" t="s">
-        <v>985</v>
+        <v>502</v>
       </c>
     </row>
     <row r="274" spans="2:2">
       <c r="B274" t="s">
-        <v>503</v>
+        <v>985</v>
       </c>
     </row>
     <row r="275" spans="2:2">
       <c r="B275" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="276" spans="2:2">
       <c r="B276" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="277" spans="2:2">
       <c r="B277" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="278" spans="2:2">
       <c r="B278" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="279" spans="2:2">
       <c r="B279" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="280" spans="2:2">
       <c r="B280" t="s">
-        <v>1044</v>
+        <v>513</v>
       </c>
     </row>
     <row r="281" spans="2:2">
       <c r="B281" t="s">
-        <v>988</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="282" spans="2:2">
       <c r="B282" t="s">
-        <v>515</v>
+        <v>988</v>
       </c>
     </row>
     <row r="283" spans="2:2">
       <c r="B283" t="s">
-        <v>991</v>
+        <v>515</v>
       </c>
     </row>
     <row r="284" spans="2:2">
       <c r="B284" t="s">
-        <v>516</v>
+        <v>991</v>
       </c>
     </row>
     <row r="285" spans="2:2">
       <c r="B285" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="286" spans="2:2">
       <c r="B286" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="287" spans="2:2">
       <c r="B287" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="288" spans="2:2">
       <c r="B288" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="289" spans="2:2">
       <c r="B289" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="290" spans="2:2">
       <c r="B290" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="291" spans="2:2">
       <c r="B291" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="292" spans="2:2">
       <c r="B292" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="293" spans="2:2">
       <c r="B293" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="294" spans="2:2">
       <c r="B294" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="295" spans="2:2">
       <c r="B295" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="296" spans="2:2">
       <c r="B296" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
     </row>
     <row r="297" spans="2:2">
       <c r="B297" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="298" spans="2:2">
       <c r="B298" t="s">
-        <v>1047</v>
+        <v>543</v>
       </c>
     </row>
     <row r="299" spans="2:2">
       <c r="B299" t="s">
-        <v>545</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="300" spans="2:2">
       <c r="B300" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="301" spans="2:2">
       <c r="B301" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="302" spans="2:2">
       <c r="B302" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="303" spans="2:2">
       <c r="B303" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="304" spans="2:2">
       <c r="B304" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="305" spans="2:2">
       <c r="B305" t="s">
-        <v>993</v>
+        <v>555</v>
       </c>
     </row>
     <row r="306" spans="2:2">
       <c r="B306" t="s">
-        <v>557</v>
+        <v>993</v>
       </c>
     </row>
     <row r="307" spans="2:2">
       <c r="B307" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
     </row>
     <row r="308" spans="2:2">
       <c r="B308" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="309" spans="2:2">
       <c r="B309" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="310" spans="2:2">
       <c r="B310" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="311" spans="2:2">
       <c r="B311" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
     </row>
     <row r="312" spans="2:2">
       <c r="B312" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="313" spans="2:2">
       <c r="B313" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
     <row r="314" spans="2:2">
       <c r="B314" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="315" spans="2:2">
       <c r="B315" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="316" spans="2:2">
       <c r="B316" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="317" spans="2:2">
       <c r="B317" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="318" spans="2:2">
       <c r="B318" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
     </row>
     <row r="319" spans="2:2">
       <c r="B319" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="320" spans="2:2">
       <c r="B320" t="s">
-        <v>996</v>
+        <v>582</v>
       </c>
     </row>
     <row r="321" spans="2:2">
       <c r="B321" t="s">
-        <v>585</v>
+        <v>996</v>
       </c>
     </row>
     <row r="322" spans="2:2">
       <c r="B322" t="s">
-        <v>999</v>
+        <v>585</v>
       </c>
     </row>
     <row r="323" spans="2:2">
       <c r="B323" t="s">
-        <v>587</v>
+        <v>999</v>
       </c>
     </row>
     <row r="324" spans="2:2">
       <c r="B324" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
     </row>
     <row r="325" spans="2:2">
       <c r="B325" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="326" spans="2:2">
       <c r="B326" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
     </row>
     <row r="327" spans="2:2">
       <c r="B327" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="328" spans="2:2">
       <c r="B328" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
     </row>
     <row r="329" spans="2:2">
       <c r="B329" t="s">
-        <v>1083</v>
+        <v>596</v>
       </c>
     </row>
     <row r="330" spans="2:2">
       <c r="B330" t="s">
-        <v>598</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="331" spans="2:2">
       <c r="B331" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
     </row>
     <row r="332" spans="2:2">
       <c r="B332" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="333" spans="2:2">
       <c r="B333" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="334" spans="2:2">
       <c r="B334" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
     </row>
     <row r="335" spans="2:2">
       <c r="B335" t="s">
-        <v>1102</v>
+        <v>606</v>
       </c>
     </row>
     <row r="336" spans="2:2">
       <c r="B336" t="s">
-        <v>608</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="337" spans="2:2">
       <c r="B337" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="338" spans="2:2">
       <c r="B338" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="339" spans="2:2">
       <c r="B339" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="340" spans="2:2">
       <c r="B340" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="341" spans="2:2">
       <c r="B341" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="342" spans="2:2">
       <c r="B342" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="343" spans="2:2">
       <c r="B343" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="344" spans="2:2">
       <c r="B344" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
     </row>
     <row r="345" spans="2:2">
       <c r="B345" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
     </row>
     <row r="346" spans="2:2">
       <c r="B346" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
     </row>
     <row r="347" spans="2:2">
       <c r="B347" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
     </row>
     <row r="348" spans="2:2">
       <c r="B348" t="s">
-        <v>1002</v>
+        <v>630</v>
       </c>
     </row>
     <row r="349" spans="2:2">
       <c r="B349" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="350" spans="2:2">
       <c r="B350" t="s">
-        <v>632</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="351" spans="2:2">
       <c r="B351" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="352" spans="2:2">
       <c r="B352" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
     </row>
     <row r="353" spans="2:2">
       <c r="B353" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
     </row>
     <row r="354" spans="2:2">
       <c r="B354" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
     </row>
     <row r="355" spans="2:2">
       <c r="B355" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
     </row>
     <row r="356" spans="2:2">
       <c r="B356" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
     </row>
     <row r="357" spans="2:2">
       <c r="B357" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
     </row>
     <row r="358" spans="2:2">
       <c r="B358" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
     </row>
     <row r="359" spans="2:2">
       <c r="B359" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
     </row>
     <row r="360" spans="2:2">
       <c r="B360" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
     </row>
     <row r="361" spans="2:2">
       <c r="B361" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
     </row>
     <row r="362" spans="2:2">
       <c r="B362" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
     </row>
     <row r="363" spans="2:2">
       <c r="B363" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
     </row>
     <row r="364" spans="2:2">
       <c r="B364" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
     </row>
     <row r="365" spans="2:2">
       <c r="B365" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
     </row>
     <row r="366" spans="2:2">
       <c r="B366" t="s">
-        <v>1049</v>
+        <v>664</v>
       </c>
     </row>
     <row r="367" spans="2:2">
       <c r="B367" t="s">
-        <v>1008</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="368" spans="2:2">
       <c r="B368" t="s">
-        <v>665</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="369" spans="2:2">
       <c r="B369" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
     </row>
     <row r="370" spans="2:2">
       <c r="B370" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="371" spans="2:2">
       <c r="B371" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
     </row>
     <row r="372" spans="2:2">
       <c r="B372" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
     </row>
     <row r="373" spans="2:2">
       <c r="B373" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
     </row>
     <row r="374" spans="2:2">
       <c r="B374" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
     </row>
     <row r="375" spans="2:2">
       <c r="B375" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
     </row>
     <row r="376" spans="2:2">
       <c r="B376" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
     </row>
     <row r="377" spans="2:2">
       <c r="B377" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
     </row>
     <row r="378" spans="2:2">
       <c r="B378" t="s">
-        <v>1010</v>
+        <v>683</v>
       </c>
     </row>
     <row r="379" spans="2:2">
       <c r="B379" t="s">
-        <v>685</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="380" spans="2:2">
       <c r="B380" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
     </row>
     <row r="381" spans="2:2">
       <c r="B381" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
     </row>
     <row r="382" spans="2:2">
       <c r="B382" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
     </row>
     <row r="383" spans="2:2">
       <c r="B383" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
     </row>
     <row r="384" spans="2:2">
       <c r="B384" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
     </row>
     <row r="385" spans="2:2">
       <c r="B385" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
     </row>
     <row r="386" spans="2:2">
       <c r="B386" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
     </row>
     <row r="387" spans="2:2">
       <c r="B387" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="388" spans="2:2">
       <c r="B388" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
     </row>
     <row r="389" spans="2:2">
       <c r="B389" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
     </row>
     <row r="390" spans="2:2">
       <c r="B390" t="s">
-        <v>1012</v>
+        <v>706</v>
       </c>
     </row>
     <row r="391" spans="2:2">
       <c r="B391" t="s">
-        <v>708</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="392" spans="2:2">
       <c r="B392" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
     </row>
     <row r="393" spans="2:2">
       <c r="B393" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
     </row>
     <row r="394" spans="2:2">
       <c r="B394" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="395" spans="2:2">
       <c r="B395" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
     </row>
     <row r="396" spans="2:2">
       <c r="B396" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
     </row>
     <row r="397" spans="2:2">
       <c r="B397" t="s">
-        <v>1095</v>
+        <v>718</v>
       </c>
     </row>
     <row r="398" spans="2:2">
       <c r="B398" t="s">
-        <v>720</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="399" spans="2:2">
       <c r="B399" t="s">
-        <v>1015</v>
+        <v>720</v>
       </c>
     </row>
     <row r="400" spans="2:2">
       <c r="B400" t="s">
-        <v>722</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="401" spans="2:2">
       <c r="B401" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="402" spans="2:2">
       <c r="B402" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
     </row>
     <row r="403" spans="2:2">
       <c r="B403" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
     </row>
     <row r="404" spans="2:2">
       <c r="B404" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
     </row>
     <row r="405" spans="2:2">
       <c r="B405" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
     </row>
     <row r="406" spans="2:2">
       <c r="B406" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
     </row>
     <row r="407" spans="2:2">
       <c r="B407" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
     </row>
     <row r="408" spans="2:2">
       <c r="B408" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
     </row>
     <row r="409" spans="2:2">
       <c r="B409" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
     </row>
     <row r="410" spans="2:2">
       <c r="B410" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
     </row>
     <row r="411" spans="2:2">
       <c r="B411" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
     </row>
     <row r="412" spans="2:2">
       <c r="B412" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
     </row>
     <row r="413" spans="2:2">
       <c r="B413" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
     </row>
     <row r="414" spans="2:2">
       <c r="B414" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
     </row>
     <row r="415" spans="2:2">
       <c r="B415" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
     </row>
     <row r="416" spans="2:2">
       <c r="B416" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
     </row>
     <row r="417" spans="2:2">
       <c r="B417" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
     </row>
     <row r="418" spans="2:2">
       <c r="B418" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
     </row>
     <row r="419" spans="2:2">
       <c r="B419" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
     </row>
     <row r="420" spans="2:2">
       <c r="B420" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
     </row>
     <row r="421" spans="2:2">
       <c r="B421" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
     </row>
     <row r="422" spans="2:2">
       <c r="B422" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
     </row>
     <row r="423" spans="2:2">
       <c r="B423" t="s">
-        <v>1106</v>
+        <v>765</v>
       </c>
     </row>
     <row r="424" spans="2:2">
       <c r="B424" t="s">
-        <v>767</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="425" spans="2:2">
       <c r="B425" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
     </row>
     <row r="426" spans="2:2">
       <c r="B426" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
     </row>
     <row r="427" spans="2:2">
       <c r="B427" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
     </row>
     <row r="428" spans="2:2">
       <c r="B428" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
     </row>
     <row r="429" spans="2:2">
       <c r="B429" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
     </row>
     <row r="430" spans="2:2">
       <c r="B430" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
     </row>
     <row r="431" spans="2:2">
       <c r="B431" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="432" spans="2:2">
       <c r="B432" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
     </row>
     <row r="433" spans="2:2">
       <c r="B433" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="434" spans="2:2">
       <c r="B434" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
     </row>
     <row r="435" spans="2:2">
       <c r="B435" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
     <row r="436" spans="2:2">
       <c r="B436" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
     </row>
     <row r="437" spans="2:2">
       <c r="B437" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
     </row>
     <row r="438" spans="2:2">
       <c r="B438" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
     </row>
     <row r="439" spans="2:2">
       <c r="B439" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
     </row>
     <row r="440" spans="2:2">
       <c r="B440" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
     </row>
     <row r="441" spans="2:2">
       <c r="B441" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
     </row>
     <row r="442" spans="2:2">
       <c r="B442" t="s">
-        <v>1110</v>
+        <v>803</v>
       </c>
     </row>
     <row r="443" spans="2:2">
       <c r="B443" t="s">
-        <v>1114</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="444" spans="2:2">
       <c r="B444" t="s">
-        <v>805</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="445" spans="2:2">
       <c r="B445" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
     </row>
     <row r="446" spans="2:2">
       <c r="B446" t="s">
-        <v>1116</v>
+        <v>807</v>
       </c>
     </row>
     <row r="447" spans="2:2">
       <c r="B447" t="s">
-        <v>1018</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="448" spans="2:2">
       <c r="B448" t="s">
-        <v>809</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="449" spans="2:2">
       <c r="B449" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
     </row>
     <row r="450" spans="2:2">
       <c r="B450" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
     </row>
     <row r="451" spans="2:2">
       <c r="B451" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
     </row>
     <row r="452" spans="2:2">
       <c r="B452" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
     </row>
     <row r="453" spans="2:2">
       <c r="B453" t="s">
-        <v>1051</v>
+        <v>817</v>
       </c>
     </row>
     <row r="454" spans="2:2">
       <c r="B454" t="s">
-        <v>819</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="455" spans="2:2">
       <c r="B455" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
     </row>
     <row r="456" spans="2:2">
       <c r="B456" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
     </row>
     <row r="457" spans="2:2">
       <c r="B457" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
     </row>
     <row r="458" spans="2:2">
       <c r="B458" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
     </row>
     <row r="459" spans="2:2">
       <c r="B459" t="s">
-        <v>1053</v>
+        <v>827</v>
       </c>
     </row>
     <row r="460" spans="2:2">
       <c r="B460" t="s">
-        <v>829</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="461" spans="2:2">
       <c r="B461" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="462" spans="2:2">
       <c r="B462" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
     </row>
     <row r="463" spans="2:2">
       <c r="B463" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
     </row>
     <row r="464" spans="2:2">
       <c r="B464" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
     </row>
     <row r="465" spans="2:2">
       <c r="B465" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
     </row>
     <row r="466" spans="2:2">
       <c r="B466" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="467" spans="2:2">
       <c r="B467" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="468" spans="2:2">
       <c r="B468" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
     </row>
     <row r="469" spans="2:2">
       <c r="B469" t="s">
-        <v>1055</v>
+        <v>845</v>
       </c>
     </row>
     <row r="470" spans="2:2">
       <c r="B470" t="s">
-        <v>847</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="471" spans="2:2">
       <c r="B471" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
     </row>
     <row r="472" spans="2:2">
       <c r="B472" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
     </row>
     <row r="473" spans="2:2">
       <c r="B473" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
     </row>
     <row r="474" spans="2:2">
       <c r="B474" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="475" spans="2:2">
       <c r="B475" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
     </row>
     <row r="476" spans="2:2">
       <c r="B476" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
     </row>
     <row r="477" spans="2:2">
       <c r="B477" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
     </row>
     <row r="478" spans="2:2">
       <c r="B478" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
     </row>
     <row r="479" spans="2:2">
       <c r="B479" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
     </row>
     <row r="480" spans="2:2">
       <c r="B480" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
     </row>
     <row r="481" spans="2:2">
       <c r="B481" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
     </row>
     <row r="482" spans="2:2">
       <c r="B482" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
     </row>
     <row r="483" spans="2:2">
       <c r="B483" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
     </row>
     <row r="484" spans="2:2">
       <c r="B484" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
     </row>
     <row r="485" spans="2:2">
       <c r="B485" t="s">
-        <v>1021</v>
+        <v>875</v>
       </c>
     </row>
     <row r="486" spans="2:2">
       <c r="B486" t="s">
-        <v>877</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="487" spans="2:2">
       <c r="B487" t="s">
-        <v>1023</v>
+        <v>877</v>
       </c>
     </row>
     <row r="488" spans="2:2">
       <c r="B488" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="489" spans="2:2">
       <c r="B489" t="s">
-        <v>879</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="490" spans="2:2">
       <c r="B490" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
     </row>
     <row r="491" spans="2:2">
       <c r="B491" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
     </row>
     <row r="492" spans="2:2">
       <c r="B492" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
     </row>
     <row r="493" spans="2:2">
       <c r="B493" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
     </row>
     <row r="494" spans="2:2">
       <c r="B494" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
     </row>
     <row r="495" spans="2:2">
       <c r="B495" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
     </row>
     <row r="496" spans="2:2">
       <c r="B496" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
     </row>
     <row r="497" spans="2:2">
       <c r="B497" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
     </row>
     <row r="498" spans="2:2">
       <c r="B498" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
     </row>
     <row r="499" spans="2:2">
       <c r="B499" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
     </row>
     <row r="500" spans="2:2">
       <c r="B500" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
     </row>
     <row r="501" spans="2:2">
       <c r="B501" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
     </row>
     <row r="502" spans="2:2">
       <c r="B502" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
     </row>
     <row r="503" spans="2:2">
       <c r="B503" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
     </row>
     <row r="504" spans="2:2">
       <c r="B504" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="505" spans="2:2">
       <c r="B505" t="s">
-        <v>1086</v>
+        <v>910</v>
       </c>
     </row>
     <row r="506" spans="2:2">
       <c r="B506" t="s">
-        <v>912</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="507" spans="2:2">
       <c r="B507" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
     </row>
     <row r="508" spans="2:2">
       <c r="B508" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
     </row>
     <row r="509" spans="2:2">
       <c r="B509" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
     </row>
     <row r="510" spans="2:2">
       <c r="B510" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
     </row>
     <row r="511" spans="2:2">
       <c r="B511" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
     </row>
     <row r="512" spans="2:2">
       <c r="B512" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
     </row>
     <row r="513" spans="1:2">
       <c r="B513" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
     </row>
     <row r="514" spans="1:2">
       <c r="B514" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="515" spans="1:2">
       <c r="B515" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
     </row>
     <row r="516" spans="1:2">
       <c r="B516" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
     </row>
     <row r="517" spans="1:2">
       <c r="B517" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
     </row>
     <row r="518" spans="1:2">
       <c r="B518" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="519" spans="1:2">
+      <c r="B519" t="s">
         <v>937</v>
       </c>
     </row>
-    <row r="520" spans="1:2">
-      <c r="A520" t="s">
-        <v>1122</v>
-      </c>
-      <c r="B520" t="s">
-        <v>1070</v>
-      </c>
-    </row>
     <row r="521" spans="1:2">
+      <c r="A521" t="s">
+        <v>1125</v>
+      </c>
       <c r="B521" t="s">
         <v>1070</v>
       </c>
     </row>
     <row r="522" spans="1:2">
       <c r="B522" t="s">
-        <v>958</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="523" spans="1:2">
       <c r="B523" t="s">
-        <v>1079</v>
+        <v>958</v>
       </c>
     </row>
     <row r="524" spans="1:2">
       <c r="B524" t="s">
-        <v>972</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="525" spans="1:2">
       <c r="B525" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="526" spans="1:2">
+      <c r="B526" t="s">
         <v>983</v>
       </c>
     </row>
-    <row r="527" spans="1:2">
-      <c r="A527" t="s">
-        <v>1123</v>
-      </c>
-      <c r="B527" t="s">
+    <row r="528" spans="1:2">
+      <c r="A528" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B528" t="s">
         <v>1035</v>
       </c>
     </row>
-    <row r="529" spans="1:2">
-      <c r="A529" t="s">
-        <v>1124</v>
-      </c>
-      <c r="B529" t="s">
+    <row r="530" spans="1:2">
+      <c r="A530" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B530" t="s">
         <v>955</v>
       </c>
     </row>
-    <row r="530" spans="1:2">
-      <c r="B530" t="s">
+    <row r="531" spans="1:2">
+      <c r="B531" t="s">
         <v>1015</v>
       </c>
     </row>

--- a/pdb/nsp3/SARS-CoV-2/domains_and_infos_of_nsp3.xlsx
+++ b/pdb/nsp3/SARS-CoV-2/domains_and_infos_of_nsp3.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2691" uniqueCount="1128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2697" uniqueCount="1131">
   <si>
     <t>nsp3_Macro1_</t>
   </si>
@@ -2930,6 +2930,15 @@
   </si>
   <si>
     <t>2020-05-14</t>
+  </si>
+  <si>
+    <t>8cx9</t>
+  </si>
+  <si>
+    <t>STRUCTURE OF THE SARS-COV2 PLPRO (C111S) IN COMPLEX WITH A DIMERIC UBV THAT INHIBITS ACTIVITY BY AN UNUSUAL ALLOSTERIC MECHANISM</t>
+  </si>
+  <si>
+    <t>2022-05-20</t>
   </si>
   <si>
     <t>6wrh</t>
@@ -4731,7 +4740,7 @@
         <v>130</v>
       </c>
       <c r="B59">
-        <v>0.9399999999999999</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="C59" t="s">
         <v>131</v>
@@ -6108,7 +6117,7 @@
         <v>296</v>
       </c>
       <c r="B140">
-        <v>0.95</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="C140" t="s">
         <v>297</v>
@@ -9168,7 +9177,7 @@
         <v>661</v>
       </c>
       <c r="B320">
-        <v>0.96</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="C320" t="s">
         <v>662</v>
@@ -9457,7 +9466,7 @@
         <v>695</v>
       </c>
       <c r="B337">
-        <v>0.85</v>
+        <v>0.8500000000000001</v>
       </c>
       <c r="C337" t="s">
         <v>696</v>
@@ -10545,7 +10554,7 @@
         <v>825</v>
       </c>
       <c r="B401">
-        <v>0.88</v>
+        <v>0.8800000000000001</v>
       </c>
       <c r="C401" t="s">
         <v>826</v>
@@ -11089,7 +11098,7 @@
         <v>889</v>
       </c>
       <c r="B433">
-        <v>0.84</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="C433" t="s">
         <v>890</v>
@@ -11509,7 +11518,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>1091</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -11531,36 +11540,36 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>1092</v>
+        <v>1095</v>
       </c>
       <c r="B3">
         <v>1.7</v>
       </c>
       <c r="C3" t="s">
-        <v>1093</v>
+        <v>1096</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>1094</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>1095</v>
+        <v>1098</v>
       </c>
       <c r="B4">
         <v>2.1</v>
       </c>
       <c r="C4" t="s">
-        <v>1096</v>
+        <v>1099</v>
       </c>
       <c r="D4" t="s">
         <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>1094</v>
+        <v>1097</v>
       </c>
     </row>
   </sheetData>
@@ -11580,7 +11589,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>1097</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -11602,53 +11611,53 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>1098</v>
+        <v>1101</v>
       </c>
       <c r="B3">
         <v>1.93</v>
       </c>
       <c r="C3" t="s">
-        <v>1099</v>
+        <v>1102</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>1100</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="B4">
         <v>3.21</v>
       </c>
       <c r="C4" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
       <c r="D4" t="s">
         <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>1103</v>
+        <v>1106</v>
       </c>
       <c r="B5">
         <v>2.73</v>
       </c>
       <c r="C5" t="s">
-        <v>1104</v>
+        <v>1107</v>
       </c>
       <c r="D5" t="s">
         <v>8</v>
       </c>
       <c r="E5" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
     </row>
   </sheetData>
@@ -11668,7 +11677,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -11690,19 +11699,19 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
       <c r="B3">
         <v>2.17</v>
       </c>
       <c r="C3" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
     </row>
   </sheetData>
@@ -11722,7 +11731,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>1110</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -11744,19 +11753,19 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="B3">
         <v>2.72</v>
       </c>
       <c r="C3" t="s">
-        <v>1112</v>
+        <v>1115</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>1113</v>
+        <v>1116</v>
       </c>
     </row>
   </sheetData>
@@ -11776,7 +11785,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>1114</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -11798,16 +11807,16 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>1115</v>
+        <v>1118</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>1116</v>
+        <v>1119</v>
       </c>
       <c r="D3" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
       <c r="E3" t="s">
         <v>960</v>
@@ -11830,7 +11839,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>1118</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -11852,19 +11861,19 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>1119</v>
+        <v>1122</v>
       </c>
       <c r="B3">
         <v>2.68</v>
       </c>
       <c r="C3" t="s">
-        <v>1120</v>
+        <v>1123</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>1121</v>
+        <v>1124</v>
       </c>
     </row>
   </sheetData>
@@ -11874,7 +11883,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B531"/>
+  <dimension ref="A1:B533"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.7109375" customWidth="1"/>
@@ -11882,12 +11891,12 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>1123</v>
+        <v>1126</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
@@ -11895,7 +11904,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>1124</v>
+        <v>1127</v>
       </c>
       <c r="B3" t="s">
         <v>6</v>
@@ -12028,7 +12037,7 @@
     </row>
     <row r="29" spans="2:2">
       <c r="B29" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="30" spans="2:2">
@@ -12128,7 +12137,7 @@
     </row>
     <row r="49" spans="2:2">
       <c r="B49" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="50" spans="2:2">
@@ -12158,7 +12167,7 @@
     </row>
     <row r="55" spans="2:2">
       <c r="B55" t="s">
-        <v>1062</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="56" spans="2:2">
@@ -12193,7 +12202,7 @@
     </row>
     <row r="62" spans="2:2">
       <c r="B62" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="63" spans="2:2">
@@ -12203,7 +12212,7 @@
     </row>
     <row r="64" spans="2:2">
       <c r="B64" t="s">
-        <v>1066</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="65" spans="2:2">
@@ -12223,7 +12232,7 @@
     </row>
     <row r="68" spans="2:2">
       <c r="B68" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="69" spans="2:2">
@@ -12243,7 +12252,7 @@
     </row>
     <row r="72" spans="2:2">
       <c r="B72" t="s">
-        <v>1035</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="73" spans="2:2">
@@ -12263,7 +12272,7 @@
     </row>
     <row r="76" spans="2:2">
       <c r="B76" t="s">
-        <v>1074</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="77" spans="2:2">
@@ -12558,1077 +12567,1077 @@
     </row>
     <row r="135" spans="2:2">
       <c r="B135" t="s">
-        <v>251</v>
+        <v>967</v>
       </c>
     </row>
     <row r="136" spans="2:2">
       <c r="B136" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="137" spans="2:2">
       <c r="B137" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="138" spans="2:2">
       <c r="B138" t="s">
-        <v>1038</v>
+        <v>255</v>
       </c>
     </row>
     <row r="139" spans="2:2">
       <c r="B139" t="s">
-        <v>257</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="140" spans="2:2">
       <c r="B140" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="141" spans="2:2">
       <c r="B141" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="142" spans="2:2">
       <c r="B142" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="143" spans="2:2">
       <c r="B143" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="144" spans="2:2">
       <c r="B144" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="145" spans="2:2">
       <c r="B145" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="146" spans="2:2">
       <c r="B146" t="s">
-        <v>1077</v>
+        <v>269</v>
       </c>
     </row>
     <row r="147" spans="2:2">
       <c r="B147" t="s">
-        <v>271</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="148" spans="2:2">
       <c r="B148" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="149" spans="2:2">
       <c r="B149" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="150" spans="2:2">
       <c r="B150" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="151" spans="2:2">
       <c r="B151" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="152" spans="2:2">
       <c r="B152" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="153" spans="2:2">
       <c r="B153" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="154" spans="2:2">
       <c r="B154" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="155" spans="2:2">
       <c r="B155" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="156" spans="2:2">
       <c r="B156" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="157" spans="2:2">
       <c r="B157" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="158" spans="2:2">
       <c r="B158" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="159" spans="2:2">
       <c r="B159" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="160" spans="2:2">
       <c r="B160" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="161" spans="2:2">
       <c r="B161" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="162" spans="2:2">
       <c r="B162" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="163" spans="2:2">
       <c r="B163" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="164" spans="2:2">
       <c r="B164" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="165" spans="2:2">
       <c r="B165" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="166" spans="2:2">
       <c r="B166" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="167" spans="2:2">
       <c r="B167" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="168" spans="2:2">
       <c r="B168" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="169" spans="2:2">
       <c r="B169" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="170" spans="2:2">
       <c r="B170" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="171" spans="2:2">
       <c r="B171" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="172" spans="2:2">
       <c r="B172" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="173" spans="2:2">
       <c r="B173" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="174" spans="2:2">
       <c r="B174" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="175" spans="2:2">
       <c r="B175" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="176" spans="2:2">
       <c r="B176" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="177" spans="2:2">
       <c r="B177" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="178" spans="2:2">
       <c r="B178" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="179" spans="2:2">
       <c r="B179" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="180" spans="2:2">
       <c r="B180" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="181" spans="2:2">
       <c r="B181" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="182" spans="2:2">
       <c r="B182" t="s">
-        <v>1089</v>
+        <v>342</v>
       </c>
     </row>
     <row r="183" spans="2:2">
       <c r="B183" t="s">
-        <v>344</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="184" spans="2:2">
       <c r="B184" t="s">
-        <v>1079</v>
+        <v>344</v>
       </c>
     </row>
     <row r="185" spans="2:2">
       <c r="B185" t="s">
-        <v>346</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="186" spans="2:2">
       <c r="B186" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="187" spans="2:2">
       <c r="B187" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="188" spans="2:2">
       <c r="B188" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="189" spans="2:2">
       <c r="B189" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="190" spans="2:2">
       <c r="B190" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="191" spans="2:2">
       <c r="B191" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="192" spans="2:2">
       <c r="B192" t="s">
-        <v>1092</v>
+        <v>358</v>
       </c>
     </row>
     <row r="193" spans="2:2">
       <c r="B193" t="s">
-        <v>361</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="195" spans="2:2">
       <c r="B195" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="196" spans="2:2">
       <c r="B196" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="197" spans="2:2">
       <c r="B197" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="198" spans="2:2">
       <c r="B198" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="199" spans="2:2">
       <c r="B199" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="200" spans="2:2">
       <c r="B200" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="201" spans="2:2">
       <c r="B201" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="202" spans="2:2">
       <c r="B202" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="203" spans="2:2">
       <c r="B203" t="s">
-        <v>1098</v>
+        <v>379</v>
       </c>
     </row>
     <row r="204" spans="2:2">
       <c r="B204" t="s">
-        <v>967</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="205" spans="2:2">
       <c r="B205" t="s">
-        <v>381</v>
+        <v>970</v>
       </c>
     </row>
     <row r="206" spans="2:2">
       <c r="B206" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="207" spans="2:2">
       <c r="B207" t="s">
-        <v>969</v>
+        <v>383</v>
       </c>
     </row>
     <row r="208" spans="2:2">
       <c r="B208" t="s">
-        <v>385</v>
+        <v>972</v>
       </c>
     </row>
     <row r="209" spans="2:2">
       <c r="B209" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="210" spans="2:2">
       <c r="B210" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
     </row>
     <row r="211" spans="2:2">
       <c r="B211" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="212" spans="2:2">
       <c r="B212" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="213" spans="2:2">
       <c r="B213" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="214" spans="2:2">
       <c r="B214" t="s">
-        <v>972</v>
+        <v>397</v>
       </c>
     </row>
     <row r="215" spans="2:2">
       <c r="B215" t="s">
-        <v>399</v>
+        <v>975</v>
       </c>
     </row>
     <row r="216" spans="2:2">
       <c r="B216" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="217" spans="2:2">
       <c r="B217" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="218" spans="2:2">
       <c r="B218" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="219" spans="2:2">
       <c r="B219" t="s">
-        <v>1081</v>
+        <v>405</v>
       </c>
     </row>
     <row r="220" spans="2:2">
       <c r="B220" t="s">
-        <v>407</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="221" spans="2:2">
       <c r="B221" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="222" spans="2:2">
       <c r="B222" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="223" spans="2:2">
       <c r="B223" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="224" spans="2:2">
       <c r="B224" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="225" spans="2:2">
       <c r="B225" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="226" spans="2:2">
       <c r="B226" t="s">
-        <v>1041</v>
+        <v>417</v>
       </c>
     </row>
     <row r="227" spans="2:2">
       <c r="B227" t="s">
-        <v>419</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="228" spans="2:2">
       <c r="B228" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="229" spans="2:2">
       <c r="B229" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="230" spans="2:2">
       <c r="B230" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="231" spans="2:2">
       <c r="B231" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="232" spans="2:2">
       <c r="B232" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="233" spans="2:2">
       <c r="B233" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="234" spans="2:2">
       <c r="B234" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
     </row>
     <row r="235" spans="2:2">
       <c r="B235" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="236" spans="2:2">
       <c r="B236" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="237" spans="2:2">
       <c r="B237" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="238" spans="2:2">
       <c r="B238" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="239" spans="2:2">
       <c r="B239" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="240" spans="2:2">
       <c r="B240" t="s">
-        <v>975</v>
+        <v>444</v>
       </c>
     </row>
     <row r="241" spans="2:2">
       <c r="B241" t="s">
-        <v>446</v>
+        <v>978</v>
       </c>
     </row>
     <row r="242" spans="2:2">
       <c r="B242" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="243" spans="2:2">
       <c r="B243" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="244" spans="2:2">
       <c r="B244" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="245" spans="2:2">
       <c r="B245" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="246" spans="2:2">
       <c r="B246" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="247" spans="2:2">
       <c r="B247" t="s">
-        <v>977</v>
+        <v>456</v>
       </c>
     </row>
     <row r="248" spans="2:2">
       <c r="B248" t="s">
-        <v>458</v>
+        <v>980</v>
       </c>
     </row>
     <row r="249" spans="2:2">
       <c r="B249" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="250" spans="2:2">
       <c r="B250" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="251" spans="2:2">
       <c r="B251" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="252" spans="2:2">
       <c r="B252" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="253" spans="2:2">
       <c r="B253" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="254" spans="2:2">
       <c r="B254" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="255" spans="2:2">
       <c r="B255" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="256" spans="2:2">
       <c r="B256" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="257" spans="2:2">
       <c r="B257" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="258" spans="2:2">
       <c r="B258" t="s">
-        <v>980</v>
+        <v>476</v>
       </c>
     </row>
     <row r="259" spans="2:2">
       <c r="B259" t="s">
-        <v>478</v>
+        <v>983</v>
       </c>
     </row>
     <row r="260" spans="2:2">
       <c r="B260" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="261" spans="2:2">
       <c r="B261" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="262" spans="2:2">
       <c r="B262" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="263" spans="2:2">
       <c r="B263" t="s">
-        <v>1107</v>
+        <v>484</v>
       </c>
     </row>
     <row r="264" spans="2:2">
       <c r="B264" t="s">
-        <v>486</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="265" spans="2:2">
       <c r="B265" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="266" spans="2:2">
       <c r="B266" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="267" spans="2:2">
       <c r="B267" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="268" spans="2:2">
       <c r="B268" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="269" spans="2:2">
       <c r="B269" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="270" spans="2:2">
       <c r="B270" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="271" spans="2:2">
       <c r="B271" t="s">
-        <v>983</v>
+        <v>498</v>
       </c>
     </row>
     <row r="272" spans="2:2">
       <c r="B272" t="s">
-        <v>500</v>
+        <v>986</v>
       </c>
     </row>
     <row r="273" spans="2:2">
       <c r="B273" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="274" spans="2:2">
       <c r="B274" t="s">
-        <v>985</v>
+        <v>502</v>
       </c>
     </row>
     <row r="275" spans="2:2">
       <c r="B275" t="s">
-        <v>503</v>
+        <v>988</v>
       </c>
     </row>
     <row r="276" spans="2:2">
       <c r="B276" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="277" spans="2:2">
       <c r="B277" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="278" spans="2:2">
       <c r="B278" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="279" spans="2:2">
       <c r="B279" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="280" spans="2:2">
       <c r="B280" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="281" spans="2:2">
       <c r="B281" t="s">
-        <v>1044</v>
+        <v>513</v>
       </c>
     </row>
     <row r="282" spans="2:2">
       <c r="B282" t="s">
-        <v>988</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="283" spans="2:2">
       <c r="B283" t="s">
-        <v>515</v>
+        <v>991</v>
       </c>
     </row>
     <row r="284" spans="2:2">
       <c r="B284" t="s">
-        <v>991</v>
+        <v>515</v>
       </c>
     </row>
     <row r="285" spans="2:2">
       <c r="B285" t="s">
-        <v>516</v>
+        <v>994</v>
       </c>
     </row>
     <row r="286" spans="2:2">
       <c r="B286" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="287" spans="2:2">
       <c r="B287" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="288" spans="2:2">
       <c r="B288" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="289" spans="2:2">
       <c r="B289" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="290" spans="2:2">
       <c r="B290" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="291" spans="2:2">
       <c r="B291" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="292" spans="2:2">
       <c r="B292" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="293" spans="2:2">
       <c r="B293" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="294" spans="2:2">
       <c r="B294" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="295" spans="2:2">
       <c r="B295" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="296" spans="2:2">
       <c r="B296" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="297" spans="2:2">
       <c r="B297" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
     </row>
     <row r="298" spans="2:2">
       <c r="B298" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="299" spans="2:2">
       <c r="B299" t="s">
-        <v>1047</v>
+        <v>543</v>
       </c>
     </row>
     <row r="300" spans="2:2">
       <c r="B300" t="s">
-        <v>545</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="301" spans="2:2">
       <c r="B301" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="302" spans="2:2">
       <c r="B302" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="303" spans="2:2">
       <c r="B303" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="304" spans="2:2">
       <c r="B304" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="305" spans="2:2">
       <c r="B305" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="306" spans="2:2">
       <c r="B306" t="s">
-        <v>993</v>
+        <v>555</v>
       </c>
     </row>
     <row r="307" spans="2:2">
       <c r="B307" t="s">
-        <v>557</v>
+        <v>996</v>
       </c>
     </row>
     <row r="308" spans="2:2">
       <c r="B308" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
     </row>
     <row r="309" spans="2:2">
       <c r="B309" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="310" spans="2:2">
       <c r="B310" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="311" spans="2:2">
       <c r="B311" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="312" spans="2:2">
       <c r="B312" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
     </row>
     <row r="313" spans="2:2">
       <c r="B313" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="314" spans="2:2">
       <c r="B314" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
     <row r="315" spans="2:2">
       <c r="B315" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="316" spans="2:2">
       <c r="B316" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="317" spans="2:2">
       <c r="B317" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="318" spans="2:2">
       <c r="B318" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="319" spans="2:2">
       <c r="B319" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
     </row>
     <row r="320" spans="2:2">
       <c r="B320" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="321" spans="2:2">
       <c r="B321" t="s">
-        <v>996</v>
+        <v>582</v>
       </c>
     </row>
     <row r="322" spans="2:2">
       <c r="B322" t="s">
-        <v>585</v>
+        <v>999</v>
       </c>
     </row>
     <row r="323" spans="2:2">
       <c r="B323" t="s">
-        <v>999</v>
+        <v>585</v>
       </c>
     </row>
     <row r="324" spans="2:2">
       <c r="B324" t="s">
-        <v>587</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="325" spans="2:2">
       <c r="B325" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
     </row>
     <row r="326" spans="2:2">
       <c r="B326" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="327" spans="2:2">
       <c r="B327" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
     </row>
     <row r="328" spans="2:2">
       <c r="B328" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="329" spans="2:2">
       <c r="B329" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
     </row>
     <row r="330" spans="2:2">
       <c r="B330" t="s">
-        <v>1083</v>
+        <v>596</v>
       </c>
     </row>
     <row r="331" spans="2:2">
       <c r="B331" t="s">
-        <v>598</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="332" spans="2:2">
       <c r="B332" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
     </row>
     <row r="333" spans="2:2">
       <c r="B333" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="334" spans="2:2">
       <c r="B334" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="335" spans="2:2">
       <c r="B335" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
     </row>
     <row r="336" spans="2:2">
       <c r="B336" t="s">
-        <v>1111</v>
+        <v>606</v>
       </c>
     </row>
     <row r="337" spans="2:2">
       <c r="B337" t="s">
-        <v>608</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="338" spans="2:2">
       <c r="B338" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="339" spans="2:2">
       <c r="B339" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="340" spans="2:2">
       <c r="B340" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="341" spans="2:2">
       <c r="B341" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="342" spans="2:2">
       <c r="B342" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="343" spans="2:2">
       <c r="B343" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="344" spans="2:2">
       <c r="B344" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="345" spans="2:2">
       <c r="B345" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
     </row>
     <row r="346" spans="2:2">
       <c r="B346" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
     </row>
     <row r="347" spans="2:2">
       <c r="B347" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
     </row>
     <row r="348" spans="2:2">
       <c r="B348" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
     </row>
     <row r="349" spans="2:2">
       <c r="B349" t="s">
-        <v>1002</v>
+        <v>630</v>
       </c>
     </row>
     <row r="350" spans="2:2">
@@ -13638,692 +13647,692 @@
     </row>
     <row r="351" spans="2:2">
       <c r="B351" t="s">
-        <v>632</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="352" spans="2:2">
       <c r="B352" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="353" spans="2:2">
       <c r="B353" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
     </row>
     <row r="354" spans="2:2">
       <c r="B354" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
     </row>
     <row r="355" spans="2:2">
       <c r="B355" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
     </row>
     <row r="356" spans="2:2">
       <c r="B356" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
     </row>
     <row r="357" spans="2:2">
       <c r="B357" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
     </row>
     <row r="358" spans="2:2">
       <c r="B358" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
     </row>
     <row r="359" spans="2:2">
       <c r="B359" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
     </row>
     <row r="360" spans="2:2">
       <c r="B360" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
     </row>
     <row r="361" spans="2:2">
       <c r="B361" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
     </row>
     <row r="362" spans="2:2">
       <c r="B362" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
     </row>
     <row r="363" spans="2:2">
       <c r="B363" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
     </row>
     <row r="364" spans="2:2">
       <c r="B364" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
     </row>
     <row r="365" spans="2:2">
       <c r="B365" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
     </row>
     <row r="366" spans="2:2">
       <c r="B366" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
     </row>
     <row r="367" spans="2:2">
       <c r="B367" t="s">
-        <v>1049</v>
+        <v>664</v>
       </c>
     </row>
     <row r="368" spans="2:2">
       <c r="B368" t="s">
-        <v>1008</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="369" spans="2:2">
       <c r="B369" t="s">
-        <v>665</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="370" spans="2:2">
       <c r="B370" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
     </row>
     <row r="371" spans="2:2">
       <c r="B371" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="372" spans="2:2">
       <c r="B372" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
     </row>
     <row r="373" spans="2:2">
       <c r="B373" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
     </row>
     <row r="374" spans="2:2">
       <c r="B374" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
     </row>
     <row r="375" spans="2:2">
       <c r="B375" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
     </row>
     <row r="376" spans="2:2">
       <c r="B376" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
     </row>
     <row r="377" spans="2:2">
       <c r="B377" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
     </row>
     <row r="378" spans="2:2">
       <c r="B378" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
     </row>
     <row r="379" spans="2:2">
       <c r="B379" t="s">
-        <v>1010</v>
+        <v>683</v>
       </c>
     </row>
     <row r="380" spans="2:2">
       <c r="B380" t="s">
-        <v>685</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="381" spans="2:2">
       <c r="B381" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
     </row>
     <row r="382" spans="2:2">
       <c r="B382" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
     </row>
     <row r="383" spans="2:2">
       <c r="B383" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
     </row>
     <row r="384" spans="2:2">
       <c r="B384" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
     </row>
     <row r="385" spans="2:2">
       <c r="B385" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
     </row>
     <row r="386" spans="2:2">
       <c r="B386" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
     </row>
     <row r="387" spans="2:2">
       <c r="B387" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
     </row>
     <row r="388" spans="2:2">
       <c r="B388" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="389" spans="2:2">
       <c r="B389" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
     </row>
     <row r="390" spans="2:2">
       <c r="B390" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
     </row>
     <row r="391" spans="2:2">
       <c r="B391" t="s">
-        <v>1012</v>
+        <v>706</v>
       </c>
     </row>
     <row r="392" spans="2:2">
       <c r="B392" t="s">
-        <v>708</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="393" spans="2:2">
       <c r="B393" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
     </row>
     <row r="394" spans="2:2">
       <c r="B394" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
     </row>
     <row r="395" spans="2:2">
       <c r="B395" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="396" spans="2:2">
       <c r="B396" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
     </row>
     <row r="397" spans="2:2">
       <c r="B397" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
     </row>
     <row r="398" spans="2:2">
       <c r="B398" t="s">
-        <v>1095</v>
+        <v>718</v>
       </c>
     </row>
     <row r="399" spans="2:2">
       <c r="B399" t="s">
-        <v>720</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="400" spans="2:2">
       <c r="B400" t="s">
-        <v>1015</v>
+        <v>720</v>
       </c>
     </row>
     <row r="401" spans="2:2">
       <c r="B401" t="s">
-        <v>722</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="402" spans="2:2">
       <c r="B402" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="403" spans="2:2">
       <c r="B403" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
     </row>
     <row r="404" spans="2:2">
       <c r="B404" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
     </row>
     <row r="405" spans="2:2">
       <c r="B405" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
     </row>
     <row r="406" spans="2:2">
       <c r="B406" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
     </row>
     <row r="407" spans="2:2">
       <c r="B407" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
     </row>
     <row r="408" spans="2:2">
       <c r="B408" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
     </row>
     <row r="409" spans="2:2">
       <c r="B409" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
     </row>
     <row r="410" spans="2:2">
       <c r="B410" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
     </row>
     <row r="411" spans="2:2">
       <c r="B411" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
     </row>
     <row r="412" spans="2:2">
       <c r="B412" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
     </row>
     <row r="413" spans="2:2">
       <c r="B413" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
     </row>
     <row r="414" spans="2:2">
       <c r="B414" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
     </row>
     <row r="415" spans="2:2">
       <c r="B415" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
     </row>
     <row r="416" spans="2:2">
       <c r="B416" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
     </row>
     <row r="417" spans="2:2">
       <c r="B417" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
     </row>
     <row r="418" spans="2:2">
       <c r="B418" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
     </row>
     <row r="419" spans="2:2">
       <c r="B419" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
     </row>
     <row r="420" spans="2:2">
       <c r="B420" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
     </row>
     <row r="421" spans="2:2">
       <c r="B421" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
     </row>
     <row r="422" spans="2:2">
       <c r="B422" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
     </row>
     <row r="423" spans="2:2">
       <c r="B423" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
     </row>
     <row r="424" spans="2:2">
       <c r="B424" t="s">
-        <v>1115</v>
+        <v>765</v>
       </c>
     </row>
     <row r="425" spans="2:2">
       <c r="B425" t="s">
-        <v>767</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="426" spans="2:2">
       <c r="B426" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
     </row>
     <row r="427" spans="2:2">
       <c r="B427" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
     </row>
     <row r="428" spans="2:2">
       <c r="B428" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
     </row>
     <row r="429" spans="2:2">
       <c r="B429" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
     </row>
     <row r="430" spans="2:2">
       <c r="B430" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
     </row>
     <row r="431" spans="2:2">
       <c r="B431" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
     </row>
     <row r="432" spans="2:2">
       <c r="B432" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="433" spans="2:2">
       <c r="B433" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
     </row>
     <row r="434" spans="2:2">
       <c r="B434" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="435" spans="2:2">
       <c r="B435" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
     </row>
     <row r="436" spans="2:2">
       <c r="B436" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
     <row r="437" spans="2:2">
       <c r="B437" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
     </row>
     <row r="438" spans="2:2">
       <c r="B438" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
     </row>
     <row r="439" spans="2:2">
       <c r="B439" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
     </row>
     <row r="440" spans="2:2">
       <c r="B440" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
     </row>
     <row r="441" spans="2:2">
       <c r="B441" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
     </row>
     <row r="442" spans="2:2">
       <c r="B442" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
     </row>
     <row r="443" spans="2:2">
       <c r="B443" t="s">
-        <v>1119</v>
+        <v>803</v>
       </c>
     </row>
     <row r="444" spans="2:2">
       <c r="B444" t="s">
-        <v>1101</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="445" spans="2:2">
       <c r="B445" t="s">
-        <v>805</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="446" spans="2:2">
       <c r="B446" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
     </row>
     <row r="447" spans="2:2">
       <c r="B447" t="s">
-        <v>1103</v>
+        <v>807</v>
       </c>
     </row>
     <row r="448" spans="2:2">
       <c r="B448" t="s">
-        <v>1018</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="449" spans="2:2">
       <c r="B449" t="s">
-        <v>809</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="450" spans="2:2">
       <c r="B450" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
     </row>
     <row r="451" spans="2:2">
       <c r="B451" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
     </row>
     <row r="452" spans="2:2">
       <c r="B452" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
     </row>
     <row r="453" spans="2:2">
       <c r="B453" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
     </row>
     <row r="454" spans="2:2">
       <c r="B454" t="s">
-        <v>1051</v>
+        <v>817</v>
       </c>
     </row>
     <row r="455" spans="2:2">
       <c r="B455" t="s">
-        <v>819</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="456" spans="2:2">
       <c r="B456" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
     </row>
     <row r="457" spans="2:2">
       <c r="B457" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
     </row>
     <row r="458" spans="2:2">
       <c r="B458" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
     </row>
     <row r="459" spans="2:2">
       <c r="B459" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
     </row>
     <row r="460" spans="2:2">
       <c r="B460" t="s">
-        <v>1053</v>
+        <v>827</v>
       </c>
     </row>
     <row r="461" spans="2:2">
       <c r="B461" t="s">
-        <v>829</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="462" spans="2:2">
       <c r="B462" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="463" spans="2:2">
       <c r="B463" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
     </row>
     <row r="464" spans="2:2">
       <c r="B464" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
     </row>
     <row r="465" spans="2:2">
       <c r="B465" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
     </row>
     <row r="466" spans="2:2">
       <c r="B466" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
     </row>
     <row r="467" spans="2:2">
       <c r="B467" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="468" spans="2:2">
       <c r="B468" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="469" spans="2:2">
       <c r="B469" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
     </row>
     <row r="470" spans="2:2">
       <c r="B470" t="s">
-        <v>1055</v>
+        <v>845</v>
       </c>
     </row>
     <row r="471" spans="2:2">
       <c r="B471" t="s">
-        <v>847</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="472" spans="2:2">
       <c r="B472" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
     </row>
     <row r="473" spans="2:2">
       <c r="B473" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
     </row>
     <row r="474" spans="2:2">
       <c r="B474" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
     </row>
     <row r="475" spans="2:2">
       <c r="B475" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="476" spans="2:2">
       <c r="B476" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
     </row>
     <row r="477" spans="2:2">
       <c r="B477" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
     </row>
     <row r="478" spans="2:2">
       <c r="B478" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
     </row>
     <row r="479" spans="2:2">
       <c r="B479" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
     </row>
     <row r="480" spans="2:2">
       <c r="B480" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
     </row>
     <row r="481" spans="2:2">
       <c r="B481" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
     </row>
     <row r="482" spans="2:2">
       <c r="B482" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
     </row>
     <row r="483" spans="2:2">
       <c r="B483" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
     </row>
     <row r="484" spans="2:2">
       <c r="B484" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
     </row>
     <row r="485" spans="2:2">
       <c r="B485" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
     </row>
     <row r="486" spans="2:2">
       <c r="B486" t="s">
-        <v>1021</v>
+        <v>875</v>
       </c>
     </row>
     <row r="487" spans="2:2">
       <c r="B487" t="s">
-        <v>877</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="488" spans="2:2">
       <c r="B488" t="s">
-        <v>1023</v>
+        <v>877</v>
       </c>
     </row>
     <row r="489" spans="2:2">
@@ -14333,206 +14342,216 @@
     </row>
     <row r="490" spans="2:2">
       <c r="B490" t="s">
-        <v>879</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="491" spans="2:2">
       <c r="B491" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
     </row>
     <row r="492" spans="2:2">
       <c r="B492" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
     </row>
     <row r="493" spans="2:2">
       <c r="B493" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
     </row>
     <row r="494" spans="2:2">
       <c r="B494" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
     </row>
     <row r="495" spans="2:2">
       <c r="B495" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
     </row>
     <row r="496" spans="2:2">
       <c r="B496" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
     </row>
     <row r="497" spans="2:2">
       <c r="B497" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
     </row>
     <row r="498" spans="2:2">
       <c r="B498" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
     </row>
     <row r="499" spans="2:2">
       <c r="B499" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
     </row>
     <row r="500" spans="2:2">
       <c r="B500" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
     </row>
     <row r="501" spans="2:2">
       <c r="B501" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
     </row>
     <row r="502" spans="2:2">
       <c r="B502" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
     </row>
     <row r="503" spans="2:2">
       <c r="B503" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
     </row>
     <row r="504" spans="2:2">
       <c r="B504" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
     </row>
     <row r="505" spans="2:2">
       <c r="B505" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="506" spans="2:2">
       <c r="B506" t="s">
-        <v>1086</v>
+        <v>910</v>
       </c>
     </row>
     <row r="507" spans="2:2">
       <c r="B507" t="s">
-        <v>912</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="508" spans="2:2">
       <c r="B508" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
     </row>
     <row r="509" spans="2:2">
       <c r="B509" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
     </row>
     <row r="510" spans="2:2">
       <c r="B510" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
     </row>
     <row r="511" spans="2:2">
       <c r="B511" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
     </row>
     <row r="512" spans="2:2">
       <c r="B512" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
     </row>
     <row r="513" spans="1:2">
       <c r="B513" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
     </row>
     <row r="514" spans="1:2">
       <c r="B514" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
     </row>
     <row r="515" spans="1:2">
       <c r="B515" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="516" spans="1:2">
       <c r="B516" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
     </row>
     <row r="517" spans="1:2">
       <c r="B517" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
     </row>
     <row r="518" spans="1:2">
       <c r="B518" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
     </row>
     <row r="519" spans="1:2">
       <c r="B519" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="520" spans="1:2">
+      <c r="B520" t="s">
         <v>937</v>
       </c>
     </row>
-    <row r="521" spans="1:2">
-      <c r="A521" t="s">
-        <v>1125</v>
-      </c>
-      <c r="B521" t="s">
-        <v>1070</v>
-      </c>
-    </row>
     <row r="522" spans="1:2">
+      <c r="A522" t="s">
+        <v>1128</v>
+      </c>
       <c r="B522" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="523" spans="1:2">
       <c r="B523" t="s">
-        <v>958</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="524" spans="1:2">
       <c r="B524" t="s">
-        <v>1079</v>
+        <v>958</v>
       </c>
     </row>
     <row r="525" spans="1:2">
       <c r="B525" t="s">
-        <v>972</v>
+        <v>967</v>
       </c>
     </row>
     <row r="526" spans="1:2">
       <c r="B526" t="s">
-        <v>983</v>
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="527" spans="1:2">
+      <c r="B527" t="s">
+        <v>975</v>
       </c>
     </row>
     <row r="528" spans="1:2">
-      <c r="A528" t="s">
-        <v>1126</v>
-      </c>
       <c r="B528" t="s">
-        <v>1035</v>
+        <v>986</v>
       </c>
     </row>
     <row r="530" spans="1:2">
       <c r="A530" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="B530" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="532" spans="1:2">
+      <c r="A532" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B532" t="s">
         <v>955</v>
       </c>
     </row>
-    <row r="531" spans="1:2">
-      <c r="B531" t="s">
-        <v>1015</v>
+    <row r="533" spans="1:2">
+      <c r="B533" t="s">
+        <v>1018</v>
       </c>
     </row>
   </sheetData>
@@ -14542,7 +14561,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="110.7109375" customWidth="1"/>
@@ -14730,7 +14749,7 @@
         <v>967</v>
       </c>
       <c r="B12">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="C12" t="s">
         <v>968</v>
@@ -14739,24 +14758,24 @@
         <v>8</v>
       </c>
       <c r="E12" t="s">
-        <v>45</v>
+        <v>969</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="B13">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="C13" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="D13" t="s">
         <v>8</v>
       </c>
       <c r="E13" t="s">
-        <v>971</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -14764,7 +14783,7 @@
         <v>972</v>
       </c>
       <c r="B14">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="C14" t="s">
         <v>973</v>
@@ -14781,7 +14800,7 @@
         <v>975</v>
       </c>
       <c r="B15">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="C15" t="s">
         <v>976</v>
@@ -14790,24 +14809,24 @@
         <v>8</v>
       </c>
       <c r="E15" t="s">
-        <v>963</v>
+        <v>977</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="B16">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="C16" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="D16" t="s">
         <v>8</v>
       </c>
       <c r="E16" t="s">
-        <v>979</v>
+        <v>963</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -14815,7 +14834,7 @@
         <v>980</v>
       </c>
       <c r="B17">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="C17" t="s">
         <v>981</v>
@@ -14832,7 +14851,7 @@
         <v>983</v>
       </c>
       <c r="B18">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="C18" t="s">
         <v>984</v>
@@ -14841,24 +14860,24 @@
         <v>8</v>
       </c>
       <c r="E18" t="s">
-        <v>960</v>
+        <v>985</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="B19">
-        <v>1.6</v>
+        <v>1.88</v>
       </c>
       <c r="C19" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="D19" t="s">
         <v>8</v>
       </c>
       <c r="E19" t="s">
-        <v>987</v>
+        <v>960</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -14866,7 +14885,7 @@
         <v>988</v>
       </c>
       <c r="B20">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="C20" t="s">
         <v>989</v>
@@ -14883,7 +14902,7 @@
         <v>991</v>
       </c>
       <c r="B21">
-        <v>1.95</v>
+        <v>2.9</v>
       </c>
       <c r="C21" t="s">
         <v>992</v>
@@ -14892,24 +14911,24 @@
         <v>8</v>
       </c>
       <c r="E21" t="s">
-        <v>951</v>
+        <v>993</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="B22">
-        <v>2.9</v>
+        <v>1.95</v>
       </c>
       <c r="C22" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="D22" t="s">
         <v>8</v>
       </c>
       <c r="E22" t="s">
-        <v>995</v>
+        <v>951</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -14917,7 +14936,7 @@
         <v>996</v>
       </c>
       <c r="B23">
-        <v>2.48</v>
+        <v>2.9</v>
       </c>
       <c r="C23" t="s">
         <v>997</v>
@@ -14934,7 +14953,7 @@
         <v>999</v>
       </c>
       <c r="B24">
-        <v>3.2</v>
+        <v>2.48</v>
       </c>
       <c r="C24" t="s">
         <v>1000</v>
@@ -14951,7 +14970,7 @@
         <v>1002</v>
       </c>
       <c r="B25">
-        <v>1.97</v>
+        <v>3.2</v>
       </c>
       <c r="C25" t="s">
         <v>1003</v>
@@ -14968,7 +14987,7 @@
         <v>1005</v>
       </c>
       <c r="B26">
-        <v>2.3</v>
+        <v>1.97</v>
       </c>
       <c r="C26" t="s">
         <v>1006</v>
@@ -14994,41 +15013,41 @@
         <v>8</v>
       </c>
       <c r="E27" t="s">
-        <v>951</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="B28">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="C28" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="D28" t="s">
         <v>8</v>
       </c>
       <c r="E28" t="s">
-        <v>982</v>
+        <v>951</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B29">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="C29" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="D29" t="s">
         <v>8</v>
       </c>
       <c r="E29" t="s">
-        <v>1014</v>
+        <v>985</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -15036,7 +15055,7 @@
         <v>1015</v>
       </c>
       <c r="B30">
-        <v>1.66</v>
+        <v>2.04</v>
       </c>
       <c r="C30" t="s">
         <v>1016</v>
@@ -15053,7 +15072,7 @@
         <v>1018</v>
       </c>
       <c r="B31">
-        <v>2.48</v>
+        <v>1.66</v>
       </c>
       <c r="C31" t="s">
         <v>1019</v>
@@ -15070,7 +15089,7 @@
         <v>1021</v>
       </c>
       <c r="B32">
-        <v>2.8</v>
+        <v>2.48</v>
       </c>
       <c r="C32" t="s">
         <v>1022</v>
@@ -15079,24 +15098,24 @@
         <v>8</v>
       </c>
       <c r="E32" t="s">
-        <v>954</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="B33">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="C33" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="D33" t="s">
         <v>8</v>
       </c>
       <c r="E33" t="s">
-        <v>1025</v>
+        <v>954</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -15104,7 +15123,7 @@
         <v>1026</v>
       </c>
       <c r="B34">
-        <v>2.02</v>
+        <v>2.5</v>
       </c>
       <c r="C34" t="s">
         <v>1027</v>
@@ -15113,6 +15132,23 @@
         <v>8</v>
       </c>
       <c r="E34" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B35">
+        <v>2.02</v>
+      </c>
+      <c r="C35" t="s">
+        <v>1030</v>
+      </c>
+      <c r="D35" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" t="s">
         <v>948</v>
       </c>
     </row>
@@ -15133,7 +15169,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -15155,189 +15191,189 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
       <c r="B3">
         <v>2.7</v>
       </c>
       <c r="C3" t="s">
-        <v>1030</v>
+        <v>1033</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="B4">
         <v>2.59</v>
       </c>
       <c r="C4" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="D4" t="s">
         <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>1035</v>
+        <v>1038</v>
       </c>
       <c r="B5">
         <v>3.18</v>
       </c>
       <c r="C5" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="D5" t="s">
         <v>8</v>
       </c>
       <c r="E5" t="s">
-        <v>1037</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>1038</v>
+        <v>1041</v>
       </c>
       <c r="B6">
         <v>1.75</v>
       </c>
       <c r="C6" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="D6" t="s">
         <v>8</v>
       </c>
       <c r="E6" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="B7">
         <v>1.88</v>
       </c>
       <c r="C7" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="D7" t="s">
         <v>8</v>
       </c>
       <c r="E7" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="B8">
         <v>2.66</v>
       </c>
       <c r="C8" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
       <c r="D8" t="s">
         <v>8</v>
       </c>
       <c r="E8" t="s">
-        <v>1046</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>1047</v>
+        <v>1050</v>
       </c>
       <c r="B9">
         <v>1.76</v>
       </c>
       <c r="C9" t="s">
-        <v>1048</v>
+        <v>1051</v>
       </c>
       <c r="D9" t="s">
         <v>8</v>
       </c>
       <c r="E9" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="B10">
         <v>1.84</v>
       </c>
       <c r="C10" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
       <c r="D10" t="s">
         <v>8</v>
       </c>
       <c r="E10" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="B11">
         <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
       <c r="D11" t="s">
         <v>8</v>
       </c>
       <c r="E11" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>1053</v>
+        <v>1056</v>
       </c>
       <c r="B12">
         <v>1.92</v>
       </c>
       <c r="C12" t="s">
-        <v>1054</v>
+        <v>1057</v>
       </c>
       <c r="D12" t="s">
         <v>8</v>
       </c>
       <c r="E12" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
       <c r="B13">
         <v>1.77</v>
       </c>
       <c r="C13" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
       <c r="D13" t="s">
         <v>8</v>
       </c>
       <c r="E13" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
     </row>
   </sheetData>
@@ -15357,7 +15393,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -15379,19 +15415,19 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
       <c r="B3">
         <v>2.2</v>
       </c>
       <c r="C3" t="s">
-        <v>1059</v>
+        <v>1062</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>1060</v>
+        <v>1063</v>
       </c>
     </row>
   </sheetData>
@@ -15411,7 +15447,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -15433,19 +15469,19 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>1062</v>
+        <v>1065</v>
       </c>
       <c r="B3">
         <v>1.32</v>
       </c>
       <c r="C3" t="s">
-        <v>1063</v>
+        <v>1066</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>1064</v>
+        <v>1067</v>
       </c>
     </row>
   </sheetData>
@@ -15465,7 +15501,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>1065</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -15487,19 +15523,19 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>1066</v>
+        <v>1069</v>
       </c>
       <c r="B3">
         <v>2.45</v>
       </c>
       <c r="C3" t="s">
-        <v>1067</v>
+        <v>1070</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>1068</v>
+        <v>1071</v>
       </c>
     </row>
   </sheetData>
@@ -15519,7 +15555,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -15541,19 +15577,19 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="B3">
         <v>1.45</v>
       </c>
       <c r="C3" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>1072</v>
+        <v>1075</v>
       </c>
     </row>
   </sheetData>
@@ -15573,7 +15609,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -15595,64 +15631,64 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>1074</v>
+        <v>1077</v>
       </c>
       <c r="B3">
         <v>1.9</v>
       </c>
       <c r="C3" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>1076</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
       <c r="B4">
         <v>2.11</v>
       </c>
       <c r="C4" t="s">
-        <v>1078</v>
+        <v>1081</v>
       </c>
       <c r="D4" t="s">
         <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>1076</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>1079</v>
+        <v>1082</v>
       </c>
       <c r="B5">
         <v>2.7</v>
       </c>
       <c r="C5" t="s">
-        <v>1080</v>
+        <v>1083</v>
       </c>
       <c r="D5" t="s">
         <v>8</v>
       </c>
       <c r="E5" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>1081</v>
+        <v>1084</v>
       </c>
       <c r="B6">
         <v>2.58</v>
       </c>
       <c r="C6" t="s">
-        <v>1082</v>
+        <v>1085</v>
       </c>
       <c r="D6" t="s">
         <v>8</v>
@@ -15663,30 +15699,30 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>1083</v>
+        <v>1086</v>
       </c>
       <c r="B7">
         <v>1.93</v>
       </c>
       <c r="C7" t="s">
-        <v>1084</v>
+        <v>1087</v>
       </c>
       <c r="D7" t="s">
         <v>8</v>
       </c>
       <c r="E7" t="s">
-        <v>1085</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>1086</v>
+        <v>1089</v>
       </c>
       <c r="B8">
         <v>2.05</v>
       </c>
       <c r="C8" t="s">
-        <v>1087</v>
+        <v>1090</v>
       </c>
       <c r="D8" t="s">
         <v>8</v>
@@ -15712,7 +15748,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>1088</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -15734,13 +15770,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>1089</v>
+        <v>1092</v>
       </c>
       <c r="B3">
         <v>0.93</v>
       </c>
       <c r="C3" t="s">
-        <v>1090</v>
+        <v>1093</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>

--- a/pdb/nsp3/SARS-CoV-2/domains_and_infos_of_nsp3.xlsx
+++ b/pdb/nsp3/SARS-CoV-2/domains_and_infos_of_nsp3.xlsx
@@ -4740,7 +4740,7 @@
         <v>130</v>
       </c>
       <c r="B59">
-        <v>0.9400000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="C59" t="s">
         <v>131</v>
@@ -6117,7 +6117,7 @@
         <v>296</v>
       </c>
       <c r="B140">
-        <v>0.9500000000000001</v>
+        <v>0.95</v>
       </c>
       <c r="C140" t="s">
         <v>297</v>
@@ -9177,7 +9177,7 @@
         <v>661</v>
       </c>
       <c r="B320">
-        <v>0.9600000000000001</v>
+        <v>0.96</v>
       </c>
       <c r="C320" t="s">
         <v>662</v>
@@ -9466,7 +9466,7 @@
         <v>695</v>
       </c>
       <c r="B337">
-        <v>0.8500000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="C337" t="s">
         <v>696</v>
@@ -10554,7 +10554,7 @@
         <v>825</v>
       </c>
       <c r="B401">
-        <v>0.8800000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="C401" t="s">
         <v>826</v>
@@ -11098,7 +11098,7 @@
         <v>889</v>
       </c>
       <c r="B433">
-        <v>0.8400000000000001</v>
+        <v>0.84</v>
       </c>
       <c r="C433" t="s">
         <v>890</v>

--- a/pdb/nsp3/SARS-CoV-2/domains_and_infos_of_nsp3.xlsx
+++ b/pdb/nsp3/SARS-CoV-2/domains_and_infos_of_nsp3.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2697" uniqueCount="1131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2702" uniqueCount="1134">
   <si>
     <t>nsp3_Macro1_</t>
   </si>
@@ -2969,6 +2969,15 @@
   </si>
   <si>
     <t>STRUCTURE OF SARS-COV-2 PAPAIN-LIKE PROTEASE PLPRO IN COMPLEX WITH 4- (2-HYDROXYETHYL)PHENOL</t>
+  </si>
+  <si>
+    <t>8g62</t>
+  </si>
+  <si>
+    <t>PAPAIN-LIKE PROTEASE OF SARS COV-2 IN COMPLEX WITH REMODILIN NCGC 390004</t>
+  </si>
+  <si>
+    <t>2023-02-14</t>
   </si>
   <si>
     <t>7sqe</t>
@@ -11518,7 +11527,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>1094</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -11540,36 +11549,36 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>1095</v>
+        <v>1098</v>
       </c>
       <c r="B3">
         <v>1.7</v>
       </c>
       <c r="C3" t="s">
-        <v>1096</v>
+        <v>1099</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>1097</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>1098</v>
+        <v>1101</v>
       </c>
       <c r="B4">
         <v>2.1</v>
       </c>
       <c r="C4" t="s">
-        <v>1099</v>
+        <v>1102</v>
       </c>
       <c r="D4" t="s">
         <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>1097</v>
+        <v>1100</v>
       </c>
     </row>
   </sheetData>
@@ -11589,7 +11598,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>1100</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -11611,53 +11620,53 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="B3">
         <v>1.93</v>
       </c>
       <c r="C3" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>1103</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>1104</v>
+        <v>1107</v>
       </c>
       <c r="B4">
         <v>3.21</v>
       </c>
       <c r="C4" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D4" t="s">
         <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
       <c r="B5">
         <v>2.73</v>
       </c>
       <c r="C5" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
       <c r="D5" t="s">
         <v>8</v>
       </c>
       <c r="E5" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
     </row>
   </sheetData>
@@ -11677,7 +11686,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -11699,19 +11708,19 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>1110</v>
+        <v>1113</v>
       </c>
       <c r="B3">
         <v>2.17</v>
       </c>
       <c r="C3" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>1112</v>
+        <v>1115</v>
       </c>
     </row>
   </sheetData>
@@ -11731,7 +11740,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>1113</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -11753,19 +11762,19 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>1114</v>
+        <v>1117</v>
       </c>
       <c r="B3">
         <v>2.72</v>
       </c>
       <c r="C3" t="s">
-        <v>1115</v>
+        <v>1118</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>1116</v>
+        <v>1119</v>
       </c>
     </row>
   </sheetData>
@@ -11785,7 +11794,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -11807,16 +11816,16 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>1118</v>
+        <v>1121</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>1119</v>
+        <v>1122</v>
       </c>
       <c r="D3" t="s">
-        <v>1120</v>
+        <v>1123</v>
       </c>
       <c r="E3" t="s">
         <v>960</v>
@@ -11839,7 +11848,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>1121</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -11861,19 +11870,19 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="B3">
         <v>2.68</v>
       </c>
       <c r="C3" t="s">
-        <v>1123</v>
+        <v>1126</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>1124</v>
+        <v>1127</v>
       </c>
     </row>
   </sheetData>
@@ -11883,7 +11892,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B533"/>
+  <dimension ref="A1:B534"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.7109375" customWidth="1"/>
@@ -11891,12 +11900,12 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>1125</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>1126</v>
+        <v>1129</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
@@ -11904,7 +11913,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>1127</v>
+        <v>1130</v>
       </c>
       <c r="B3" t="s">
         <v>6</v>
@@ -12037,7 +12046,7 @@
     </row>
     <row r="29" spans="2:2">
       <c r="B29" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="30" spans="2:2">
@@ -12137,7 +12146,7 @@
     </row>
     <row r="49" spans="2:2">
       <c r="B49" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="50" spans="2:2">
@@ -12167,7 +12176,7 @@
     </row>
     <row r="55" spans="2:2">
       <c r="B55" t="s">
-        <v>1065</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="56" spans="2:2">
@@ -12202,7 +12211,7 @@
     </row>
     <row r="62" spans="2:2">
       <c r="B62" t="s">
-        <v>1035</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="63" spans="2:2">
@@ -12212,7 +12221,7 @@
     </row>
     <row r="64" spans="2:2">
       <c r="B64" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="65" spans="2:2">
@@ -12232,7 +12241,7 @@
     </row>
     <row r="68" spans="2:2">
       <c r="B68" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="69" spans="2:2">
@@ -12252,7 +12261,7 @@
     </row>
     <row r="72" spans="2:2">
       <c r="B72" t="s">
-        <v>1038</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="73" spans="2:2">
@@ -12272,7 +12281,7 @@
     </row>
     <row r="76" spans="2:2">
       <c r="B76" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="77" spans="2:2">
@@ -12587,7 +12596,7 @@
     </row>
     <row r="139" spans="2:2">
       <c r="B139" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="140" spans="2:2">
@@ -12627,7 +12636,7 @@
     </row>
     <row r="147" spans="2:2">
       <c r="B147" t="s">
-        <v>1080</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="148" spans="2:2">
@@ -12807,7 +12816,7 @@
     </row>
     <row r="183" spans="2:2">
       <c r="B183" t="s">
-        <v>1092</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="184" spans="2:2">
@@ -12817,7 +12826,7 @@
     </row>
     <row r="185" spans="2:2">
       <c r="B185" t="s">
-        <v>1082</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="186" spans="2:2">
@@ -12857,7 +12866,7 @@
     </row>
     <row r="193" spans="2:2">
       <c r="B193" t="s">
-        <v>1095</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="194" spans="2:2">
@@ -12912,7 +12921,7 @@
     </row>
     <row r="204" spans="2:2">
       <c r="B204" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="205" spans="2:2">
@@ -12992,7 +13001,7 @@
     </row>
     <row r="220" spans="2:2">
       <c r="B220" t="s">
-        <v>1084</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="221" spans="2:2">
@@ -13027,7 +13036,7 @@
     </row>
     <row r="227" spans="2:2">
       <c r="B227" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="228" spans="2:2">
@@ -13127,522 +13136,522 @@
     </row>
     <row r="247" spans="2:2">
       <c r="B247" t="s">
-        <v>456</v>
+        <v>980</v>
       </c>
     </row>
     <row r="248" spans="2:2">
       <c r="B248" t="s">
-        <v>980</v>
+        <v>456</v>
       </c>
     </row>
     <row r="249" spans="2:2">
       <c r="B249" t="s">
-        <v>458</v>
+        <v>983</v>
       </c>
     </row>
     <row r="250" spans="2:2">
       <c r="B250" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="251" spans="2:2">
       <c r="B251" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="252" spans="2:2">
       <c r="B252" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="253" spans="2:2">
       <c r="B253" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="254" spans="2:2">
       <c r="B254" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="255" spans="2:2">
       <c r="B255" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="256" spans="2:2">
       <c r="B256" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="257" spans="2:2">
       <c r="B257" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="258" spans="2:2">
       <c r="B258" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="259" spans="2:2">
       <c r="B259" t="s">
-        <v>983</v>
+        <v>476</v>
       </c>
     </row>
     <row r="260" spans="2:2">
       <c r="B260" t="s">
-        <v>478</v>
+        <v>986</v>
       </c>
     </row>
     <row r="261" spans="2:2">
       <c r="B261" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="262" spans="2:2">
       <c r="B262" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="263" spans="2:2">
       <c r="B263" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="264" spans="2:2">
       <c r="B264" t="s">
-        <v>1110</v>
+        <v>484</v>
       </c>
     </row>
     <row r="265" spans="2:2">
       <c r="B265" t="s">
-        <v>486</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="266" spans="2:2">
       <c r="B266" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="267" spans="2:2">
       <c r="B267" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="268" spans="2:2">
       <c r="B268" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="269" spans="2:2">
       <c r="B269" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="270" spans="2:2">
       <c r="B270" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="271" spans="2:2">
       <c r="B271" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="272" spans="2:2">
       <c r="B272" t="s">
-        <v>986</v>
+        <v>498</v>
       </c>
     </row>
     <row r="273" spans="2:2">
       <c r="B273" t="s">
-        <v>500</v>
+        <v>989</v>
       </c>
     </row>
     <row r="274" spans="2:2">
       <c r="B274" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="275" spans="2:2">
       <c r="B275" t="s">
-        <v>988</v>
+        <v>502</v>
       </c>
     </row>
     <row r="276" spans="2:2">
       <c r="B276" t="s">
-        <v>503</v>
+        <v>991</v>
       </c>
     </row>
     <row r="277" spans="2:2">
       <c r="B277" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="278" spans="2:2">
       <c r="B278" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="279" spans="2:2">
       <c r="B279" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="280" spans="2:2">
       <c r="B280" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="281" spans="2:2">
       <c r="B281" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="282" spans="2:2">
       <c r="B282" t="s">
-        <v>1047</v>
+        <v>513</v>
       </c>
     </row>
     <row r="283" spans="2:2">
       <c r="B283" t="s">
-        <v>991</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="284" spans="2:2">
       <c r="B284" t="s">
-        <v>515</v>
+        <v>994</v>
       </c>
     </row>
     <row r="285" spans="2:2">
       <c r="B285" t="s">
-        <v>994</v>
+        <v>515</v>
       </c>
     </row>
     <row r="286" spans="2:2">
       <c r="B286" t="s">
-        <v>516</v>
+        <v>997</v>
       </c>
     </row>
     <row r="287" spans="2:2">
       <c r="B287" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="288" spans="2:2">
       <c r="B288" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="289" spans="2:2">
       <c r="B289" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="290" spans="2:2">
       <c r="B290" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="291" spans="2:2">
       <c r="B291" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="292" spans="2:2">
       <c r="B292" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="293" spans="2:2">
       <c r="B293" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="294" spans="2:2">
       <c r="B294" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="295" spans="2:2">
       <c r="B295" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="296" spans="2:2">
       <c r="B296" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="297" spans="2:2">
       <c r="B297" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="298" spans="2:2">
       <c r="B298" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
     </row>
     <row r="299" spans="2:2">
       <c r="B299" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="300" spans="2:2">
       <c r="B300" t="s">
-        <v>1050</v>
+        <v>543</v>
       </c>
     </row>
     <row r="301" spans="2:2">
       <c r="B301" t="s">
-        <v>545</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="302" spans="2:2">
       <c r="B302" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="303" spans="2:2">
       <c r="B303" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="304" spans="2:2">
       <c r="B304" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="305" spans="2:2">
       <c r="B305" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="306" spans="2:2">
       <c r="B306" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="307" spans="2:2">
       <c r="B307" t="s">
-        <v>996</v>
+        <v>555</v>
       </c>
     </row>
     <row r="308" spans="2:2">
       <c r="B308" t="s">
-        <v>557</v>
+        <v>999</v>
       </c>
     </row>
     <row r="309" spans="2:2">
       <c r="B309" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
     </row>
     <row r="310" spans="2:2">
       <c r="B310" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="311" spans="2:2">
       <c r="B311" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="312" spans="2:2">
       <c r="B312" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="313" spans="2:2">
       <c r="B313" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
     </row>
     <row r="314" spans="2:2">
       <c r="B314" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="315" spans="2:2">
       <c r="B315" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
     <row r="316" spans="2:2">
       <c r="B316" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="317" spans="2:2">
       <c r="B317" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="318" spans="2:2">
       <c r="B318" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="319" spans="2:2">
       <c r="B319" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="320" spans="2:2">
       <c r="B320" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
     </row>
     <row r="321" spans="2:2">
       <c r="B321" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="322" spans="2:2">
       <c r="B322" t="s">
-        <v>999</v>
+        <v>582</v>
       </c>
     </row>
     <row r="323" spans="2:2">
       <c r="B323" t="s">
-        <v>585</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="324" spans="2:2">
       <c r="B324" t="s">
-        <v>1002</v>
+        <v>585</v>
       </c>
     </row>
     <row r="325" spans="2:2">
       <c r="B325" t="s">
-        <v>587</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="326" spans="2:2">
       <c r="B326" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
     </row>
     <row r="327" spans="2:2">
       <c r="B327" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="328" spans="2:2">
       <c r="B328" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
     </row>
     <row r="329" spans="2:2">
       <c r="B329" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="330" spans="2:2">
       <c r="B330" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
     </row>
     <row r="331" spans="2:2">
       <c r="B331" t="s">
-        <v>1086</v>
+        <v>596</v>
       </c>
     </row>
     <row r="332" spans="2:2">
       <c r="B332" t="s">
-        <v>598</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="333" spans="2:2">
       <c r="B333" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
     </row>
     <row r="334" spans="2:2">
       <c r="B334" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="335" spans="2:2">
       <c r="B335" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="336" spans="2:2">
       <c r="B336" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
     </row>
     <row r="337" spans="2:2">
       <c r="B337" t="s">
-        <v>1114</v>
+        <v>606</v>
       </c>
     </row>
     <row r="338" spans="2:2">
       <c r="B338" t="s">
-        <v>608</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="339" spans="2:2">
       <c r="B339" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="340" spans="2:2">
       <c r="B340" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="341" spans="2:2">
       <c r="B341" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="342" spans="2:2">
       <c r="B342" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="343" spans="2:2">
       <c r="B343" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="344" spans="2:2">
       <c r="B344" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="345" spans="2:2">
       <c r="B345" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="346" spans="2:2">
       <c r="B346" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
     </row>
     <row r="347" spans="2:2">
       <c r="B347" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
     </row>
     <row r="348" spans="2:2">
       <c r="B348" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
     </row>
     <row r="349" spans="2:2">
       <c r="B349" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
     </row>
     <row r="350" spans="2:2">
       <c r="B350" t="s">
-        <v>1005</v>
+        <v>630</v>
       </c>
     </row>
     <row r="351" spans="2:2">
@@ -13652,692 +13661,692 @@
     </row>
     <row r="352" spans="2:2">
       <c r="B352" t="s">
-        <v>632</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="353" spans="2:2">
       <c r="B353" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="354" spans="2:2">
       <c r="B354" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
     </row>
     <row r="355" spans="2:2">
       <c r="B355" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
     </row>
     <row r="356" spans="2:2">
       <c r="B356" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
     </row>
     <row r="357" spans="2:2">
       <c r="B357" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
     </row>
     <row r="358" spans="2:2">
       <c r="B358" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
     </row>
     <row r="359" spans="2:2">
       <c r="B359" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
     </row>
     <row r="360" spans="2:2">
       <c r="B360" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
     </row>
     <row r="361" spans="2:2">
       <c r="B361" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
     </row>
     <row r="362" spans="2:2">
       <c r="B362" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
     </row>
     <row r="363" spans="2:2">
       <c r="B363" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
     </row>
     <row r="364" spans="2:2">
       <c r="B364" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
     </row>
     <row r="365" spans="2:2">
       <c r="B365" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
     </row>
     <row r="366" spans="2:2">
       <c r="B366" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
     </row>
     <row r="367" spans="2:2">
       <c r="B367" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
     </row>
     <row r="368" spans="2:2">
       <c r="B368" t="s">
-        <v>1052</v>
+        <v>664</v>
       </c>
     </row>
     <row r="369" spans="2:2">
       <c r="B369" t="s">
-        <v>1011</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="370" spans="2:2">
       <c r="B370" t="s">
-        <v>665</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="371" spans="2:2">
       <c r="B371" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
     </row>
     <row r="372" spans="2:2">
       <c r="B372" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="373" spans="2:2">
       <c r="B373" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
     </row>
     <row r="374" spans="2:2">
       <c r="B374" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
     </row>
     <row r="375" spans="2:2">
       <c r="B375" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
     </row>
     <row r="376" spans="2:2">
       <c r="B376" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
     </row>
     <row r="377" spans="2:2">
       <c r="B377" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
     </row>
     <row r="378" spans="2:2">
       <c r="B378" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
     </row>
     <row r="379" spans="2:2">
       <c r="B379" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
     </row>
     <row r="380" spans="2:2">
       <c r="B380" t="s">
-        <v>1013</v>
+        <v>683</v>
       </c>
     </row>
     <row r="381" spans="2:2">
       <c r="B381" t="s">
-        <v>685</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="382" spans="2:2">
       <c r="B382" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
     </row>
     <row r="383" spans="2:2">
       <c r="B383" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
     </row>
     <row r="384" spans="2:2">
       <c r="B384" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
     </row>
     <row r="385" spans="2:2">
       <c r="B385" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
     </row>
     <row r="386" spans="2:2">
       <c r="B386" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
     </row>
     <row r="387" spans="2:2">
       <c r="B387" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
     </row>
     <row r="388" spans="2:2">
       <c r="B388" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
     </row>
     <row r="389" spans="2:2">
       <c r="B389" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="390" spans="2:2">
       <c r="B390" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
     </row>
     <row r="391" spans="2:2">
       <c r="B391" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
     </row>
     <row r="392" spans="2:2">
       <c r="B392" t="s">
-        <v>1015</v>
+        <v>706</v>
       </c>
     </row>
     <row r="393" spans="2:2">
       <c r="B393" t="s">
-        <v>708</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="394" spans="2:2">
       <c r="B394" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
     </row>
     <row r="395" spans="2:2">
       <c r="B395" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
     </row>
     <row r="396" spans="2:2">
       <c r="B396" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="397" spans="2:2">
       <c r="B397" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
     </row>
     <row r="398" spans="2:2">
       <c r="B398" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
     </row>
     <row r="399" spans="2:2">
       <c r="B399" t="s">
-        <v>1098</v>
+        <v>718</v>
       </c>
     </row>
     <row r="400" spans="2:2">
       <c r="B400" t="s">
-        <v>720</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="401" spans="2:2">
       <c r="B401" t="s">
-        <v>1018</v>
+        <v>720</v>
       </c>
     </row>
     <row r="402" spans="2:2">
       <c r="B402" t="s">
-        <v>722</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="403" spans="2:2">
       <c r="B403" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="404" spans="2:2">
       <c r="B404" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
     </row>
     <row r="405" spans="2:2">
       <c r="B405" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
     </row>
     <row r="406" spans="2:2">
       <c r="B406" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
     </row>
     <row r="407" spans="2:2">
       <c r="B407" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
     </row>
     <row r="408" spans="2:2">
       <c r="B408" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
     </row>
     <row r="409" spans="2:2">
       <c r="B409" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
     </row>
     <row r="410" spans="2:2">
       <c r="B410" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
     </row>
     <row r="411" spans="2:2">
       <c r="B411" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
     </row>
     <row r="412" spans="2:2">
       <c r="B412" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
     </row>
     <row r="413" spans="2:2">
       <c r="B413" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
     </row>
     <row r="414" spans="2:2">
       <c r="B414" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
     </row>
     <row r="415" spans="2:2">
       <c r="B415" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
     </row>
     <row r="416" spans="2:2">
       <c r="B416" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
     </row>
     <row r="417" spans="2:2">
       <c r="B417" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
     </row>
     <row r="418" spans="2:2">
       <c r="B418" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
     </row>
     <row r="419" spans="2:2">
       <c r="B419" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
     </row>
     <row r="420" spans="2:2">
       <c r="B420" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
     </row>
     <row r="421" spans="2:2">
       <c r="B421" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
     </row>
     <row r="422" spans="2:2">
       <c r="B422" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
     </row>
     <row r="423" spans="2:2">
       <c r="B423" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
     </row>
     <row r="424" spans="2:2">
       <c r="B424" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
     </row>
     <row r="425" spans="2:2">
       <c r="B425" t="s">
-        <v>1118</v>
+        <v>765</v>
       </c>
     </row>
     <row r="426" spans="2:2">
       <c r="B426" t="s">
-        <v>767</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="427" spans="2:2">
       <c r="B427" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
     </row>
     <row r="428" spans="2:2">
       <c r="B428" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
     </row>
     <row r="429" spans="2:2">
       <c r="B429" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
     </row>
     <row r="430" spans="2:2">
       <c r="B430" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
     </row>
     <row r="431" spans="2:2">
       <c r="B431" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
     </row>
     <row r="432" spans="2:2">
       <c r="B432" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
     </row>
     <row r="433" spans="2:2">
       <c r="B433" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="434" spans="2:2">
       <c r="B434" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
     </row>
     <row r="435" spans="2:2">
       <c r="B435" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="436" spans="2:2">
       <c r="B436" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
     </row>
     <row r="437" spans="2:2">
       <c r="B437" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
     <row r="438" spans="2:2">
       <c r="B438" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
     </row>
     <row r="439" spans="2:2">
       <c r="B439" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
     </row>
     <row r="440" spans="2:2">
       <c r="B440" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
     </row>
     <row r="441" spans="2:2">
       <c r="B441" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
     </row>
     <row r="442" spans="2:2">
       <c r="B442" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
     </row>
     <row r="443" spans="2:2">
       <c r="B443" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
     </row>
     <row r="444" spans="2:2">
       <c r="B444" t="s">
-        <v>1122</v>
+        <v>803</v>
       </c>
     </row>
     <row r="445" spans="2:2">
       <c r="B445" t="s">
-        <v>1104</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="446" spans="2:2">
       <c r="B446" t="s">
-        <v>805</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="447" spans="2:2">
       <c r="B447" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
     </row>
     <row r="448" spans="2:2">
       <c r="B448" t="s">
-        <v>1106</v>
+        <v>807</v>
       </c>
     </row>
     <row r="449" spans="2:2">
       <c r="B449" t="s">
-        <v>1021</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="450" spans="2:2">
       <c r="B450" t="s">
-        <v>809</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="451" spans="2:2">
       <c r="B451" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
     </row>
     <row r="452" spans="2:2">
       <c r="B452" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
     </row>
     <row r="453" spans="2:2">
       <c r="B453" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
     </row>
     <row r="454" spans="2:2">
       <c r="B454" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
     </row>
     <row r="455" spans="2:2">
       <c r="B455" t="s">
-        <v>1054</v>
+        <v>817</v>
       </c>
     </row>
     <row r="456" spans="2:2">
       <c r="B456" t="s">
-        <v>819</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="457" spans="2:2">
       <c r="B457" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
     </row>
     <row r="458" spans="2:2">
       <c r="B458" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
     </row>
     <row r="459" spans="2:2">
       <c r="B459" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
     </row>
     <row r="460" spans="2:2">
       <c r="B460" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
     </row>
     <row r="461" spans="2:2">
       <c r="B461" t="s">
-        <v>1056</v>
+        <v>827</v>
       </c>
     </row>
     <row r="462" spans="2:2">
       <c r="B462" t="s">
-        <v>829</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="463" spans="2:2">
       <c r="B463" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="464" spans="2:2">
       <c r="B464" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
     </row>
     <row r="465" spans="2:2">
       <c r="B465" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
     </row>
     <row r="466" spans="2:2">
       <c r="B466" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
     </row>
     <row r="467" spans="2:2">
       <c r="B467" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
     </row>
     <row r="468" spans="2:2">
       <c r="B468" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="469" spans="2:2">
       <c r="B469" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="470" spans="2:2">
       <c r="B470" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
     </row>
     <row r="471" spans="2:2">
       <c r="B471" t="s">
-        <v>1058</v>
+        <v>845</v>
       </c>
     </row>
     <row r="472" spans="2:2">
       <c r="B472" t="s">
-        <v>847</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="473" spans="2:2">
       <c r="B473" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
     </row>
     <row r="474" spans="2:2">
       <c r="B474" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
     </row>
     <row r="475" spans="2:2">
       <c r="B475" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
     </row>
     <row r="476" spans="2:2">
       <c r="B476" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="477" spans="2:2">
       <c r="B477" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
     </row>
     <row r="478" spans="2:2">
       <c r="B478" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
     </row>
     <row r="479" spans="2:2">
       <c r="B479" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
     </row>
     <row r="480" spans="2:2">
       <c r="B480" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
     </row>
     <row r="481" spans="2:2">
       <c r="B481" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
     </row>
     <row r="482" spans="2:2">
       <c r="B482" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
     </row>
     <row r="483" spans="2:2">
       <c r="B483" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
     </row>
     <row r="484" spans="2:2">
       <c r="B484" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
     </row>
     <row r="485" spans="2:2">
       <c r="B485" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
     </row>
     <row r="486" spans="2:2">
       <c r="B486" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
     </row>
     <row r="487" spans="2:2">
       <c r="B487" t="s">
-        <v>1024</v>
+        <v>875</v>
       </c>
     </row>
     <row r="488" spans="2:2">
       <c r="B488" t="s">
-        <v>877</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="489" spans="2:2">
       <c r="B489" t="s">
-        <v>1026</v>
+        <v>877</v>
       </c>
     </row>
     <row r="490" spans="2:2">
@@ -14347,211 +14356,216 @@
     </row>
     <row r="491" spans="2:2">
       <c r="B491" t="s">
-        <v>879</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="492" spans="2:2">
       <c r="B492" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
     </row>
     <row r="493" spans="2:2">
       <c r="B493" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
     </row>
     <row r="494" spans="2:2">
       <c r="B494" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
     </row>
     <row r="495" spans="2:2">
       <c r="B495" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
     </row>
     <row r="496" spans="2:2">
       <c r="B496" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
     </row>
     <row r="497" spans="2:2">
       <c r="B497" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
     </row>
     <row r="498" spans="2:2">
       <c r="B498" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
     </row>
     <row r="499" spans="2:2">
       <c r="B499" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
     </row>
     <row r="500" spans="2:2">
       <c r="B500" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
     </row>
     <row r="501" spans="2:2">
       <c r="B501" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
     </row>
     <row r="502" spans="2:2">
       <c r="B502" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
     </row>
     <row r="503" spans="2:2">
       <c r="B503" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
     </row>
     <row r="504" spans="2:2">
       <c r="B504" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
     </row>
     <row r="505" spans="2:2">
       <c r="B505" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
     </row>
     <row r="506" spans="2:2">
       <c r="B506" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="507" spans="2:2">
       <c r="B507" t="s">
-        <v>1089</v>
+        <v>910</v>
       </c>
     </row>
     <row r="508" spans="2:2">
       <c r="B508" t="s">
-        <v>912</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="509" spans="2:2">
       <c r="B509" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
     </row>
     <row r="510" spans="2:2">
       <c r="B510" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
     </row>
     <row r="511" spans="2:2">
       <c r="B511" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
     </row>
     <row r="512" spans="2:2">
       <c r="B512" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
     </row>
     <row r="513" spans="1:2">
       <c r="B513" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
     </row>
     <row r="514" spans="1:2">
       <c r="B514" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
     </row>
     <row r="515" spans="1:2">
       <c r="B515" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
     </row>
     <row r="516" spans="1:2">
       <c r="B516" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="517" spans="1:2">
       <c r="B517" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
     </row>
     <row r="518" spans="1:2">
       <c r="B518" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
     </row>
     <row r="519" spans="1:2">
       <c r="B519" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
     </row>
     <row r="520" spans="1:2">
       <c r="B520" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="521" spans="1:2">
+      <c r="B521" t="s">
         <v>937</v>
       </c>
     </row>
-    <row r="522" spans="1:2">
-      <c r="A522" t="s">
-        <v>1128</v>
-      </c>
-      <c r="B522" t="s">
-        <v>1073</v>
-      </c>
-    </row>
     <row r="523" spans="1:2">
+      <c r="A523" t="s">
+        <v>1131</v>
+      </c>
       <c r="B523" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="524" spans="1:2">
       <c r="B524" t="s">
-        <v>958</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="525" spans="1:2">
       <c r="B525" t="s">
-        <v>967</v>
+        <v>958</v>
       </c>
     </row>
     <row r="526" spans="1:2">
       <c r="B526" t="s">
-        <v>1082</v>
+        <v>967</v>
       </c>
     </row>
     <row r="527" spans="1:2">
       <c r="B527" t="s">
-        <v>975</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="528" spans="1:2">
       <c r="B528" t="s">
-        <v>986</v>
-      </c>
-    </row>
-    <row r="530" spans="1:2">
-      <c r="A530" t="s">
-        <v>1129</v>
-      </c>
-      <c r="B530" t="s">
-        <v>1038</v>
-      </c>
-    </row>
-    <row r="532" spans="1:2">
-      <c r="A532" t="s">
-        <v>1130</v>
-      </c>
-      <c r="B532" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="529" spans="1:2">
+      <c r="B529" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="531" spans="1:2">
+      <c r="A531" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B531" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="533" spans="1:2">
+      <c r="A533" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B533" t="s">
         <v>955</v>
       </c>
     </row>
-    <row r="533" spans="1:2">
-      <c r="B533" t="s">
-        <v>1018</v>
+    <row r="534" spans="1:2">
+      <c r="B534" t="s">
+        <v>1021</v>
       </c>
     </row>
   </sheetData>
@@ -14561,7 +14575,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="110.7109375" customWidth="1"/>
@@ -14834,7 +14848,7 @@
         <v>980</v>
       </c>
       <c r="B17">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="C17" t="s">
         <v>981</v>
@@ -14851,7 +14865,7 @@
         <v>983</v>
       </c>
       <c r="B18">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="C18" t="s">
         <v>984</v>
@@ -14868,7 +14882,7 @@
         <v>986</v>
       </c>
       <c r="B19">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="C19" t="s">
         <v>987</v>
@@ -14877,24 +14891,24 @@
         <v>8</v>
       </c>
       <c r="E19" t="s">
-        <v>960</v>
+        <v>988</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="B20">
-        <v>1.6</v>
+        <v>1.88</v>
       </c>
       <c r="C20" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="D20" t="s">
         <v>8</v>
       </c>
       <c r="E20" t="s">
-        <v>990</v>
+        <v>960</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -14902,7 +14916,7 @@
         <v>991</v>
       </c>
       <c r="B21">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="C21" t="s">
         <v>992</v>
@@ -14919,7 +14933,7 @@
         <v>994</v>
       </c>
       <c r="B22">
-        <v>1.95</v>
+        <v>2.9</v>
       </c>
       <c r="C22" t="s">
         <v>995</v>
@@ -14928,24 +14942,24 @@
         <v>8</v>
       </c>
       <c r="E22" t="s">
-        <v>951</v>
+        <v>996</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="B23">
-        <v>2.9</v>
+        <v>1.95</v>
       </c>
       <c r="C23" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="D23" t="s">
         <v>8</v>
       </c>
       <c r="E23" t="s">
-        <v>998</v>
+        <v>951</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -14953,7 +14967,7 @@
         <v>999</v>
       </c>
       <c r="B24">
-        <v>2.48</v>
+        <v>2.9</v>
       </c>
       <c r="C24" t="s">
         <v>1000</v>
@@ -14970,7 +14984,7 @@
         <v>1002</v>
       </c>
       <c r="B25">
-        <v>3.2</v>
+        <v>2.48</v>
       </c>
       <c r="C25" t="s">
         <v>1003</v>
@@ -14987,7 +15001,7 @@
         <v>1005</v>
       </c>
       <c r="B26">
-        <v>1.97</v>
+        <v>3.2</v>
       </c>
       <c r="C26" t="s">
         <v>1006</v>
@@ -15004,7 +15018,7 @@
         <v>1008</v>
       </c>
       <c r="B27">
-        <v>2.3</v>
+        <v>1.97</v>
       </c>
       <c r="C27" t="s">
         <v>1009</v>
@@ -15030,41 +15044,41 @@
         <v>8</v>
       </c>
       <c r="E28" t="s">
-        <v>951</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="B29">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="C29" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D29" t="s">
         <v>8</v>
       </c>
       <c r="E29" t="s">
-        <v>985</v>
+        <v>951</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="B30">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="C30" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="D30" t="s">
         <v>8</v>
       </c>
       <c r="E30" t="s">
-        <v>1017</v>
+        <v>988</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -15072,7 +15086,7 @@
         <v>1018</v>
       </c>
       <c r="B31">
-        <v>1.66</v>
+        <v>2.04</v>
       </c>
       <c r="C31" t="s">
         <v>1019</v>
@@ -15089,7 +15103,7 @@
         <v>1021</v>
       </c>
       <c r="B32">
-        <v>2.48</v>
+        <v>1.66</v>
       </c>
       <c r="C32" t="s">
         <v>1022</v>
@@ -15106,7 +15120,7 @@
         <v>1024</v>
       </c>
       <c r="B33">
-        <v>2.8</v>
+        <v>2.48</v>
       </c>
       <c r="C33" t="s">
         <v>1025</v>
@@ -15115,24 +15129,24 @@
         <v>8</v>
       </c>
       <c r="E33" t="s">
-        <v>954</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B34">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="C34" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="D34" t="s">
         <v>8</v>
       </c>
       <c r="E34" t="s">
-        <v>1028</v>
+        <v>954</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -15140,7 +15154,7 @@
         <v>1029</v>
       </c>
       <c r="B35">
-        <v>2.02</v>
+        <v>2.5</v>
       </c>
       <c r="C35" t="s">
         <v>1030</v>
@@ -15149,6 +15163,23 @@
         <v>8</v>
       </c>
       <c r="E35" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B36">
+        <v>2.02</v>
+      </c>
+      <c r="C36" t="s">
+        <v>1033</v>
+      </c>
+      <c r="D36" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" t="s">
         <v>948</v>
       </c>
     </row>
@@ -15169,7 +15200,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -15191,189 +15222,189 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="B3">
         <v>2.7</v>
       </c>
       <c r="C3" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>1035</v>
+        <v>1038</v>
       </c>
       <c r="B4">
         <v>2.59</v>
       </c>
       <c r="C4" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="D4" t="s">
         <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>1037</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>1038</v>
+        <v>1041</v>
       </c>
       <c r="B5">
         <v>3.18</v>
       </c>
       <c r="C5" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="D5" t="s">
         <v>8</v>
       </c>
       <c r="E5" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="B6">
         <v>1.75</v>
       </c>
       <c r="C6" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="D6" t="s">
         <v>8</v>
       </c>
       <c r="E6" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="B7">
         <v>1.88</v>
       </c>
       <c r="C7" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
       <c r="D7" t="s">
         <v>8</v>
       </c>
       <c r="E7" t="s">
-        <v>1046</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>1047</v>
+        <v>1050</v>
       </c>
       <c r="B8">
         <v>2.66</v>
       </c>
       <c r="C8" t="s">
-        <v>1048</v>
+        <v>1051</v>
       </c>
       <c r="D8" t="s">
         <v>8</v>
       </c>
       <c r="E8" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
       <c r="B9">
         <v>1.76</v>
       </c>
       <c r="C9" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="D9" t="s">
         <v>8</v>
       </c>
       <c r="E9" t="s">
-        <v>1046</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
       <c r="B10">
         <v>1.84</v>
       </c>
       <c r="C10" t="s">
-        <v>1053</v>
+        <v>1056</v>
       </c>
       <c r="D10" t="s">
         <v>8</v>
       </c>
       <c r="E10" t="s">
-        <v>1046</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>1054</v>
+        <v>1057</v>
       </c>
       <c r="B11">
         <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
       <c r="D11" t="s">
         <v>8</v>
       </c>
       <c r="E11" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
       <c r="B12">
         <v>1.92</v>
       </c>
       <c r="C12" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
       <c r="D12" t="s">
         <v>8</v>
       </c>
       <c r="E12" t="s">
-        <v>1046</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
       <c r="B13">
         <v>1.77</v>
       </c>
       <c r="C13" t="s">
-        <v>1059</v>
+        <v>1062</v>
       </c>
       <c r="D13" t="s">
         <v>8</v>
       </c>
       <c r="E13" t="s">
-        <v>1046</v>
+        <v>1049</v>
       </c>
     </row>
   </sheetData>
@@ -15393,7 +15424,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>1060</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -15415,19 +15446,19 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
       <c r="B3">
         <v>2.2</v>
       </c>
       <c r="C3" t="s">
-        <v>1062</v>
+        <v>1065</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>1063</v>
+        <v>1066</v>
       </c>
     </row>
   </sheetData>
@@ -15447,7 +15478,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>1064</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -15469,19 +15500,19 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>1065</v>
+        <v>1068</v>
       </c>
       <c r="B3">
         <v>1.32</v>
       </c>
       <c r="C3" t="s">
-        <v>1066</v>
+        <v>1069</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>1067</v>
+        <v>1070</v>
       </c>
     </row>
   </sheetData>
@@ -15501,7 +15532,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>1068</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -15523,19 +15554,19 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
       <c r="B3">
         <v>2.45</v>
       </c>
       <c r="C3" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
     </row>
   </sheetData>
@@ -15555,7 +15586,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>1072</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -15577,19 +15608,19 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
       <c r="B3">
         <v>1.45</v>
       </c>
       <c r="C3" t="s">
-        <v>1074</v>
+        <v>1077</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
     </row>
   </sheetData>
@@ -15609,7 +15640,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>1076</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -15631,47 +15662,47 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
       <c r="B3">
         <v>1.9</v>
       </c>
       <c r="C3" t="s">
-        <v>1078</v>
+        <v>1081</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>1079</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>1080</v>
+        <v>1083</v>
       </c>
       <c r="B4">
         <v>2.11</v>
       </c>
       <c r="C4" t="s">
-        <v>1081</v>
+        <v>1084</v>
       </c>
       <c r="D4" t="s">
         <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>1079</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>1082</v>
+        <v>1085</v>
       </c>
       <c r="B5">
         <v>2.7</v>
       </c>
       <c r="C5" t="s">
-        <v>1083</v>
+        <v>1086</v>
       </c>
       <c r="D5" t="s">
         <v>8</v>
@@ -15682,13 +15713,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>1084</v>
+        <v>1087</v>
       </c>
       <c r="B6">
         <v>2.58</v>
       </c>
       <c r="C6" t="s">
-        <v>1085</v>
+        <v>1088</v>
       </c>
       <c r="D6" t="s">
         <v>8</v>
@@ -15699,30 +15730,30 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>1086</v>
+        <v>1089</v>
       </c>
       <c r="B7">
         <v>1.93</v>
       </c>
       <c r="C7" t="s">
-        <v>1087</v>
+        <v>1090</v>
       </c>
       <c r="D7" t="s">
         <v>8</v>
       </c>
       <c r="E7" t="s">
-        <v>1088</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>1089</v>
+        <v>1092</v>
       </c>
       <c r="B8">
         <v>2.05</v>
       </c>
       <c r="C8" t="s">
-        <v>1090</v>
+        <v>1093</v>
       </c>
       <c r="D8" t="s">
         <v>8</v>
@@ -15748,7 +15779,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>1091</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -15770,13 +15801,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>1092</v>
+        <v>1095</v>
       </c>
       <c r="B3">
         <v>0.93</v>
       </c>
       <c r="C3" t="s">
-        <v>1093</v>
+        <v>1096</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
